--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -1929,17 +1929,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1981,516 +1981,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -8001,17 +8001,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8053,1746 +8053,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CLOT by Edison Chen x adidas Superstar DS 'Coffee'</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WMNS 'Soft Yellow' From £ 185</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nike Astra Ultra WMNS 'Black' From £ 100</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Patta x Nike Air Max 1 ’87 'Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Solebox x Clarks Wallabee 'Black'</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Adidas Anthony Edwards 2 Georgia Bulldogs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 High OG Pale Ivory / Psychic Blue</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 High OG WMNS 'Psychic Blue' From £ 163</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG 'Rabbit Floral Swoosh' From £ 145</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail / Off White</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 GS Imperial Purple / Multi</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 OG Lakers</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Clot x Adidas Superstar Footwear White / Coffee</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z 'Metallic Hematite Grey'</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z Calistra 'Black'</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 Zip 'Phantom &amp; Light Crimson' From £ 185</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Shox Ride 2 Black / Metallic Dark Grey</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Soft Pearl / Sail</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Balenciaga City WMNS Silver</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>New Balance 1890 'Faded Black &amp; Utility Green' From £ 160</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 190</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -2611,10 +2611,14 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2627,7 +2631,7 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr"/>
@@ -2661,14 +2665,10 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr"/>
       <c r="I42" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr"/>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr"/>
@@ -2769,10 +2769,14 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2785,7 +2789,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -2819,14 +2823,10 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr"/>
       <c r="I45" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -2873,10 +2873,14 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2889,7 +2893,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -2923,7 +2927,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr"/>
@@ -2939,7 +2943,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -2973,14 +2977,10 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -6299,7 +6299,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -6319,7 +6319,7 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -6353,10 +6353,14 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr"/>
@@ -6403,14 +6407,10 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr"/>
       <c r="I42" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6423,7 +6423,7 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr"/>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr"/>
@@ -6511,10 +6511,14 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6527,7 +6531,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -6561,14 +6565,10 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr"/>
       <c r="I45" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -6615,10 +6615,14 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6631,7 +6635,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -6665,7 +6669,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr"/>
@@ -6681,7 +6685,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -6715,14 +6719,10 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -8001,17 +8001,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8053,6 +8053,66 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T08:00:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T08:00:50Z</t>
         </is>
       </c>
     </row>
@@ -10395,7 +10455,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10415,7 +10475,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -10457,10 +10517,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10473,7 +10537,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -10515,14 +10579,10 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10535,7 +10595,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -10577,12 +10637,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10597,13 +10657,13 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
         <v>50</v>
@@ -10639,10 +10699,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10655,13 +10719,13 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>50</v>
@@ -10697,14 +10761,10 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10717,7 +10777,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -10759,10 +10819,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10775,7 +10839,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -10817,7 +10881,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -10833,7 +10897,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -10875,14 +10939,10 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10895,7 +10955,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -8001,17 +8001,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8053,66 +8053,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:00:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:00:50Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -2403,7 +2403,9 @@
       <c r="A36" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="n">
+        <v>219</v>
+      </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2513,7 +2515,9 @@
       <c r="A38" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="n">
+        <v>299</v>
+      </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -2912,7 +2916,9 @@
       <c r="A45" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>400</v>
+      </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -7780,7 +7786,9 @@
       <c r="A36" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="n">
+        <v>219</v>
+      </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7890,7 +7898,9 @@
       <c r="A38" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="n">
+        <v>299</v>
+      </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -8289,7 +8299,9 @@
       <c r="A45" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>400</v>
+      </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -11282,17 +11294,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11334,2274 +11346,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>App entry Nike Grade School Air Griffey Max OG BOYS GRADE SCHOOL • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>App entry Nike Griffey Max 1 MENS • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>App entry Nike Grade School Air Griffey Max OG BOYS GRADE SCHOOL • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>App entry Nike Griffey Max 1 MENS • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -15746,7 +13490,7 @@
         <v>46088</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -15872,7 +13616,7 @@
         <v>46088</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -16327,7 +14071,7 @@
         <v>46088</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -780,12 +780,12 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -837,12 +837,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr"/>
@@ -872,9 +872,9 @@
         <v>46089</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -889,15 +889,19 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -913,7 +917,7 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr"/>
@@ -4779,9 +4783,9 @@
         <v>46099</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4796,23 +4800,27 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K79" s="9" t="n">
@@ -4820,7 +4828,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -4829,7 +4837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -4849,12 +4857,12 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr"/>
@@ -4873,7 +4881,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -4882,7 +4890,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr">
@@ -4902,19 +4910,15 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4930,7 +4934,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -4939,7 +4943,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="11" t="inlineStr">
@@ -4959,15 +4963,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4983,7 +4991,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -5012,12 +5020,12 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr"/>
@@ -5036,7 +5044,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -5045,7 +5053,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr">
@@ -5065,23 +5073,23 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K84" s="9" t="n">
@@ -5089,7 +5097,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -5098,12 +5106,12 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -5118,27 +5126,23 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr"/>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
@@ -5146,7 +5150,7 @@
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -5155,17 +5159,17 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -5175,15 +5179,19 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5195,11 +5203,11 @@
         </is>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -5216,9 +5224,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -5233,7 +5241,7 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr"/>
@@ -5248,11 +5256,11 @@
         </is>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -5286,14 +5294,10 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5309,7 +5313,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -5318,7 +5322,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="11" t="inlineStr">
@@ -5343,22 +5347,22 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K89" s="9" t="n">
@@ -5366,7 +5370,7 @@
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -5640,12 +5644,12 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -5663,7 +5667,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -5697,12 +5701,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -5720,7 +5724,7 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr"/>
@@ -5732,9 +5736,9 @@
         <v>46089</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5749,15 +5753,19 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -5773,7 +5781,7 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr"/>
@@ -9639,9 +9647,9 @@
         <v>46099</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -9656,23 +9664,27 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K79" s="9" t="n">
@@ -9680,7 +9692,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -9689,7 +9701,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -9709,12 +9721,12 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr"/>
@@ -9733,7 +9745,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -9742,7 +9754,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr">
@@ -9762,19 +9774,15 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9790,7 +9798,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -9799,7 +9807,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="11" t="inlineStr">
@@ -9819,15 +9827,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9843,7 +9855,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -9872,12 +9884,12 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr"/>
@@ -9896,7 +9908,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -9905,7 +9917,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr">
@@ -9925,23 +9937,23 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K84" s="9" t="n">
@@ -9949,7 +9961,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -9958,12 +9970,12 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -9978,27 +9990,23 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr"/>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
@@ -10006,7 +10014,7 @@
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -10015,17 +10023,17 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -10035,15 +10043,19 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10055,11 +10067,11 @@
         </is>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -10076,9 +10088,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -10093,7 +10105,7 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr"/>
@@ -10108,11 +10120,11 @@
         </is>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -10146,14 +10158,10 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10169,7 +10177,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -10178,7 +10186,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="11" t="inlineStr">
@@ -10203,22 +10211,22 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K89" s="9" t="n">
@@ -10226,7 +10234,7 @@
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -10248,13 +10256,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="61" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -10306,22 +10314,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -10329,7 +10337,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -10341,17 +10349,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10359,29 +10367,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>adidas Originals Anthony Edwards 2 ASW PE BOYS GRADE SCHOOL • MULTI/MULTI</t>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -10389,7 +10397,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -10401,17 +10409,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG WMNS 'Psychic Blue' From £ 163</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -10419,1627 +10427,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG 'Rabbit Floral Swoosh' From £ 145</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 HI OG Remastered GIRLS TODDLER • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z 'Metallic Hematite Grey'</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z Calistra 'Black'</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 Zip 'Phantom &amp; Light Crimson' From £ 185</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -12322,12 +10710,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -12345,7 +10733,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -12387,12 +10775,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -12410,13 +10798,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
         <v>50</v>
@@ -12432,7 +10820,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12447,15 +10835,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -12471,13 +10863,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="P6" t="n">
         <v>50</v>
@@ -16907,7 +15299,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -16922,23 +15314,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16946,13 +15342,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P77" t="n">
         <v>50</v>
@@ -16961,7 +15357,7 @@
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -16983,12 +15379,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -17007,7 +15403,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -17022,7 +15418,7 @@
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -17044,19 +15440,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17072,13 +15464,13 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
         <v>50</v>
@@ -17087,7 +15479,7 @@
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -17109,15 +15501,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17133,13 +15529,13 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>50</v>
@@ -17170,12 +15566,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -17194,7 +15590,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -17209,7 +15605,7 @@
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -17231,23 +15627,23 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -17255,13 +15651,13 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P82" t="n">
         <v>50</v>
@@ -17270,14 +15666,14 @@
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -17292,27 +15688,23 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -17320,13 +15712,13 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P83" t="n">
         <v>50</v>
@@ -17335,19 +15727,19 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -17357,15 +15749,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17377,20 +15773,20 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P84" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
@@ -17408,7 +15804,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -17423,7 +15819,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -17438,11 +15834,11 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -17451,7 +15847,7 @@
         <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
@@ -17484,14 +15880,10 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17507,7 +15899,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -17522,7 +15914,7 @@
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -17549,22 +15941,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -17572,7 +15964,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -17765,7 +16157,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -17793,7 +16185,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -17813,7 +16205,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -17849,17 +16241,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -17911,7 +16303,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -17921,7 +16313,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1326,10 +1326,14 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1379,14 +1383,10 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1489,10 +1489,14 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1508,7 +1512,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1542,12 +1546,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1599,12 +1603,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -1622,7 +1626,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1656,12 +1660,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -1679,7 +1683,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1713,12 +1717,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1770,7 +1774,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -1793,7 +1797,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -1850,7 +1854,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1884,14 +1888,10 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1941,10 +1941,14 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1960,7 +1964,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -3041,10 +3045,14 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5205,6 +5213,63 @@
       <c r="M86" s="10" t="inlineStr"/>
       <c r="N86" s="10" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5221,7 +5286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -5913,7 +5978,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -5932,7 +5997,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -5966,7 +6031,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -5985,7 +6050,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -6019,10 +6084,14 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6038,7 +6107,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -6072,14 +6141,10 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6095,7 +6160,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -6129,7 +6194,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -6148,7 +6213,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -6182,10 +6247,14 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6201,7 +6270,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -6235,12 +6304,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -6258,7 +6327,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -6292,12 +6361,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -6315,7 +6384,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -6349,12 +6418,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -6372,7 +6441,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -6406,12 +6475,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -6429,7 +6498,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -6463,7 +6532,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -6486,7 +6555,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -6520,7 +6589,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -6543,7 +6612,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -6577,14 +6646,10 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6600,7 +6665,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -6634,10 +6699,14 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6653,7 +6722,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -7734,10 +7803,14 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -9898,6 +9971,63 @@
       <c r="M86" s="10" t="inlineStr"/>
       <c r="N86" s="10" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9914,12 +10044,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -9972,22 +10102,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -9995,7 +10125,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -10007,17 +10137,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10025,29 +10155,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -10055,7 +10185,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -10067,17 +10197,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -10085,29 +10215,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -10115,727 +10245,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike Shox Ride 2 Black / Metallic Dark Grey</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11622,7 +11032,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -11641,7 +11051,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -11683,7 +11093,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -11702,7 +11112,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -11744,10 +11154,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11763,7 +11177,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -11805,14 +11219,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11828,7 +11238,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -11870,7 +11280,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -11889,7 +11299,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -11931,10 +11341,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11950,7 +11364,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -11992,12 +11406,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -12015,13 +11429,13 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P18" t="n">
         <v>50</v>
@@ -12057,12 +11471,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -12080,13 +11494,13 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
         <v>50</v>
@@ -12122,12 +11536,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -12145,13 +11559,13 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
         <v>50</v>
@@ -12187,12 +11601,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -12210,13 +11624,13 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
         <v>50</v>
@@ -12252,7 +11666,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -12275,7 +11689,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -12317,7 +11731,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -12340,7 +11754,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -12382,14 +11796,10 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -12405,7 +11815,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -12447,10 +11857,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -12466,7 +11880,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -13707,10 +13121,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -13732,7 +13150,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P45" t="n">
         <v>50</v>
@@ -16189,6 +15607,71 @@
         <v>50</v>
       </c>
       <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>12</v>
+      </c>
+      <c r="P85" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16380,7 +15863,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5"/>
@@ -16398,7 +15881,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -16526,7 +16009,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22"/>
@@ -16554,7 +16037,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1326,14 +1326,10 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1349,7 +1345,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1383,10 +1379,14 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1489,14 +1489,10 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1512,7 +1508,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1546,12 +1542,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1603,12 +1599,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -1626,7 +1622,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1660,12 +1656,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1717,12 +1713,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1774,7 +1770,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1831,7 +1827,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -1854,7 +1850,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1888,10 +1884,14 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1941,14 +1941,10 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -5978,7 +5974,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -5997,7 +5993,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -6031,7 +6027,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -6050,7 +6046,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -6084,14 +6080,10 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6107,7 +6099,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -6141,10 +6133,14 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6160,7 +6156,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -6194,7 +6190,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -6213,7 +6209,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -6247,14 +6243,10 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6270,7 +6262,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -6304,12 +6296,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -6327,7 +6319,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -6361,12 +6353,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -6384,7 +6376,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -6418,12 +6410,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -6441,7 +6433,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -6475,12 +6467,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -6498,7 +6490,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -6532,7 +6524,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -6555,7 +6547,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -6589,7 +6581,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -6612,7 +6604,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -6646,10 +6638,14 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6665,7 +6661,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -6699,14 +6695,10 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6722,7 +6714,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -10044,13 +10036,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -10117,7 +10109,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -10125,7 +10117,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-08T16:56:59Z</t>
+          <t>2026-03-08T17:51:33Z</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10139,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10155,97 +10147,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
+          <t>2026-03-08T17:51:33Z</t>
         </is>
       </c>
     </row>
@@ -11032,7 +10934,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -11051,7 +10953,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -11093,7 +10995,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -11112,7 +11014,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -11154,14 +11056,10 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11177,7 +11075,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -11219,10 +11117,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11238,7 +11140,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -11280,7 +11182,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -11299,7 +11201,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -11341,14 +11243,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11364,7 +11262,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -11406,12 +11304,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -11429,13 +11327,13 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
         <v>50</v>
@@ -11471,12 +11369,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -11494,13 +11392,13 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
         <v>50</v>
@@ -11536,12 +11434,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -11559,13 +11457,13 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
         <v>50</v>
@@ -11601,12 +11499,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -11624,13 +11522,13 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
         <v>50</v>
@@ -11666,7 +11564,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -11689,7 +11587,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -11731,7 +11629,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11754,7 +11652,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -11796,10 +11694,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11815,7 +11717,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -11857,14 +11759,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11880,7 +11778,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -983,9 +983,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr"/>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr"/>
@@ -1097,9 +1097,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr"/>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K13" s="9" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -2095,9 +2095,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -2112,10 +2112,14 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2127,11 +2131,11 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -2148,9 +2152,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2165,14 +2169,10 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -2222,18 +2222,22 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -2241,7 +2245,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -4255,7 +4259,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr"/>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr"/>
@@ -4303,12 +4307,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr"/>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr"/>
@@ -4356,12 +4360,12 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr"/>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr"/>
@@ -4392,9 +4396,9 @@
         <v>46093</v>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -4409,19 +4413,15 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr"/>
@@ -4446,12 +4446,12 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4466,27 +4466,23 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K73" s="9" t="n">
@@ -4494,7 +4490,7 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr"/>
@@ -4503,7 +4499,7 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="6" t="inlineStr">
@@ -4528,7 +4524,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr"/>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr"/>
@@ -4556,12 +4552,12 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4581,12 +4577,12 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -4604,7 +4600,7 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr"/>
@@ -4613,12 +4609,12 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4633,19 +4629,15 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr"/>
       <c r="I76" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4661,7 +4653,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr"/>
@@ -4670,7 +4662,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="6" t="inlineStr">
@@ -4690,19 +4682,15 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr"/>
       <c r="I77" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4718,7 +4706,7 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr"/>
@@ -4727,55 +4715,51 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr"/>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr"/>
@@ -4784,12 +4768,12 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4804,19 +4788,15 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4832,7 +4812,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -4841,7 +4821,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -4861,17 +4841,17 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -4889,7 +4869,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -4898,7 +4878,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="6" t="inlineStr">
@@ -4918,12 +4898,12 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr"/>
@@ -4942,7 +4922,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -4951,7 +4931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="6" t="inlineStr">
@@ -4971,15 +4951,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4995,7 +4979,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -5004,12 +4988,12 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -5024,17 +5008,17 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
@@ -5052,7 +5036,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -5061,7 +5045,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="6" t="inlineStr">
@@ -5081,15 +5065,19 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr"/>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5105,7 +5093,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -5114,51 +5102,55 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -5167,12 +5159,12 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -5187,23 +5179,27 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K86" s="9" t="n">
@@ -5211,7 +5207,7 @@
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -5220,12 +5216,12 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>46109</v>
+        <v>46097</v>
       </c>
       <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -5240,19 +5236,15 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5268,7 +5260,7 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -5277,12 +5269,12 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="B88" s="5" t="inlineStr"/>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -5302,18 +5294,22 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr"/>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K88" s="9" t="n">
@@ -5321,7 +5317,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -5330,7 +5326,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="6" t="inlineStr">
@@ -5338,9 +5334,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -5350,15 +5346,19 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr"/>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5370,11 +5370,11 @@
         </is>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -5383,12 +5383,12 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -5403,15 +5403,19 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5427,7 +5431,7 @@
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr"/>
@@ -5436,7 +5440,7 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
       <c r="C91" s="6" t="inlineStr">
@@ -5456,19 +5460,15 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr"/>
       <c r="I91" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr"/>
@@ -5493,12 +5493,12 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -5513,27 +5513,27 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K92" s="9" t="n">
@@ -5541,12 +5541,554 @@
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr"/>
       <c r="N92" s="10" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr"/>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+        </is>
+      </c>
+      <c r="M98" s="10" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
+      <c r="O98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr"/>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+        </is>
+      </c>
+      <c r="M100" s="10" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr"/>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+        </is>
+      </c>
+      <c r="M102" s="10" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5563,7 +6105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -6018,9 +6560,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -6035,7 +6577,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -6054,11 +6596,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr"/>
@@ -6087,17 +6629,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -6111,11 +6653,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr"/>
@@ -6132,9 +6674,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -6144,12 +6686,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -6168,11 +6710,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr"/>
@@ -6201,27 +6743,27 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K13" s="9" t="n">
@@ -6229,7 +6771,7 @@
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr"/>
@@ -7090,7 +7632,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -7100,12 +7642,12 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
@@ -7113,7 +7655,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -7130,9 +7672,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -7147,10 +7689,14 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7162,11 +7708,11 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -7183,9 +7729,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -7200,14 +7746,10 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7219,11 +7761,11 @@
         </is>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -7257,18 +7799,22 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -7276,7 +7822,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -9290,7 +9836,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr"/>
@@ -9309,7 +9855,7 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr"/>
@@ -9338,12 +9884,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr"/>
@@ -9362,7 +9908,7 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr"/>
@@ -9391,12 +9937,12 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr"/>
@@ -9415,7 +9961,7 @@
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr"/>
@@ -9427,9 +9973,9 @@
         <v>46093</v>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -9444,19 +9990,15 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9472,7 +10014,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr"/>
@@ -9481,12 +10023,12 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -9501,27 +10043,23 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K73" s="9" t="n">
@@ -9529,7 +10067,7 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr"/>
@@ -9538,7 +10076,7 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="6" t="inlineStr">
@@ -9563,7 +10101,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr"/>
@@ -9582,7 +10120,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr"/>
@@ -9591,12 +10129,12 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -9616,12 +10154,12 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -9639,7 +10177,7 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr"/>
@@ -9648,12 +10186,12 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -9668,19 +10206,15 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr"/>
       <c r="I76" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9696,7 +10230,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr"/>
@@ -9705,7 +10239,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="6" t="inlineStr">
@@ -9725,19 +10259,15 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr"/>
       <c r="I77" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9753,7 +10283,7 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr"/>
@@ -9762,55 +10292,51 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr"/>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr"/>
@@ -9819,12 +10345,12 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -9839,19 +10365,15 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9867,7 +10389,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -9876,7 +10398,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -9896,17 +10418,17 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -9924,7 +10446,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -9933,7 +10455,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="6" t="inlineStr">
@@ -9953,12 +10475,12 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr"/>
@@ -9977,7 +10499,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -9986,7 +10508,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="6" t="inlineStr">
@@ -10006,15 +10528,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10030,7 +10556,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -10039,12 +10565,12 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -10059,17 +10585,17 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
@@ -10087,7 +10613,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -10096,7 +10622,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="6" t="inlineStr">
@@ -10116,15 +10642,19 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr"/>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10140,7 +10670,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -10149,51 +10679,55 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -10202,12 +10736,12 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -10222,23 +10756,27 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K86" s="9" t="n">
@@ -10246,7 +10784,7 @@
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -10255,12 +10793,12 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>46109</v>
+        <v>46097</v>
       </c>
       <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -10275,19 +10813,15 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10303,7 +10837,7 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -10312,12 +10846,12 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="B88" s="5" t="inlineStr"/>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -10337,18 +10871,22 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr"/>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K88" s="9" t="n">
@@ -10356,7 +10894,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -10365,7 +10903,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="6" t="inlineStr">
@@ -10373,9 +10911,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -10385,15 +10923,19 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr"/>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10405,11 +10947,11 @@
         </is>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -10418,12 +10960,12 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -10438,15 +10980,19 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10462,7 +11008,7 @@
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr"/>
@@ -10471,7 +11017,7 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
       <c r="C91" s="6" t="inlineStr">
@@ -10491,19 +11037,15 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr"/>
       <c r="I91" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10519,7 +11061,7 @@
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr"/>
@@ -10528,12 +11070,12 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -10548,27 +11090,27 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K92" s="9" t="n">
@@ -10576,12 +11118,554 @@
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr"/>
       <c r="N92" s="10" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr"/>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+        </is>
+      </c>
+      <c r="M98" s="10" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
+      <c r="O98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr"/>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+        </is>
+      </c>
+      <c r="M100" s="10" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr"/>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+        </is>
+      </c>
+      <c r="M102" s="10" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10598,13 +11682,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -10656,22 +11740,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'Black' From £ 182</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -10679,29 +11763,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'Nacre'</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10709,7 +11793,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10721,17 +11805,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'White' From £ 182</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -10739,7 +11823,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10751,17 +11835,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike SB Ishod Apparel Collection</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -10769,29 +11853,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -10799,29 +11883,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -10829,29 +11913,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -10859,19 +11943,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10881,7 +11965,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Soft Pearl / Sail</t>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -10889,19 +11973,19 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10911,7 +11995,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -10919,19 +12003,19 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10941,7 +12025,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -10949,7 +12033,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10961,7 +12045,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10971,7 +12055,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -10979,7 +12063,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10991,17 +12075,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -11009,7 +12093,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -11021,17 +12105,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -11039,7 +12123,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -11051,17 +12135,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -11069,7 +12153,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -11081,7 +12165,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11091,7 +12175,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -11099,7 +12183,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -11111,17 +12195,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -11129,7 +12213,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -11141,17 +12225,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -11159,29 +12243,29 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -11189,29 +12273,29 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -11219,29 +12303,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -11249,1597 +12333,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Nike Grade School LeBron XXIII BOYS GRADE SCHOOL • SILT RED/METALLIC COPPER/BLACK</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -13359,7 +12853,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -13374,7 +12868,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -13393,11 +12887,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -13406,7 +12900,7 @@
         <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -13434,17 +12928,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -13458,17 +12952,17 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
         <v>70</v>
@@ -13489,7 +12983,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13499,12 +12993,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13523,11 +13017,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -13536,7 +13030,7 @@
         <v>14</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -13564,27 +13058,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -13592,13 +13086,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
         <v>50</v>
@@ -14581,7 +14075,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -14591,12 +14085,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -14604,7 +14098,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -14631,7 +14125,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -14646,10 +14140,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -14661,11 +14159,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -14674,7 +14172,7 @@
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -14692,7 +14190,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14707,14 +14205,10 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -14726,11 +14220,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -14739,7 +14233,7 @@
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -14772,18 +14266,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -14791,7 +14289,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -17101,7 +16599,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -17120,7 +16618,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -17157,12 +16655,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -17181,7 +16679,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -17218,12 +16716,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -17242,13 +16740,13 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P69" t="n">
         <v>50</v>
@@ -17264,7 +16762,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -17279,19 +16777,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17307,13 +16801,13 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P70" t="n">
         <v>50</v>
@@ -17322,14 +16816,14 @@
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -17344,27 +16838,23 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -17372,13 +16862,13 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P71" t="n">
         <v>50</v>
@@ -17387,7 +16877,7 @@
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -17414,7 +16904,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -17433,7 +16923,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -17448,14 +16938,14 @@
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -17475,12 +16965,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17498,13 +16988,13 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P73" t="n">
         <v>50</v>
@@ -17513,14 +17003,14 @@
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -17535,19 +17025,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17563,13 +17049,13 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
         <v>50</v>
@@ -17578,7 +17064,7 @@
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -17600,19 +17086,15 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17628,7 +17110,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -17643,79 +17125,75 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -17730,19 +17208,15 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17758,13 +17232,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
         <v>50</v>
@@ -17773,7 +17247,7 @@
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -17795,17 +17269,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17823,7 +17297,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -17838,7 +17312,7 @@
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -17860,12 +17334,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -17884,13 +17358,13 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P79" t="n">
         <v>50</v>
@@ -17899,7 +17373,7 @@
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -17921,15 +17395,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17945,13 +17423,13 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>50</v>
@@ -17960,14 +17438,14 @@
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -17982,17 +17460,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -18010,13 +17488,13 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P81" t="n">
         <v>50</v>
@@ -18025,7 +17503,7 @@
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -18047,15 +17525,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18071,13 +17553,13 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
         <v>50</v>
@@ -18086,75 +17568,79 @@
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P83" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -18169,23 +17655,27 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -18193,13 +17683,13 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="P84" t="n">
         <v>50</v>
@@ -18208,14 +17698,14 @@
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
-        <v>46109</v>
+        <v>46097</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -18230,19 +17720,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18258,13 +17744,13 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
         <v>50</v>
@@ -18273,14 +17759,14 @@
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -18300,18 +17786,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -18319,13 +17809,13 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P86" t="n">
         <v>50</v>
@@ -18334,7 +17824,7 @@
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -18346,7 +17836,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -18356,15 +17846,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18376,33 +17870,33 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P87" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -18417,15 +17911,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18441,13 +17939,13 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P88" t="n">
         <v>50</v>
@@ -18456,7 +17954,7 @@
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -18478,19 +17976,15 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18506,13 +18000,13 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
         <v>50</v>
@@ -18521,14 +18015,14 @@
     </row>
     <row r="90">
       <c r="A90" s="14" t="n">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18543,27 +18037,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -18571,18 +18065,640 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P90" t="n">
         <v>50</v>
       </c>
       <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>22</v>
+      </c>
+      <c r="P91" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>12</v>
+      </c>
+      <c r="P94" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>4</v>
+      </c>
+      <c r="P95" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>12</v>
+      </c>
+      <c r="P97" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>12</v>
+      </c>
+      <c r="P98" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>12</v>
+      </c>
+      <c r="P99" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>12</v>
+      </c>
+      <c r="P100" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18764,7 +18880,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -18774,7 +18890,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5"/>
@@ -18792,7 +18908,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -18812,7 +18928,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -18822,23 +18938,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -18848,21 +18964,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -18910,7 +19026,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -18920,7 +19036,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22"/>
@@ -18948,7 +19064,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P45"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -715,7 +715,9 @@
       <c r="A4" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -732,7 +734,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -769,7 +771,9 @@
       <c r="A5" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
@@ -786,7 +790,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -823,7 +827,9 @@
       <c r="A6" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
@@ -840,7 +846,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -881,7 +887,9 @@
       <c r="A7" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="13" t="inlineStr">
@@ -898,7 +906,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -939,7 +947,9 @@
       <c r="A8" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
@@ -956,7 +966,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -997,7 +1007,9 @@
       <c r="A9" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
@@ -1008,13 +1020,13 @@
       <c r="F9" s="8" t="n">
         <v>16</v>
       </c>
-      <c r="G9" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>50</v>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>83</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1028,7 +1040,7 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
@@ -1042,11 +1054,11 @@
         </is>
       </c>
       <c r="N9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="P9" s="12" t="inlineStr"/>
@@ -1055,16 +1067,18 @@
       <c r="A10" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>24</v>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1072,7 +1086,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1086,17 +1100,17 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="N10" s="6" t="n">
@@ -1104,7 +1118,7 @@
       </c>
       <c r="O10" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="P10" s="12" t="inlineStr"/>
@@ -1116,13 +1130,13 @@
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>12</v>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1144,10 +1158,14 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr"/>
+          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1158,7 +1176,7 @@
       </c>
       <c r="O11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="P11" s="12" t="inlineStr"/>
@@ -1170,13 +1188,13 @@
       <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>28</v>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1198,14 +1216,10 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1216,7 +1230,7 @@
       </c>
       <c r="O12" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P12" s="12" t="inlineStr"/>
@@ -1228,13 +1242,13 @@
       <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>12</v>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1256,10 +1270,14 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -1270,7 +1288,7 @@
       </c>
       <c r="O13" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="P13" s="12" t="inlineStr"/>
@@ -1310,7 +1328,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr"/>
@@ -1342,7 +1360,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1359,22 +1377,18 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="N15" s="6" t="n">
@@ -1382,7 +1396,7 @@
       </c>
       <c r="O15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P15" s="12" t="inlineStr"/>
@@ -1391,7 +1405,9 @@
       <c r="A16" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
@@ -1408,7 +1424,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1422,10 +1438,14 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1436,7 +1456,7 @@
       </c>
       <c r="O16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="P16" s="12" t="inlineStr"/>
@@ -1445,7 +1465,9 @@
       <c r="A17" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
@@ -1462,7 +1484,7 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -1471,19 +1493,15 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1494,7 +1512,7 @@
       </c>
       <c r="O17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="P17" s="12" t="inlineStr"/>
@@ -1503,7 +1521,9 @@
       <c r="A18" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
@@ -1512,7 +1532,7 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1520,7 +1540,7 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1529,15 +1549,19 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr"/>
+          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1548,7 +1572,7 @@
       </c>
       <c r="O18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr"/>
@@ -1557,16 +1581,18 @@
       <c r="A19" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F19" s="14" t="n">
-        <v>24</v>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1574,7 +1600,7 @@
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
@@ -1588,14 +1614,10 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1606,7 +1628,7 @@
       </c>
       <c r="O19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="P19" s="12" t="inlineStr"/>
@@ -1615,16 +1637,18 @@
       <c r="A20" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>12</v>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1632,7 +1656,7 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1646,12 +1670,12 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M20" s="6" t="inlineStr">
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="P20" s="12" t="inlineStr"/>
@@ -1673,16 +1697,18 @@
       <c r="A21" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F21" s="14" t="n">
-        <v>22</v>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1690,7 +1716,7 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
@@ -1704,12 +1730,12 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
@@ -1722,7 +1748,7 @@
       </c>
       <c r="O21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="P21" s="12" t="inlineStr"/>
@@ -1731,16 +1757,18 @@
       <c r="A22" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>12</v>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1748,7 +1776,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1762,10 +1790,14 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1776,7 +1808,7 @@
       </c>
       <c r="O22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="P22" s="12" t="inlineStr"/>
@@ -1785,7 +1817,9 @@
       <c r="A23" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
@@ -1802,7 +1836,7 @@
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
@@ -1816,7 +1850,7 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="L23" s="12" t="inlineStr"/>
@@ -1830,7 +1864,7 @@
       </c>
       <c r="O23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="P23" s="12" t="inlineStr"/>
@@ -1839,7 +1873,9 @@
       <c r="A24" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
@@ -1856,7 +1892,7 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -1870,7 +1906,7 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="L24" s="12" t="inlineStr"/>
@@ -1884,7 +1920,7 @@
       </c>
       <c r="O24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="P24" s="12" t="inlineStr"/>
@@ -1893,7 +1929,9 @@
       <c r="A25" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
@@ -1910,7 +1948,7 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
@@ -1924,14 +1962,10 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1942,7 +1976,7 @@
       </c>
       <c r="O25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="P25" s="12" t="inlineStr"/>
@@ -1951,7 +1985,9 @@
       <c r="A26" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
@@ -1968,7 +2004,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -1982,12 +2018,12 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr">
@@ -2000,7 +2036,7 @@
       </c>
       <c r="O26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="P26" s="12" t="inlineStr"/>
@@ -2009,16 +2045,18 @@
       <c r="A27" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>24</v>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2026,7 +2064,7 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
@@ -2040,12 +2078,12 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr">
@@ -2058,7 +2096,7 @@
       </c>
       <c r="O27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="P27" s="12" t="inlineStr"/>
@@ -2067,7 +2105,9 @@
       <c r="A28" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr">
@@ -2084,7 +2124,7 @@
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2098,7 +2138,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2116,7 +2156,7 @@
       </c>
       <c r="O28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="P28" s="12" t="inlineStr"/>
@@ -2125,7 +2165,9 @@
       <c r="A29" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
@@ -2142,7 +2184,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2156,7 +2198,7 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -2174,7 +2216,7 @@
       </c>
       <c r="O29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="P29" s="12" t="inlineStr"/>
@@ -2183,7 +2225,9 @@
       <c r="A30" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="13" t="inlineStr">
@@ -2200,7 +2244,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2214,12 +2258,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr">
@@ -2232,7 +2276,7 @@
       </c>
       <c r="O30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="P30" s="12" t="inlineStr"/>
@@ -2241,16 +2285,18 @@
       <c r="A31" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>12</v>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2258,7 +2304,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2272,12 +2318,12 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr">
@@ -2290,7 +2336,7 @@
       </c>
       <c r="O31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="P31" s="12" t="inlineStr"/>
@@ -2299,7 +2345,9 @@
       <c r="A32" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
@@ -2308,7 +2356,7 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2316,7 +2364,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2325,12 +2373,12 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -2348,7 +2396,7 @@
       </c>
       <c r="O32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="P32" s="12" t="inlineStr"/>
@@ -2357,7 +2405,9 @@
       <c r="A33" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
@@ -2374,7 +2424,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2388,10 +2438,14 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2402,7 +2456,7 @@
       </c>
       <c r="O33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="P33" s="12" t="inlineStr"/>
@@ -2411,7 +2465,9 @@
       <c r="A34" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
@@ -2428,7 +2484,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2442,14 +2498,10 @@
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2460,7 +2512,7 @@
       </c>
       <c r="O34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="P34" s="12" t="inlineStr"/>
@@ -2469,7 +2521,9 @@
       <c r="A35" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
@@ -2478,7 +2532,7 @@
         </is>
       </c>
       <c r="F35" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2495,15 +2549,19 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L35" s="12" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L35" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2514,7 +2572,7 @@
       </c>
       <c r="O35" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="P35" s="12" t="inlineStr"/>
@@ -2532,7 +2590,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2540,7 +2598,7 @@
         </is>
       </c>
       <c r="H36" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I36" s="11" t="inlineStr">
         <is>
@@ -2549,19 +2607,15 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2572,25 +2626,27 @@
       </c>
       <c r="O36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="P36" s="12" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B37" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F37" s="14" t="n">
-        <v>28</v>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2598,7 +2654,7 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
@@ -2607,22 +2663,22 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle, exclusive</t>
         </is>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="N37" s="6" t="n">
@@ -2630,7 +2686,7 @@
       </c>
       <c r="O37" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="P37" s="12" t="inlineStr"/>
@@ -2650,17 +2706,17 @@
       <c r="F38" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H38" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="I38" s="17" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I38" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -2670,7 +2726,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
@@ -2684,11 +2740,11 @@
         </is>
       </c>
       <c r="N38" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="P38" s="12" t="inlineStr"/>
@@ -2700,25 +2756,25 @@
       <c r="B39" s="5" t="inlineStr"/>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F39" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G39" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I39" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G39" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="I39" s="17" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
@@ -2728,21 +2784,25 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr"/>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="N39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="P39" s="12" t="inlineStr"/>
@@ -2754,13 +2814,13 @@
       <c r="B40" s="5" t="inlineStr"/>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F40" s="14" t="n">
-        <v>24</v>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F40" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -2777,19 +2837,15 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="L40" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="L40" s="12" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -2800,25 +2856,25 @@
       </c>
       <c r="O40" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="P40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="B41" s="5" t="inlineStr"/>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="n">
-        <v>7</v>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F41" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -2835,17 +2891,17 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M41" s="6" t="inlineStr">
@@ -2858,14 +2914,14 @@
       </c>
       <c r="O41" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="P41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B42" s="5" t="inlineStr"/>
       <c r="C42" s="5" t="inlineStr"/>
@@ -2876,7 +2932,7 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -2893,22 +2949,22 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="N42" s="6" t="n">
@@ -2916,7 +2972,7 @@
       </c>
       <c r="O42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="P42" s="12" t="inlineStr"/>
@@ -2925,7 +2981,9 @@
       <c r="A43" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B43" s="5" t="inlineStr"/>
+      <c r="B43" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
@@ -2934,7 +2992,7 @@
         </is>
       </c>
       <c r="F43" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -2942,7 +3000,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -2951,15 +3009,19 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2970,7 +3032,7 @@
       </c>
       <c r="O43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="P43" s="12" t="inlineStr"/>
@@ -2979,7 +3041,9 @@
       <c r="A44" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B44" s="5" t="inlineStr"/>
+      <c r="B44" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
@@ -2988,7 +3052,7 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -2996,7 +3060,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3005,19 +3069,15 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3028,7 +3088,7 @@
       </c>
       <c r="O44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="P44" s="12" t="inlineStr"/>
@@ -3037,7 +3097,9 @@
       <c r="A45" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
@@ -3054,7 +3116,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3068,28 +3130,88 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="P45" s="12" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C46" s="5" t="inlineStr"/>
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
+        <is>
           <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
-      <c r="L45" s="12" t="inlineStr">
+      <c r="L46" s="12" t="inlineStr">
         <is>
           <t>women</t>
         </is>
       </c>
-      <c r="M45" s="6" t="inlineStr">
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" s="12" t="inlineStr">
+      <c r="N46" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="P45" s="12" t="inlineStr"/>
+      <c r="P46" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3106,17 +3228,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3158,6 +3280,1338 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:32:01Z</t>
         </is>
       </c>
     </row>
@@ -3172,7 +4626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3286,7 +4740,7 @@
         <v>46095</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -3338,7 +4792,7 @@
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -3347,7 +4801,7 @@
         <v>46095</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -3399,7 +4853,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -3408,7 +4862,7 @@
         <v>46095</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -3464,7 +4918,7 @@
         <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -3473,7 +4927,7 @@
         <v>46095</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -3529,7 +4983,7 @@
         <v>38</v>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -3538,7 +4992,7 @@
         <v>46095</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3594,7 +5048,7 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -3603,7 +5057,7 @@
         <v>46095</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -3612,7 +5066,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3627,7 +5081,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3646,11 +5100,11 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
@@ -3659,7 +5113,7 @@
         <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="Q7" t="inlineStr"/>
     </row>
@@ -3668,11 +5122,11 @@
         <v>46095</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3692,22 +5146,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -3715,16 +5169,16 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -3737,7 +5191,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3757,10 +5211,14 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -3776,13 +5234,13 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P9" t="n">
         <v>50</v>
@@ -3798,7 +5256,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3818,14 +5276,10 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
+          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -3841,13 +5295,13 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="P10" t="n">
         <v>50</v>
@@ -3863,7 +5317,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3883,10 +5337,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -3902,13 +5360,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P11" t="n">
         <v>50</v>
@@ -3944,7 +5402,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -4000,27 +5458,23 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -4028,13 +5482,13 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P13" t="n">
         <v>50</v>
@@ -4046,7 +5500,7 @@
         <v>46095</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -4070,10 +5524,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4089,7 +5547,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -4098,7 +5556,7 @@
         <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -4107,7 +5565,7 @@
         <v>46095</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -4126,19 +5584,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4154,7 +5608,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -4163,7 +5617,7 @@
         <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -4172,7 +5626,7 @@
         <v>46095</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -4191,15 +5645,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4215,16 +5673,16 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -4233,11 +5691,11 @@
         <v>46095</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4257,14 +5715,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4280,16 +5734,16 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -4298,11 +5752,11 @@
         <v>46095</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4322,12 +5776,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -4345,16 +5799,16 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -4363,11 +5817,11 @@
         <v>46095</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4387,12 +5841,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -4410,16 +5864,16 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
@@ -4428,11 +5882,11 @@
         <v>46095</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4452,10 +5906,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4471,16 +5929,16 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -4489,7 +5947,7 @@
         <v>46095</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -4513,7 +5971,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -4532,7 +5990,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
@@ -4541,7 +5999,7 @@
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -4550,7 +6008,7 @@
         <v>46095</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -4574,7 +6032,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -4593,7 +6051,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -4602,7 +6060,7 @@
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -4611,7 +6069,7 @@
         <v>46095</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -4635,14 +6093,10 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4658,7 +6112,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -4667,7 +6121,7 @@
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -4676,7 +6130,7 @@
         <v>46095</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -4700,12 +6154,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -4723,7 +6177,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -4732,7 +6186,7 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -4741,11 +6195,11 @@
         <v>46095</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4765,12 +6219,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -4788,16 +6242,16 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -4806,7 +6260,7 @@
         <v>46095</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -4830,7 +6284,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4853,7 +6307,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="M26" t="inlineStr"/>
@@ -4862,7 +6316,7 @@
         <v>24</v>
       </c>
       <c r="P26" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -4871,7 +6325,7 @@
         <v>46095</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -4895,7 +6349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4918,7 +6372,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -4927,7 +6381,7 @@
         <v>24</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -4936,7 +6390,7 @@
         <v>46095</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -4960,12 +6414,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4983,7 +6437,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -4992,7 +6446,7 @@
         <v>24</v>
       </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -5001,11 +6455,11 @@
         <v>46095</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5025,12 +6479,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -5048,16 +6502,16 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -5066,7 +6520,7 @@
         <v>46095</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -5085,12 +6539,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5113,16 +6567,16 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -5131,7 +6585,7 @@
         <v>46095</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -5155,10 +6609,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5174,7 +6632,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="M31" t="inlineStr"/>
@@ -5183,7 +6641,7 @@
         <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -5192,7 +6650,7 @@
         <v>46095</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -5216,14 +6674,10 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5239,7 +6693,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="M32" t="inlineStr"/>
@@ -5248,7 +6702,7 @@
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -5257,7 +6711,7 @@
         <v>46095</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -5276,15 +6730,19 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5300,17 +6758,13 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>https://images.footlocker.com/content/dam/final/footlocker/site/homepage/2026/february/260225-fl-flca-recrne5wvpiszp57g-top-nav-image-update/260225-fl-flca-recRNe5WvpISZp57G-top-nav-image-update-mens-basketball.jpg</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P33" t="n">
         <v>59</v>
@@ -5341,19 +6795,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5369,29 +6819,33 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>https://images.footlocker.com/content/dam/final/footlocker/site/homepage/2026/february/260225-fl-flca-recrne5wvpiszp57g-top-nav-image-update/260225-fl-flca-recRNe5WvpISZp57G-top-nav-image-update-mens-basketball.jpg</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5406,27 +6860,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle, exclusive</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -5434,16 +6888,16 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="P35" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -5461,12 +6915,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5476,7 +6930,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5495,11 +6949,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M36" t="inlineStr"/>
@@ -5508,7 +6962,7 @@
         <v>28</v>
       </c>
       <c r="P36" t="n">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="Q36" t="inlineStr"/>
     </row>
@@ -5521,17 +6975,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5541,10 +6995,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -5556,20 +7014,20 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="P37" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="Q37" t="inlineStr"/>
     </row>
@@ -5582,7 +7040,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5597,19 +7055,15 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -5625,13 +7079,13 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="P38" t="n">
         <v>50</v>
@@ -5640,14 +7094,14 @@
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
-        <v>46098</v>
+        <v>46096</v>
       </c>
       <c r="B39" t="n">
         <v>0</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5662,17 +7116,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -5682,7 +7136,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -5690,13 +7144,13 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P39" t="n">
         <v>50</v>
@@ -5705,7 +7159,7 @@
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B40" t="n">
         <v>0</v>
@@ -5727,27 +7181,27 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -5755,13 +7209,13 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="P40" t="n">
         <v>50</v>
@@ -5773,7 +7227,7 @@
         <v>46113</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5792,15 +7246,19 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5816,16 +7274,16 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
@@ -5834,7 +7292,7 @@
         <v>46113</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5853,19 +7311,15 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5881,16 +7335,16 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -5899,7 +7353,7 @@
         <v>46113</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5923,7 +7377,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -5946,7 +7400,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="M43" t="inlineStr"/>
@@ -5955,9 +7409,74 @@
         <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B44" t="n">
+        <v>130</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="n">
+        <v>7</v>
+      </c>
+      <c r="P44" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6146,7 +7665,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4"/>
@@ -6175,7 +7694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -6283,7 +7802,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21"/>
@@ -6301,7 +7820,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -715,7 +715,9 @@
       <c r="A4" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B4" s="5" t="inlineStr"/>
+      <c r="B4" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -732,7 +734,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -769,7 +771,9 @@
       <c r="A5" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B5" s="5" t="inlineStr"/>
+      <c r="B5" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
@@ -786,7 +790,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -823,7 +827,9 @@
       <c r="A6" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B6" s="5" t="inlineStr"/>
+      <c r="B6" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
@@ -840,7 +846,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -881,7 +887,9 @@
       <c r="A7" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="13" t="inlineStr">
@@ -898,7 +906,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -939,7 +947,9 @@
       <c r="A8" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
@@ -956,7 +966,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1057,7 +1067,9 @@
       <c r="A10" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B10" s="5" t="inlineStr"/>
+      <c r="B10" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
@@ -1074,7 +1086,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1393,7 +1405,9 @@
       <c r="A16" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B16" s="5" t="inlineStr"/>
+      <c r="B16" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="7" t="inlineStr">
@@ -1410,7 +1424,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1451,7 +1465,9 @@
       <c r="A17" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="B17" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
@@ -1468,7 +1484,7 @@
         </is>
       </c>
       <c r="H17" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
@@ -1505,7 +1521,9 @@
       <c r="A18" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B18" s="5" t="inlineStr"/>
+      <c r="B18" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
@@ -1522,7 +1540,7 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
@@ -1563,7 +1581,9 @@
       <c r="A19" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
@@ -1580,7 +1600,7 @@
         </is>
       </c>
       <c r="H19" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
@@ -1617,7 +1637,9 @@
       <c r="A20" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B20" s="5" t="inlineStr"/>
+      <c r="B20" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="13" t="inlineStr">
@@ -1634,7 +1656,7 @@
         </is>
       </c>
       <c r="H20" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
@@ -1675,7 +1697,9 @@
       <c r="A21" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
@@ -1692,7 +1716,7 @@
         </is>
       </c>
       <c r="H21" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
@@ -1733,7 +1757,9 @@
       <c r="A22" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="13" t="inlineStr">
@@ -1750,7 +1776,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
@@ -1791,7 +1817,9 @@
       <c r="A23" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="7" t="inlineStr">
@@ -1808,7 +1836,7 @@
         </is>
       </c>
       <c r="H23" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
@@ -1845,7 +1873,9 @@
       <c r="A24" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="7" t="inlineStr">
@@ -1862,7 +1892,7 @@
         </is>
       </c>
       <c r="H24" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
@@ -1899,7 +1929,9 @@
       <c r="A25" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="7" t="inlineStr">
@@ -1916,7 +1948,7 @@
         </is>
       </c>
       <c r="H25" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
@@ -1953,7 +1985,9 @@
       <c r="A26" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B26" s="5" t="inlineStr"/>
+      <c r="B26" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="7" t="inlineStr">
@@ -1970,7 +2004,7 @@
         </is>
       </c>
       <c r="H26" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
@@ -2011,7 +2045,9 @@
       <c r="A27" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B27" s="5" t="inlineStr"/>
+      <c r="B27" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
       <c r="E27" s="7" t="inlineStr">
@@ -2028,7 +2064,7 @@
         </is>
       </c>
       <c r="H27" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
@@ -2069,7 +2105,9 @@
       <c r="A28" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B28" s="5" t="inlineStr"/>
+      <c r="B28" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="13" t="inlineStr">
@@ -2086,7 +2124,7 @@
         </is>
       </c>
       <c r="H28" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
@@ -2127,7 +2165,9 @@
       <c r="A29" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="13" t="inlineStr">
@@ -2144,7 +2184,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2185,7 +2225,9 @@
       <c r="A30" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B30" s="5" t="inlineStr"/>
+      <c r="B30" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="13" t="inlineStr">
@@ -2202,7 +2244,7 @@
         </is>
       </c>
       <c r="H30" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
@@ -2243,7 +2285,9 @@
       <c r="A31" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B31" s="5" t="inlineStr"/>
+      <c r="B31" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="13" t="inlineStr">
@@ -2260,7 +2304,7 @@
         </is>
       </c>
       <c r="H31" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
@@ -2301,7 +2345,9 @@
       <c r="A32" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
@@ -2318,7 +2364,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2359,7 +2405,9 @@
       <c r="A33" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="7" t="inlineStr">
@@ -2376,7 +2424,7 @@
         </is>
       </c>
       <c r="H33" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
@@ -2417,7 +2465,9 @@
       <c r="A34" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
@@ -2434,7 +2484,7 @@
         </is>
       </c>
       <c r="H34" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
@@ -2471,7 +2521,9 @@
       <c r="A35" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="7" t="inlineStr">
@@ -2488,7 +2540,7 @@
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I35" s="11" t="inlineStr">
         <is>
@@ -2529,7 +2581,9 @@
       <c r="A36" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="7" t="inlineStr">
@@ -2583,7 +2637,9 @@
       <c r="A37" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B37" s="5" t="inlineStr"/>
+      <c r="B37" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="7" t="inlineStr">
@@ -2600,7 +2656,7 @@
         </is>
       </c>
       <c r="H37" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
@@ -2927,7 +2983,9 @@
       <c r="A43" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B43" s="5" t="inlineStr"/>
+      <c r="B43" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="7" t="inlineStr">
@@ -2944,7 +3002,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -2985,7 +3043,9 @@
       <c r="A44" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B44" s="5" t="inlineStr"/>
+      <c r="B44" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="7" t="inlineStr">
@@ -3002,7 +3062,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3039,7 +3099,9 @@
       <c r="A45" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
       <c r="E45" s="7" t="inlineStr">
@@ -3056,7 +3118,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3097,7 +3159,9 @@
       <c r="A46" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B46" s="5" t="inlineStr"/>
+      <c r="B46" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
@@ -3114,7 +3178,7 @@
         </is>
       </c>
       <c r="H46" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
@@ -3166,7 +3230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3249,17 +3313,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3291,17 +3355,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3333,17 +3397,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3375,17 +3439,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3417,17 +3481,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3459,17 +3523,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3501,17 +3565,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3543,17 +3607,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3585,17 +3649,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3627,17 +3691,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3733,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3711,17 +3775,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3753,17 +3817,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3795,17 +3859,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3837,17 +3901,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3879,17 +3943,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3921,17 +3985,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -3963,17 +4027,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4005,17 +4069,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4047,17 +4111,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4089,17 +4153,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4131,17 +4195,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4173,17 +4237,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4215,17 +4279,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4257,17 +4321,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4299,17 +4363,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4341,17 +4405,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4363,17 +4427,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4383,17 +4447,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>215</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4410,12 +4474,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4425,17 +4489,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4516,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4467,17 +4531,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
           <t>130</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-14T05:36:08Z</t>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4499,27 +4563,69 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>retailPrice</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:50:10Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>RETAIL_CHANGED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>retailPrice</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:36:08Z</t>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4754,7 @@
         <v>46095</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -4700,7 +4806,7 @@
         <v>12</v>
       </c>
       <c r="P2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q2" t="inlineStr"/>
     </row>
@@ -4709,7 +4815,7 @@
         <v>46095</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -4761,7 +4867,7 @@
         <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q3" t="inlineStr"/>
     </row>
@@ -4770,7 +4876,7 @@
         <v>46095</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -4826,7 +4932,7 @@
         <v>16</v>
       </c>
       <c r="P4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q4" t="inlineStr"/>
     </row>
@@ -4835,7 +4941,7 @@
         <v>46095</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -4891,7 +4997,7 @@
         <v>38</v>
       </c>
       <c r="P5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q5" t="inlineStr"/>
     </row>
@@ -4900,7 +5006,7 @@
         <v>46095</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -4956,7 +5062,7 @@
         <v>16</v>
       </c>
       <c r="P6" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q6" t="inlineStr"/>
     </row>
@@ -5030,7 +5136,7 @@
         <v>46095</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -5086,7 +5192,7 @@
         <v>16</v>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -5408,7 +5514,7 @@
         <v>46095</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -5464,7 +5570,7 @@
         <v>7</v>
       </c>
       <c r="P14" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q14" t="inlineStr"/>
     </row>
@@ -5473,7 +5579,7 @@
         <v>46095</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -5525,7 +5631,7 @@
         <v>7</v>
       </c>
       <c r="P15" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q15" t="inlineStr"/>
     </row>
@@ -5534,7 +5640,7 @@
         <v>46095</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -5590,7 +5696,7 @@
         <v>7</v>
       </c>
       <c r="P16" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q16" t="inlineStr"/>
     </row>
@@ -5599,7 +5705,7 @@
         <v>46095</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -5651,7 +5757,7 @@
         <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q17" t="inlineStr"/>
     </row>
@@ -5660,7 +5766,7 @@
         <v>46095</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -5716,7 +5822,7 @@
         <v>24</v>
       </c>
       <c r="P18" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q18" t="inlineStr"/>
     </row>
@@ -5725,7 +5831,7 @@
         <v>46095</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -5781,7 +5887,7 @@
         <v>12</v>
       </c>
       <c r="P19" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q19" t="inlineStr"/>
     </row>
@@ -5790,7 +5896,7 @@
         <v>46095</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5846,7 +5952,7 @@
         <v>22</v>
       </c>
       <c r="P20" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q20" t="inlineStr"/>
     </row>
@@ -5855,7 +5961,7 @@
         <v>46095</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -5907,7 +6013,7 @@
         <v>12</v>
       </c>
       <c r="P21" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q21" t="inlineStr"/>
     </row>
@@ -5916,7 +6022,7 @@
         <v>46095</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5968,7 +6074,7 @@
         <v>12</v>
       </c>
       <c r="P22" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q22" t="inlineStr"/>
     </row>
@@ -5977,7 +6083,7 @@
         <v>46095</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -6029,7 +6135,7 @@
         <v>12</v>
       </c>
       <c r="P23" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q23" t="inlineStr"/>
     </row>
@@ -6038,7 +6144,7 @@
         <v>46095</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -6094,7 +6200,7 @@
         <v>12</v>
       </c>
       <c r="P24" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q24" t="inlineStr"/>
     </row>
@@ -6103,7 +6209,7 @@
         <v>46095</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -6159,7 +6265,7 @@
         <v>12</v>
       </c>
       <c r="P25" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q25" t="inlineStr"/>
     </row>
@@ -6168,7 +6274,7 @@
         <v>46095</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6224,7 +6330,7 @@
         <v>24</v>
       </c>
       <c r="P26" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q26" t="inlineStr"/>
     </row>
@@ -6233,7 +6339,7 @@
         <v>46095</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -6289,7 +6395,7 @@
         <v>24</v>
       </c>
       <c r="P27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q27" t="inlineStr"/>
     </row>
@@ -6298,7 +6404,7 @@
         <v>46095</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -6354,7 +6460,7 @@
         <v>24</v>
       </c>
       <c r="P28" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -6363,7 +6469,7 @@
         <v>46095</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -6419,7 +6525,7 @@
         <v>24</v>
       </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -6428,7 +6534,7 @@
         <v>46095</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6484,7 +6590,7 @@
         <v>12</v>
       </c>
       <c r="P30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q30" t="inlineStr"/>
     </row>
@@ -6493,7 +6599,7 @@
         <v>46095</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6549,7 +6655,7 @@
         <v>7</v>
       </c>
       <c r="P31" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q31" t="inlineStr"/>
     </row>
@@ -6558,7 +6664,7 @@
         <v>46095</v>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6610,7 +6716,7 @@
         <v>7</v>
       </c>
       <c r="P32" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q32" t="inlineStr"/>
     </row>
@@ -6619,7 +6725,7 @@
         <v>46095</v>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6675,7 +6781,7 @@
         <v>7</v>
       </c>
       <c r="P33" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q33" t="inlineStr"/>
     </row>
@@ -6684,7 +6790,7 @@
         <v>46095</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6749,7 +6855,7 @@
         <v>46095</v>
       </c>
       <c r="B35" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6805,7 +6911,7 @@
         <v>17</v>
       </c>
       <c r="P35" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q35" t="inlineStr"/>
     </row>
@@ -7135,7 +7241,7 @@
         <v>46113</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -7191,7 +7297,7 @@
         <v>16</v>
       </c>
       <c r="P41" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q41" t="inlineStr"/>
     </row>
@@ -7200,7 +7306,7 @@
         <v>46113</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -7252,7 +7358,7 @@
         <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q42" t="inlineStr"/>
     </row>
@@ -7261,7 +7367,7 @@
         <v>46113</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -7317,7 +7423,7 @@
         <v>7</v>
       </c>
       <c r="P43" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q43" t="inlineStr"/>
     </row>
@@ -7326,7 +7432,7 @@
         <v>46113</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7382,7 +7488,7 @@
         <v>7</v>
       </c>
       <c r="P44" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="Q44" t="inlineStr"/>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -3230,17 +3230,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3282,1350 +3282,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-14T05:50:10Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -26,7 +26,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -86,6 +86,80 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="00A8C4F0"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A8C4F0"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF8080"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFE699"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007CFCFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00A8C4F0"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000E676"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF4D4D"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFC000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFD966"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00AAAAAA"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00AAAAAA"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="001F5BD6"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="15"/>
     </font>
     <font>
@@ -95,14 +169,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FF4D4D"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00FF8080"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -122,6 +192,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00173A73"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000E2246"/>
       </patternFill>
     </fill>
   </fills>
@@ -151,7 +226,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -209,6 +284,79 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,13 +365,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -594,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -835,18 +983,16 @@
       <c r="A6" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B6" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>16</v>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -854,7 +1000,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -868,22 +1014,18 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -891,7 +1033,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -905,13 +1047,13 @@
       </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>38</v>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -933,12 +1075,12 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr">
@@ -956,7 +1098,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -965,9 +1107,7 @@
       <c r="A8" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B8" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="7" t="inlineStr">
@@ -976,7 +1116,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -984,7 +1124,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -998,18 +1138,14 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
@@ -1017,7 +1153,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1031,21 +1167,21 @@
       </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G9" s="15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>83</v>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>38</v>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>59</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1059,26 +1195,30 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1087,18 +1227,16 @@
       <c r="A10" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B10" s="5" t="n">
-        <v>215</v>
-      </c>
+      <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F10" s="8" t="n">
-        <v>16</v>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1106,7 +1244,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1120,18 +1258,18 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1139,7 +1277,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1148,16 +1286,18 @@
       <c r="A11" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F11" s="14" t="n">
-        <v>24</v>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1165,7 +1305,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1179,18 +1319,18 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1198,7 +1338,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1207,7 +1347,9 @@
       <c r="A12" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B12" s="5" t="inlineStr"/>
+      <c r="B12" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr">
@@ -1216,7 +1358,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1224,7 +1366,7 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1238,14 +1380,18 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1253,7 +1399,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1262,16 +1408,18 @@
       <c r="A13" s="4" t="n">
         <v>46095</v>
       </c>
-      <c r="B13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>28</v>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F13" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1279,7 +1427,7 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -1293,18 +1441,18 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1312,7 +1460,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1352,7 +1500,7 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
+          <t>Jumpsuit Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr"/>
@@ -1407,7 +1555,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr"/>
@@ -2664,7 +2812,7 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
@@ -2679,7 +2827,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2699,7 +2847,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2716,24 +2864,16 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M37" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2744,25 +2884,27 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B38" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F38" s="14" t="n">
-        <v>28</v>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
         <is>
@@ -2770,7 +2912,7 @@
         </is>
       </c>
       <c r="H38" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I38" s="11" t="inlineStr">
         <is>
@@ -2779,23 +2921,19 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="L38" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L38" s="12" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr"/>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O38" s="6" t="n">
@@ -2803,75 +2941,75 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B39" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F39" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H39" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="I39" s="17" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I39" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
-        </is>
-      </c>
-      <c r="L39" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L39" s="12" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr"/>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O39" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B40" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
       <c r="E40" s="7" t="inlineStr">
@@ -2880,7 +3018,7 @@
         </is>
       </c>
       <c r="F40" s="8" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
@@ -2888,7 +3026,7 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I40" s="11" t="inlineStr">
         <is>
@@ -2897,19 +3035,19 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr"/>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O40" s="6" t="n">
@@ -2917,25 +3055,27 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B41" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F41" s="14" t="n">
-        <v>24</v>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -2943,7 +3083,7 @@
         </is>
       </c>
       <c r="H41" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
@@ -2952,23 +3092,19 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr"/>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O41" s="6" t="n">
@@ -2976,16 +3112,18 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="7" t="inlineStr">
@@ -2994,7 +3132,7 @@
         </is>
       </c>
       <c r="F42" s="8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3002,7 +3140,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -3011,23 +3149,19 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O42" s="6" t="n">
@@ -3035,25 +3169,27 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F43" s="14" t="n">
-        <v>28</v>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F43" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3061,7 +3197,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -3070,23 +3206,19 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O43" s="6" t="n">
@@ -3094,25 +3226,27 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr"/>
+        <v>46095</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>215</v>
+      </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F44" s="14" t="n">
-        <v>28</v>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3120,7 +3254,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3129,23 +3263,27 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L44" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O44" s="6" t="n">
@@ -3153,27 +3291,25 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B45" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F45" s="8" t="n">
-        <v>16</v>
+      <c r="E45" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F45" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3181,7 +3317,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3195,18 +3331,18 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3214,75 +3350,75 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B46" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G46" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I46" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F46" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="I46" s="17" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr"/>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
       <c r="E47" s="7" t="inlineStr">
@@ -3291,7 +3427,7 @@
         </is>
       </c>
       <c r="F47" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3299,7 +3435,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3308,23 +3444,19 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3332,27 +3464,25 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>7</v>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3360,7 +3490,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3369,34 +3499,451 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="Q48" s="12" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
+      <c r="C49" s="5" t="inlineStr"/>
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I49" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="K49" s="12" t="inlineStr">
+        <is>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr"/>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P49" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+        </is>
+      </c>
+      <c r="Q49" s="12" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
+      <c r="C50" s="5" t="inlineStr"/>
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I50" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K50" s="12" t="inlineStr">
+        <is>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="inlineStr"/>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="Q50" s="12" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr"/>
+      <c r="C51" s="5" t="inlineStr"/>
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F51" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I51" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K51" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="inlineStr"/>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P51" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="O48" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P48" s="12" t="inlineStr">
+      <c r="O52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q48" s="12" t="inlineStr"/>
+      <c r="Q55" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3413,13 +3960,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -3471,12 +4018,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>CONFIDENCE_CHANGED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3486,15 +4033,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-14T10:23:02Z</t>
+          <t>2026-03-14T10:57:13Z</t>
         </is>
       </c>
     </row>
@@ -3506,17 +4065,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3524,7 +4083,187 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-14T10:23:02Z</t>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-14T10:57:13Z</t>
         </is>
       </c>
     </row>
@@ -3539,7 +4278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3555,7 +4294,7 @@
     <col width="54" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
-    <col width="70" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
@@ -3783,11 +4522,11 @@
         <v>46095</v>
       </c>
       <c r="B4" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3807,27 +4546,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -3835,16 +4570,16 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
@@ -3857,7 +4592,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3877,12 +4612,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -3905,13 +4640,13 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Q5" t="n">
         <v>59</v>
@@ -3923,7 +4658,7 @@
         <v>46095</v>
       </c>
       <c r="B6" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -3947,23 +4682,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -3971,16 +4702,16 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
@@ -3993,12 +4724,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4013,15 +4744,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4033,20 +4768,20 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="Q7" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -4055,11 +4790,11 @@
         <v>46095</v>
       </c>
       <c r="B8" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4079,23 +4814,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -4103,16 +4838,16 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
@@ -4121,11 +4856,11 @@
         <v>46095</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4145,23 +4880,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mar 14 Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4169,16 +4904,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -4187,7 +4922,7 @@
         <v>46095</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -4211,19 +4946,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mar 14 Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -4231,16 +4970,16 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
@@ -4249,11 +4988,11 @@
         <v>46095</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4273,23 +5012,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -4297,16 +5036,16 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
@@ -4339,7 +5078,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mar 14 Jumpsuit Jordan x Teyana Taylor</t>
+          <t>Jumpsuit Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -4401,7 +5140,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mar 14 Short-Sleeve Tee Jordan x Teyana Taylor</t>
+          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -5763,7 +6502,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -5783,14 +6522,10 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://images.footlocker.com/content/dam/final/footlocker/site/homepage/2026/february/260225-fl-flca-recrne5wvpiszp57g-top-nav-image-update/260225-fl-flca-recRNe5WvpISZp57G-top-nav-image-update-mens-basketball.jpg</t>
-        </is>
-      </c>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
         <v>3</v>
@@ -5824,24 +6559,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5857,13 +6584,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -5872,14 +6599,14 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5894,28 +6621,24 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -5923,91 +6646,87 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B37" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="18" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6026,24 +6745,24 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -6051,29 +6770,29 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
-        <v>46096</v>
+        <v>46095</v>
       </c>
       <c r="B39" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6088,28 +6807,24 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -6117,25 +6832,25 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
-        <v>46098</v>
+        <v>46095</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6154,28 +6869,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mar 17 Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6183,29 +6894,29 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="18" t="n">
-        <v>46099</v>
+        <v>46095</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6220,28 +6931,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6249,29 +6956,29 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="18" t="n">
-        <v>46102</v>
+        <v>46095</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6286,28 +6993,32 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mar 21 Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6315,29 +7026,29 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="18" t="n">
-        <v>46113</v>
+        <v>46096</v>
       </c>
       <c r="B43" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6357,23 +7068,23 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6381,87 +7092,91 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q43" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
-        <v>46113</v>
+        <v>46096</v>
       </c>
       <c r="B44" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q44" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n">
-        <v>46113</v>
+        <v>46096</v>
       </c>
       <c r="B45" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6480,28 +7195,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -6509,29 +7220,29 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="n">
-        <v>46113</v>
+        <v>46096</v>
       </c>
       <c r="B46" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6546,28 +7257,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -6575,18 +7286,476 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>50</v>
+      </c>
+      <c r="R46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="18" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="n">
         <v>7</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q47" t="n">
+        <v>50</v>
+      </c>
+      <c r="R47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B48" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>50</v>
+      </c>
+      <c r="R48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B49" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>50</v>
+      </c>
+      <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B50" t="n">
+        <v>130</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q50" t="n">
         <v>59</v>
       </c>
-      <c r="R46" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B51" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>59</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" t="n">
+        <v>130</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>59</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>59</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6760,207 +7929,370 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Monthly Releases</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>By Brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>RELEASE SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>Next 35 Days  ·  52 releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="21" t="inlineStr">
+        <is>
+          <t>STATS AT A GLANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>Total Releases</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>52</v>
+      </c>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Must Watch</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="24" t="n"/>
+      <c r="D6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="24" t="n"/>
+      <c r="D7" s="24" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>High Hype</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>High Confidence</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Avg Retail Price</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="inlineStr">
+        <is>
+          <t>$206</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="22" t="inlineStr">
+        <is>
+          <t>Avg Flip %</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>HYPE BREAKDOWN</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>CONFIDENCE BREAKDOWN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="31" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D15" s="36" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="37" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>38</v>
+      </c>
+      <c r="C16" s="38" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>WHERE / RELEASE METHOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="40" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>TOP BRANDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Air Jordan</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B22" s="42" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>Nike</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B23" s="42" t="n">
         <v>16</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>████████████████████</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B24" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>██████████</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>Puma</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B25" s="42" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>████</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Vans</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B26" s="42" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>████</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>ASICS</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B27" s="42" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>Adidas</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B28" s="42" t="n">
         <v>2</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
+        <is>
+          <t>██</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>Converse</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="B29" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="43" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>Crocs</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Hype Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Confidence Breakdown</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
+      <c r="B30" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>█</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6979,26 +8311,26 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="44" t="inlineStr">
         <is>
           <t>How Scores Work</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="45" t="inlineStr">
         <is>
           <t>HYPE SCORE  (0–100+)</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>Brand Tier</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="47" t="inlineStr">
         <is>
           <t>HIGH brands (Air Jordan, Nike, Yeezy, New Balance, Adidas): +12 pts
 MID brands (Vans, Converse, Puma, Reebok, ASICS, Saucony, Hoka, Salomon): +7 pts
@@ -7007,96 +8339,96 @@
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="21" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>Collab</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="47" t="inlineStr">
         <is>
           <t>Any collab keyword (Travis Scott, Off-White, Supreme, Bad Bunny, Kith…): +20 pts</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="21" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Limited / Rare</t>
         </is>
       </c>
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="47" t="inlineStr">
         <is>
           <t>Limited, Exclusive, QS, PE, Raffle, Friends &amp; Family, Sample…: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="21" t="inlineStr">
+      <c r="A7" s="46" t="inlineStr">
         <is>
           <t>Hot Model</t>
         </is>
       </c>
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Jordan 1–13, Dunk, Air Max, Kobe, Yeezy Boost, Samba, NB 550/990…: +12 pts</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="21" t="inlineStr">
+      <c r="A8" s="46" t="inlineStr">
         <is>
           <t>Retro / Heritage</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Retro, OG, Original, Vintage, Heritage: +4 pts</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="21" t="inlineStr">
+      <c r="A9" s="46" t="inlineStr">
         <is>
           <t>Price Signal</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Retail ≥ $250 OR retail ≤ $110: +3 pts</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="21" t="inlineStr">
+      <c r="A10" s="46" t="inlineStr">
         <is>
           <t>Resale Ratio</t>
         </is>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Market ÷ Retail ≥ 2.5×: +35 pts  |  ≥ 2.0×: +28  |  ≥ 1.5×: +18  |  ≥ 1.2×: +8</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="21" t="inlineStr">
+      <c r="A11" s="46" t="inlineStr">
         <is>
           <t>Resale Spread</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="47" t="inlineStr">
         <is>
           <t>Market − Retail ≥ $200: +15 pts  |  ≥ $150: +10  |  ≥ $75: +6  |  ≥ $30: +2</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="48" t="inlineStr">
         <is>
           <t>Hype Level</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="47" t="inlineStr">
         <is>
           <t>HIGH ≥ 42 pts     MED ≥ 20 pts     LOW &lt; 20 pts</t>
         </is>
@@ -7104,103 +8436,103 @@
     </row>
     <row r="13" ht="24" customHeight="1"/>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>CONFIDENCE SCORE  (0–100)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="21" t="inlineStr">
+      <c r="A15" s="46" t="inlineStr">
         <is>
           <t>Primary Source</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="47" t="inlineStr">
         <is>
           <t>Release confirmed by primary scraper (GOAT): +25 pts</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="21" t="inlineStr">
+      <c r="A16" s="46" t="inlineStr">
         <is>
           <t>Secondary Source</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="47" t="inlineStr">
         <is>
           <t>Confirmed by at least one additional source: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="21" t="inlineStr">
+      <c r="A17" s="46" t="inlineStr">
         <is>
           <t>Retail Price</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>retailPrice field is populated: +15 pts</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="21" t="inlineStr">
+      <c r="A18" s="46" t="inlineStr">
         <is>
           <t>Image</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="47" t="inlineStr">
         <is>
           <t>imageUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="21" t="inlineStr">
+      <c r="A19" s="46" t="inlineStr">
         <is>
           <t>Release URL</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>releaseUrl field is populated: +10 pts</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
+      <c r="A20" s="46" t="inlineStr">
         <is>
           <t>Source Count</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="47" t="inlineStr">
         <is>
           <t>Seen by 3+ sources: +28 pts  |  Seen by 2 sources: +18 pts</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="21" t="inlineStr">
+      <c r="A21" s="46" t="inlineStr">
         <is>
           <t>Single-source cap</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>Releases seen by only 1 source are capped at 59 (cannot reach HIGH)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="49" t="inlineStr">
         <is>
           <t>Confidence Level</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="47" t="inlineStr">
         <is>
           <t>HIGH ≥ 60 pts     MED ≥ 32 pts     LOW &lt; 32 pts</t>
         </is>
@@ -7208,43 +8540,43 @@
     </row>
     <row r="23" ht="24" customHeight="1"/>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>PRIORITY</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="50" t="inlineStr">
         <is>
           <t>Must Watch</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>Hype = HIGH  AND  Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="47" t="inlineStr">
         <is>
           <t>Hype = HIGH + Confidence = MED, OR Hype = MED + Confidence = HIGH</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="21" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="B27" s="22" t="inlineStr">
+      <c r="A27" s="46" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="B27" s="47" t="inlineStr">
         <is>
           <t>All other hype / confidence combinations</t>
         </is>
@@ -7252,43 +8584,43 @@
     </row>
     <row r="28" ht="24" customHeight="1"/>
     <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="45" t="inlineStr">
         <is>
           <t>FLIP SCORE</t>
         </is>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="A30" s="46" t="inlineStr">
         <is>
           <t>Formula</t>
         </is>
       </c>
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>Flip % = round((Market Value − Retail Price) / Retail Price × 100)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="21" t="inlineStr">
+      <c r="A31" s="46" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
-      <c r="B31" s="22" t="inlineStr">
+      <c r="B31" s="47" t="inlineStr">
         <is>
           <t>$150 retail, $225 market  →  Flip % = +50%  (50% above retail)</t>
         </is>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="21" t="inlineStr">
+      <c r="A32" s="46" t="inlineStr">
         <is>
           <t>No value</t>
         </is>
       </c>
-      <c r="B32" s="22" t="inlineStr">
+      <c r="B32" s="47" t="inlineStr">
         <is>
           <t>Shown as blank when retail or market value is missing</t>
         </is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q55"/>
+  <dimension ref="A1:Q86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -3591,16 +3591,18 @@
       <c r="A50" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B50" s="5" t="inlineStr"/>
+      <c r="B50" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F50" s="14" t="n">
-        <v>28</v>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F50" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3608,7 +3610,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3617,23 +3619,19 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -3641,14 +3639,14 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46102</v>
+        <v>46099</v>
       </c>
       <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr"/>
@@ -3681,12 +3679,12 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
@@ -3700,27 +3698,27 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>16</v>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>38</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3742,15 +3740,19 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="M52" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3761,17 +3763,17 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr"/>
@@ -3781,7 +3783,7 @@
         </is>
       </c>
       <c r="F53" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3798,15 +3800,19 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
@@ -3818,17 +3824,17 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="6" t="inlineStr"/>
@@ -3855,17 +3861,17 @@
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr"/>
@@ -3879,17 +3885,17 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C55" s="5" t="inlineStr"/>
       <c r="D55" s="6" t="inlineStr"/>
@@ -3916,19 +3922,15 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
@@ -3940,10 +3942,1851 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr">
+        <is>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F57" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+        </is>
+      </c>
+      <c r="Q58" s="12" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B59" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C59" s="5" t="inlineStr"/>
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G59" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H59" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K59" s="12" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="L59" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="M59" s="6" t="inlineStr"/>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P59" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+        </is>
+      </c>
+      <c r="Q62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B63" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B64" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+        </is>
+      </c>
+      <c r="Q64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F65" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="L66" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+        </is>
+      </c>
+      <c r="Q66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+        </is>
+      </c>
+      <c r="Q67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="L68" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+        </is>
+      </c>
+      <c r="Q68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F69" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L70" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+        </is>
+      </c>
+      <c r="Q70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr"/>
+      <c r="M71" s="6" t="inlineStr"/>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="Q71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L72" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M72" s="6" t="inlineStr"/>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+        </is>
+      </c>
+      <c r="Q72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr"/>
+      <c r="M73" s="6" t="inlineStr"/>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="Q73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L74" s="12" t="inlineStr"/>
+      <c r="M74" s="6" t="inlineStr"/>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="Q74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="Q75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C76" s="5" t="inlineStr"/>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L76" s="12" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="Q76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="6" t="inlineStr"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L78" s="12" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="Q78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L80" s="12" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="Q80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>210</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="6" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr"/>
+      <c r="C82" s="5" t="inlineStr"/>
+      <c r="D82" s="6" t="inlineStr"/>
+      <c r="E82" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F82" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L82" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr"/>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C83" s="5" t="inlineStr"/>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr"/>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C84" s="5" t="inlineStr"/>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L84" s="12" t="inlineStr"/>
+      <c r="M84" s="6" t="inlineStr"/>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C85" s="5" t="inlineStr"/>
+      <c r="D85" s="6" t="inlineStr"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L86" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr"/>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q55" s="12" t="inlineStr"/>
+      <c r="Q86" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3960,13 +5803,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="65" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -4018,42 +5861,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CONFIDENCE_CHANGED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4065,7 +5896,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4083,7 +5914,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4095,17 +5926,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -4113,7 +5944,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4125,17 +5956,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -4143,7 +5974,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4155,17 +5986,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -4173,7 +6004,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4185,17 +6016,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -4203,7 +6034,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4215,7 +6046,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4225,7 +6056,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -4233,7 +6064,7 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4245,17 +6076,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -4263,7 +6094,697 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-14T10:57:13Z</t>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-14T17:01:57Z</t>
         </is>
       </c>
     </row>
@@ -4278,7 +6799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R53"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7370,11 +9891,11 @@
         <v>46099</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7389,28 +9910,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7418,22 +9935,22 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="18" t="n">
-        <v>46102</v>
+        <v>46099</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
@@ -7460,12 +9977,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -7484,7 +10001,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -7499,14 +10016,14 @@
     </row>
     <row r="50">
       <c r="A50" s="18" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B50" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7526,15 +10043,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7550,13 +10071,13 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="Q50" t="n">
         <v>59</v>
@@ -7565,10 +10086,10 @@
     </row>
     <row r="51">
       <c r="A51" s="18" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B51" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7587,15 +10108,19 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
@@ -7612,13 +10137,13 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q51" t="n">
         <v>59</v>
@@ -7627,10 +10152,10 @@
     </row>
     <row r="52">
       <c r="A52" s="18" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B52" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -7649,17 +10174,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -7678,7 +10203,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -7693,10 +10218,10 @@
     </row>
     <row r="53">
       <c r="A53" s="18" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B53" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7715,19 +10240,15 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
@@ -7744,7 +10265,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -7756,6 +10277,2004 @@
         <v>59</v>
       </c>
       <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B54" t="n">
+        <v>210</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>59</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B55" t="n">
+        <v>210</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>59</v>
+      </c>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B56" t="n">
+        <v>210</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>59</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B57" t="n">
+        <v>210</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>59</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B58" t="n">
+        <v>210</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>59</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B59" t="n">
+        <v>210</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>59</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B60" t="n">
+        <v>210</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>59</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B61" t="n">
+        <v>210</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>59</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B62" t="n">
+        <v>210</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>59</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B63" t="n">
+        <v>210</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>59</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B64" t="n">
+        <v>210</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>59</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B65" t="n">
+        <v>210</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>59</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B66" t="n">
+        <v>210</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>59</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B67" t="n">
+        <v>210</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>59</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B68" t="n">
+        <v>210</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>59</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B69" t="n">
+        <v>210</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>59</v>
+      </c>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B70" t="n">
+        <v>210</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>59</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B71" t="n">
+        <v>210</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>59</v>
+      </c>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B72" t="n">
+        <v>210</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>59</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B73" t="n">
+        <v>210</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>59</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B74" t="n">
+        <v>210</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>59</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B75" t="n">
+        <v>210</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>59</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B76" t="n">
+        <v>210</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>59</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B77" t="n">
+        <v>210</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>59</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B78" t="n">
+        <v>210</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>59</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B79" t="n">
+        <v>210</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>59</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>50</v>
+      </c>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B81" t="n">
+        <v>130</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>59</v>
+      </c>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B82" t="n">
+        <v>130</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>59</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B83" t="n">
+        <v>130</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>59</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B84" t="n">
+        <v>130</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>59</v>
+      </c>
+      <c r="R84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7948,7 +12467,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  52 releases</t>
+          <t>Next 35 Days  ·  83 releases</t>
         </is>
       </c>
     </row>
@@ -7966,7 +12485,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
@@ -8027,7 +12546,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>$206</t>
+          <t>$208</t>
         </is>
       </c>
       <c r="C10" s="24" t="n"/>
@@ -8084,7 +12603,7 @@
         </is>
       </c>
       <c r="B15" s="34" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
@@ -8092,7 +12611,7 @@
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8102,7 +12621,7 @@
         </is>
       </c>
       <c r="B16" s="30" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
@@ -8127,7 +12646,7 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="24" t="n"/>
@@ -8142,11 +12661,11 @@
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="41" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="B22" s="42" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
@@ -8158,15 +12677,15 @@
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="41" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="B23" s="42" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>████████████████████</t>
+          <t>████████████</t>
         </is>
       </c>
       <c r="D23" s="24" t="n"/>
@@ -8178,11 +12697,11 @@
         </is>
       </c>
       <c r="B24" s="42" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C24" s="43" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>███████████</t>
         </is>
       </c>
       <c r="D24" s="24" t="n"/>
@@ -8194,7 +12713,7 @@
         </is>
       </c>
       <c r="B25" s="42" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
@@ -8206,15 +12725,15 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B26" s="42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="43" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D26" s="24" t="n"/>
@@ -8222,15 +12741,15 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B27" s="42" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="43" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D27" s="24" t="n"/>
@@ -8242,7 +12761,7 @@
         </is>
       </c>
       <c r="B28" s="42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" s="43" t="inlineStr">
         <is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q86"/>
+  <dimension ref="A1:Q51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -867,11 +867,9 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
@@ -888,7 +886,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -902,14 +900,14 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>adidas DON Issue 7 "Best Of Adi"</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -917,27 +915,25 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9497.html</t>
+          <t>https://sneakernews.com/2026/02/26/adidas-don-issue-7-black-gold-jq9435</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>12</v>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -945,7 +941,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -954,19 +950,23 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -974,14 +974,14 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
@@ -992,19 +992,19 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G6" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I6" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+        <v>28</v>
+      </c>
+      <c r="G6" s="15" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
@@ -1014,12 +1014,12 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
@@ -1029,22 +1029,20 @@
         </is>
       </c>
       <c r="O6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46096</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr">
@@ -1053,7 +1051,7 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1061,7 +1059,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1075,22 +1073,14 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1098,25 +1088,25 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>12</v>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1133,15 +1123,19 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr"/>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
@@ -1153,27 +1147,25 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46097</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F9" s="14" t="n">
-        <v>38</v>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1181,7 +1173,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1190,27 +1182,19 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1218,14 +1202,14 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
@@ -1236,7 +1220,7 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1258,18 +1242,18 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1277,18 +1261,16 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
@@ -1297,7 +1279,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1305,7 +1287,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1314,23 +1296,23 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1338,17 +1320,17 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
@@ -1358,7 +1340,7 @@
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1375,19 +1357,15 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1399,27 +1377,25 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46099</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr"/>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="n">
-        <v>16</v>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F13" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1427,7 +1403,7 @@
         </is>
       </c>
       <c r="H13" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
@@ -1441,18 +1417,18 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O13" s="6" t="n">
@@ -1460,25 +1436,27 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B14" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>12</v>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>38</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1486,7 +1464,7 @@
         </is>
       </c>
       <c r="H14" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
@@ -1500,14 +1478,22 @@
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Jumpsuit Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O14" s="6" t="n">
@@ -1515,16 +1501,18 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="7" t="inlineStr">
@@ -1533,7 +1521,7 @@
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1541,7 +1529,7 @@
         </is>
       </c>
       <c r="H15" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
@@ -1555,14 +1543,18 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="L15" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L15" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M15" s="6" t="inlineStr"/>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O15" s="6" t="n">
@@ -1570,17 +1562,17 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
@@ -1638,10 +1630,10 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C17" s="5" t="inlineStr"/>
       <c r="D17" s="6" t="inlineStr"/>
@@ -1695,20 +1687,20 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="n">
-        <v>7</v>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1725,17 +1717,17 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>basketball, exclusive</t>
         </is>
       </c>
       <c r="M18" s="6" t="inlineStr">
@@ -1753,17 +1745,17 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="6" t="inlineStr"/>
@@ -1817,10 +1809,10 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
@@ -1878,10 +1870,10 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
@@ -1939,10 +1931,10 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
@@ -2000,10 +1992,10 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
@@ -2057,10 +2049,10 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
@@ -2114,10 +2106,10 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C25" s="5" t="inlineStr"/>
       <c r="D25" s="6" t="inlineStr"/>
@@ -2171,10 +2163,10 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
@@ -2232,20 +2224,20 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>12</v>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2267,12 +2259,12 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
@@ -2286,17 +2278,17 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
@@ -2328,7 +2320,7 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
@@ -2347,17 +2339,17 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
@@ -2389,7 +2381,7 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -2408,17 +2400,17 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C30" s="5" t="inlineStr"/>
       <c r="D30" s="6" t="inlineStr"/>
@@ -2450,12 +2442,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2469,27 +2461,27 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F31" s="14" t="n">
-        <v>24</v>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2511,12 +2503,12 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
@@ -2530,18 +2522,16 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
-        <v>46095</v>
-      </c>
-      <c r="B32" s="5" t="n">
-        <v>215</v>
-      </c>
+        <v>46099</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="7" t="inlineStr">
@@ -2558,7 +2548,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2572,18 +2562,18 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2591,17 +2581,17 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
@@ -2659,10 +2649,10 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
@@ -2716,10 +2706,10 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
@@ -2777,10 +2767,10 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
@@ -2834,10 +2824,10 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
@@ -2891,10 +2881,10 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
@@ -2948,10 +2938,10 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
@@ -3005,10 +2995,10 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
@@ -3062,10 +3052,10 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
@@ -3119,10 +3109,10 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
@@ -3176,10 +3166,10 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
@@ -3233,10 +3223,10 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
@@ -3298,7 +3288,7 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46096</v>
+        <v>46100</v>
       </c>
       <c r="B45" s="5" t="inlineStr"/>
       <c r="C45" s="5" t="inlineStr"/>
@@ -3309,7 +3299,7 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3317,7 +3307,7 @@
         </is>
       </c>
       <c r="H45" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
@@ -3326,23 +3316,23 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="L45" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3350,14 +3340,14 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46096</v>
+        <v>46100</v>
       </c>
       <c r="B46" s="5" t="inlineStr"/>
       <c r="C46" s="5" t="inlineStr"/>
@@ -3368,66 +3358,66 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="H46" s="16" t="n">
-        <v>68</v>
-      </c>
-      <c r="I46" s="17" t="inlineStr">
-        <is>
-          <t>Watch</t>
+        <v>32</v>
+      </c>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I46" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46096</v>
+        <v>46102</v>
       </c>
       <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F47" s="8" t="n">
-        <v>12</v>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F47" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3449,10 +3439,14 @@
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
@@ -3464,25 +3458,27 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46096</v>
-      </c>
-      <c r="B48" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>24</v>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3490,7 +3486,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3499,23 +3495,23 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3523,16 +3519,18 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B49" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="7" t="inlineStr">
@@ -3541,7 +3539,7 @@
         </is>
       </c>
       <c r="F49" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3549,7 +3547,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3558,23 +3556,19 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3582,17 +3576,17 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46099</v>
+        <v>46113</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
@@ -3602,7 +3596,7 @@
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3619,15 +3613,19 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
@@ -3639,25 +3637,27 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B51" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr"/>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F51" s="14" t="n">
-        <v>28</v>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F51" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
@@ -3674,23 +3674,23 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -3698,2095 +3698,10 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C52" s="5" t="inlineStr"/>
-      <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F52" s="14" t="n">
-        <v>38</v>
-      </c>
-      <c r="G52" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H52" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I52" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="L52" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M52" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
-        </is>
-      </c>
-      <c r="Q52" s="12" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B53" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C53" s="5" t="inlineStr"/>
-      <c r="D53" s="6" t="inlineStr"/>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F53" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H53" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I53" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P53" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
-        </is>
-      </c>
-      <c r="Q53" s="12" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B54" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C54" s="5" t="inlineStr"/>
-      <c r="D54" s="6" t="inlineStr"/>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F54" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G54" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H54" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I54" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P54" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
-        </is>
-      </c>
-      <c r="Q54" s="12" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B55" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C55" s="5" t="inlineStr"/>
-      <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G55" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H55" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I55" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="K55" s="12" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L55" s="12" t="inlineStr"/>
-      <c r="M55" s="6" t="inlineStr"/>
-      <c r="N55" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O55" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P55" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
-        </is>
-      </c>
-      <c r="Q55" s="12" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B56" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C56" s="5" t="inlineStr"/>
-      <c r="D56" s="6" t="inlineStr"/>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F56" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="G56" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H56" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I56" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="L56" s="12" t="inlineStr">
-        <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M56" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P56" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
-        </is>
-      </c>
-      <c r="Q56" s="12" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C57" s="5" t="inlineStr"/>
-      <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G57" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H57" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I57" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr"/>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P57" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
-        </is>
-      </c>
-      <c r="Q57" s="12" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B58" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C58" s="5" t="inlineStr"/>
-      <c r="D58" s="6" t="inlineStr"/>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F58" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G58" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H58" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I58" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L58" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
-      <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P58" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
-        </is>
-      </c>
-      <c r="Q58" s="12" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B59" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C59" s="5" t="inlineStr"/>
-      <c r="D59" s="6" t="inlineStr"/>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F59" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G59" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H59" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I59" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K59" s="12" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="L59" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O59" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P59" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
-        </is>
-      </c>
-      <c r="Q59" s="12" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="6" t="inlineStr"/>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>22</v>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
-      <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
-        </is>
-      </c>
-      <c r="Q60" s="12" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="6" t="inlineStr"/>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F61" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L61" s="12" t="inlineStr"/>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F62" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L62" s="12" t="inlineStr"/>
-      <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
-        </is>
-      </c>
-      <c r="Q62" s="12" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B63" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C63" s="5" t="inlineStr"/>
-      <c r="D63" s="6" t="inlineStr"/>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G63" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H63" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I63" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J63" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="L63" s="12" t="inlineStr"/>
-      <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O63" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P63" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
-        </is>
-      </c>
-      <c r="Q63" s="12" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B64" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C64" s="5" t="inlineStr"/>
-      <c r="D64" s="6" t="inlineStr"/>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G64" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H64" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I64" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J64" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K64" s="12" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="L64" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O64" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P64" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
-        </is>
-      </c>
-      <c r="Q64" s="12" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B65" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C65" s="5" t="inlineStr"/>
-      <c r="D65" s="6" t="inlineStr"/>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F65" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H65" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I65" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J65" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K65" s="12" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="L65" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O65" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P65" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
-        </is>
-      </c>
-      <c r="Q65" s="12" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B66" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C66" s="5" t="inlineStr"/>
-      <c r="D66" s="6" t="inlineStr"/>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F66" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G66" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H66" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I66" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K66" s="12" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="L66" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M66" s="6" t="inlineStr"/>
-      <c r="N66" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P66" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
-        </is>
-      </c>
-      <c r="Q66" s="12" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B67" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C67" s="5" t="inlineStr"/>
-      <c r="D67" s="6" t="inlineStr"/>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F67" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G67" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H67" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I67" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J67" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K67" s="12" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="L67" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O67" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P67" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
-        </is>
-      </c>
-      <c r="Q67" s="12" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B68" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C68" s="5" t="inlineStr"/>
-      <c r="D68" s="6" t="inlineStr"/>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F68" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="G68" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H68" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I68" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K68" s="12" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="L68" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O68" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P68" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
-        </is>
-      </c>
-      <c r="Q68" s="12" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B69" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C69" s="5" t="inlineStr"/>
-      <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F69" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G69" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H69" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I69" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K69" s="12" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L69" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P69" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
-        </is>
-      </c>
-      <c r="Q69" s="12" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B70" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C70" s="5" t="inlineStr"/>
-      <c r="D70" s="6" t="inlineStr"/>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G70" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H70" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I70" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="K70" s="12" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L70" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O70" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P70" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
-        </is>
-      </c>
-      <c r="Q70" s="12" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B71" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C71" s="5" t="inlineStr"/>
-      <c r="D71" s="6" t="inlineStr"/>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F71" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G71" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H71" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I71" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="K71" s="12" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L71" s="12" t="inlineStr"/>
-      <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O71" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P71" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
-        </is>
-      </c>
-      <c r="Q71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B72" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C72" s="5" t="inlineStr"/>
-      <c r="D72" s="6" t="inlineStr"/>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G72" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I72" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="K72" s="12" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L72" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O72" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P72" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
-        </is>
-      </c>
-      <c r="Q72" s="12" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B73" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C73" s="5" t="inlineStr"/>
-      <c r="D73" s="6" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F73" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G73" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I73" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K73" s="12" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L73" s="12" t="inlineStr"/>
-      <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O73" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P73" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="Q73" s="12" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B74" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C74" s="5" t="inlineStr"/>
-      <c r="D74" s="6" t="inlineStr"/>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F74" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G74" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H74" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I74" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K74" s="12" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L74" s="12" t="inlineStr"/>
-      <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O74" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P74" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="Q74" s="12" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B75" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C75" s="5" t="inlineStr"/>
-      <c r="D75" s="6" t="inlineStr"/>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F75" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G75" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H75" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I75" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K75" s="12" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="L75" s="12" t="inlineStr"/>
-      <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O75" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P75" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="Q75" s="12" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B76" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C76" s="5" t="inlineStr"/>
-      <c r="D76" s="6" t="inlineStr"/>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F76" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I76" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L76" s="12" t="inlineStr"/>
-      <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O76" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P76" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="Q76" s="12" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B77" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C77" s="5" t="inlineStr"/>
-      <c r="D77" s="6" t="inlineStr"/>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F77" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I77" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L77" s="12" t="inlineStr"/>
-      <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O77" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P77" s="12" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="Q77" s="12" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B78" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C78" s="5" t="inlineStr"/>
-      <c r="D78" s="6" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F78" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I78" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K78" s="12" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L78" s="12" t="inlineStr"/>
-      <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P78" s="12" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="Q78" s="12" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B79" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C79" s="5" t="inlineStr"/>
-      <c r="D79" s="6" t="inlineStr"/>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F79" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G79" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I79" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K79" s="12" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L79" s="12" t="inlineStr"/>
-      <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O79" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P79" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="Q79" s="12" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B80" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C80" s="5" t="inlineStr"/>
-      <c r="D80" s="6" t="inlineStr"/>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F80" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H80" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I80" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J80" s="6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="K80" s="12" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L80" s="12" t="inlineStr"/>
-      <c r="M80" s="6" t="inlineStr"/>
-      <c r="N80" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O80" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P80" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="Q80" s="12" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B81" s="5" t="n">
-        <v>210</v>
-      </c>
-      <c r="C81" s="5" t="inlineStr"/>
-      <c r="D81" s="6" t="inlineStr"/>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F81" s="8" t="n">
-        <v>17</v>
-      </c>
-      <c r="G81" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I81" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K81" s="12" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L81" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M81" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="N81" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O81" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P81" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
-        </is>
-      </c>
-      <c r="Q81" s="12" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B82" s="5" t="inlineStr"/>
-      <c r="C82" s="5" t="inlineStr"/>
-      <c r="D82" s="6" t="inlineStr"/>
-      <c r="E82" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F82" s="14" t="n">
-        <v>28</v>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I82" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J82" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K82" s="12" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
-        </is>
-      </c>
-      <c r="L82" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="M82" s="6" t="inlineStr"/>
-      <c r="N82" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O82" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P82" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="Q82" s="12" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B83" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C83" s="5" t="inlineStr"/>
-      <c r="D83" s="6" t="inlineStr"/>
-      <c r="E83" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F83" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H83" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I83" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J83" s="6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="K83" s="12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L83" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O83" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P83" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="Q83" s="12" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B84" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C84" s="5" t="inlineStr"/>
-      <c r="D84" s="6" t="inlineStr"/>
-      <c r="E84" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="G84" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I84" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J84" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K84" s="12" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L84" s="12" t="inlineStr"/>
-      <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O84" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P84" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="Q84" s="12" t="inlineStr"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B85" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C85" s="5" t="inlineStr"/>
-      <c r="D85" s="6" t="inlineStr"/>
-      <c r="E85" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G85" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I85" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J85" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L85" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O85" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P85" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="Q85" s="12" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B86" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C86" s="5" t="inlineStr"/>
-      <c r="D86" s="6" t="inlineStr"/>
-      <c r="E86" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="G86" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I86" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J86" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K86" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L86" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O86" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P86" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q86" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5803,7 +3718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5861,12 +3776,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5876,7 +3791,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -5884,29 +3799,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -5914,19 +3829,19 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5936,7 +3851,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -5944,29 +3859,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -5974,29 +3889,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -6004,29 +3919,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -6034,29 +3949,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -6064,29 +3979,29 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -6094,29 +4009,29 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -6124,29 +4039,29 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -6154,29 +4069,29 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -6184,29 +4099,29 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -6214,29 +4129,29 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -6244,29 +4159,29 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Jumpsuit Jordan x Teyana Taylor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -6274,29 +4189,29 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -6304,19 +4219,19 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6326,7 +4241,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -6334,19 +4249,19 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6356,7 +4271,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -6364,19 +4279,19 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6386,7 +4301,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -6394,19 +4309,19 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6416,7 +4331,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -6424,19 +4339,19 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -6446,7 +4361,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -6454,29 +4369,29 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
@@ -6484,29 +4399,29 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -6514,29 +4429,29 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
@@ -6544,29 +4459,29 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
@@ -6574,29 +4489,29 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
@@ -6604,29 +4519,29 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -6634,29 +4549,29 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -6664,29 +4579,29 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -6694,29 +4609,29 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -6724,19 +4639,19 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6746,7 +4661,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -6754,29 +4669,29 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -6784,7 +4699,487 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-03-14T17:01:57Z</t>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>adidas DON Issue 7 "Best Of Adi"</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Jacquemus x Nike Moon Shoe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-03-15T07:17:05Z</t>
         </is>
       </c>
     </row>
@@ -6799,7 +5194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R84"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6815,7 +5210,7 @@
     <col width="54" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
     <col width="70" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="70" customWidth="1" min="14" max="14"/>
     <col width="7" customWidth="1" min="15" max="15"/>
     <col width="16" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
@@ -6916,10 +5311,10 @@
     </row>
     <row r="2">
       <c r="A2" s="18" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -6943,19 +5338,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>adidas DON Issue 7 "Best Of Adi"</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -6963,7 +5358,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9497.html</t>
+          <t>https://sneakernews.com/2026/02/26/adidas-don-issue-7-black-gold-jq9435</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -6972,20 +5367,20 @@
         <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="18" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B3" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -7000,24 +5395,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Air Jordan 13 Retro White and University Red</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -7025,22 +5424,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="18" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -7052,12 +5451,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -7067,12 +5466,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Air Jordan 14 Retro Black and University Blue</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -7083,33 +5482,33 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-teyana-taylor-concrete-rose</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="18" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B5" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -7133,27 +5532,19 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jordan x Teyana Taylor Apparel Collection</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -7161,29 +5552,29 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/J3003102.html</t>
+          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="18" t="n">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -7198,15 +5589,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
@@ -7215,7 +5610,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.nike.com/launch</t>
         </is>
       </c>
       <c r="L6" t="n">
@@ -7223,13 +5618,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -7238,14 +5633,14 @@
     </row>
     <row r="7">
       <c r="A7" s="18" t="n">
-        <v>46095</v>
+        <v>46097</v>
       </c>
       <c r="B7" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7260,32 +5655,24 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -7293,22 +5680,22 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="18" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
@@ -7335,23 +5722,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L8" t="n">
@@ -7359,13 +5746,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
@@ -7374,10 +5761,10 @@
     </row>
     <row r="9">
       <c r="A9" s="18" t="n">
-        <v>46095</v>
+        <v>46098</v>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -7396,28 +5783,28 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -7425,25 +5812,25 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B10" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -7462,19 +5849,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -7491,13 +5874,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -7506,14 +5889,14 @@
     </row>
     <row r="11">
       <c r="A11" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B11" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -7533,23 +5916,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -7557,29 +5940,29 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q11" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -7599,19 +5982,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jumpsuit Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L12" t="n">
@@ -7619,25 +6010,25 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -7661,19 +6052,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L13" t="n">
@@ -7681,25 +6076,25 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B14" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -7762,10 +6157,10 @@
     </row>
     <row r="15">
       <c r="A15" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B15" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -7824,14 +6219,14 @@
     </row>
     <row r="16">
       <c r="A16" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B16" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7846,17 +6241,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>retro</t>
+          <t>basketball, exclusive</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -7879,13 +6274,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -7894,10 +6289,10 @@
     </row>
     <row r="17">
       <c r="A17" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B17" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -7956,10 +6351,10 @@
     </row>
     <row r="18">
       <c r="A18" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B18" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -8022,10 +6417,10 @@
     </row>
     <row r="19">
       <c r="A19" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B19" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -8088,10 +6483,10 @@
     </row>
     <row r="20">
       <c r="A20" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B20" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -8154,10 +6549,10 @@
     </row>
     <row r="21">
       <c r="A21" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B21" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -8216,10 +6611,10 @@
     </row>
     <row r="22">
       <c r="A22" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B22" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -8278,10 +6673,10 @@
     </row>
     <row r="23">
       <c r="A23" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B23" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -8340,10 +6735,10 @@
     </row>
     <row r="24">
       <c r="A24" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B24" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -8406,14 +6801,14 @@
     </row>
     <row r="25">
       <c r="A25" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B25" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -8433,12 +6828,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -8457,13 +6852,13 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q25" t="n">
         <v>59</v>
@@ -8472,10 +6867,10 @@
     </row>
     <row r="26">
       <c r="A26" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B26" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -8499,7 +6894,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8523,7 +6918,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
@@ -8538,10 +6933,10 @@
     </row>
     <row r="27">
       <c r="A27" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B27" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -8565,7 +6960,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8589,7 +6984,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -8604,10 +6999,10 @@
     </row>
     <row r="28">
       <c r="A28" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B28" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -8631,12 +7026,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -8655,7 +7050,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -8670,14 +7065,14 @@
     </row>
     <row r="29">
       <c r="A29" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B29" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -8697,12 +7092,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -8721,13 +7116,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -8736,10 +7131,10 @@
     </row>
     <row r="30">
       <c r="A30" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B30" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -8763,23 +7158,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -8787,7 +7182,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -8796,16 +7191,16 @@
         <v>12</v>
       </c>
       <c r="Q30" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B31" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -8868,10 +7263,10 @@
     </row>
     <row r="32">
       <c r="A32" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B32" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -8930,10 +7325,10 @@
     </row>
     <row r="33">
       <c r="A33" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B33" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -8996,10 +7391,10 @@
     </row>
     <row r="34">
       <c r="A34" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B34" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -9058,10 +7453,10 @@
     </row>
     <row r="35">
       <c r="A35" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B35" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -9120,10 +7515,10 @@
     </row>
     <row r="36">
       <c r="A36" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B36" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -9182,10 +7577,10 @@
     </row>
     <row r="37">
       <c r="A37" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B37" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -9244,10 +7639,10 @@
     </row>
     <row r="38">
       <c r="A38" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B38" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -9306,10 +7701,10 @@
     </row>
     <row r="39">
       <c r="A39" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B39" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -9368,10 +7763,10 @@
     </row>
     <row r="40">
       <c r="A40" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B40" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -9430,10 +7825,10 @@
     </row>
     <row r="41">
       <c r="A41" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B41" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -9492,10 +7887,10 @@
     </row>
     <row r="42">
       <c r="A42" s="18" t="n">
-        <v>46095</v>
+        <v>46099</v>
       </c>
       <c r="B42" t="n">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -9562,7 +7957,7 @@
     </row>
     <row r="43">
       <c r="A43" s="18" t="n">
-        <v>46096</v>
+        <v>46100</v>
       </c>
       <c r="B43" t="n">
         <v>0</v>
@@ -9584,28 +7979,28 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -9613,22 +8008,26 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-13-retro-white-and-university-red</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
+        </is>
+      </c>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q43" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
-        <v>46096</v>
+        <v>46100</v>
       </c>
       <c r="B44" t="n">
         <v>0</v>
@@ -9640,68 +8039,72 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
+        </is>
+      </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q44" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="18" t="n">
-        <v>46096</v>
+        <v>46102</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9721,10 +8124,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
@@ -9733,7 +8140,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -9741,13 +8148,13 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/jordan-teyana-taylor-apparel-collection-static</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q45" t="n">
         <v>50</v>
@@ -9756,14 +8163,14 @@
     </row>
     <row r="46">
       <c r="A46" s="18" t="n">
-        <v>46096</v>
+        <v>46113</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9778,28 +8185,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -9807,25 +8214,25 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="18" t="n">
-        <v>46098</v>
+        <v>46113</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -9844,28 +8251,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -9873,25 +8276,25 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="n">
-        <v>46099</v>
+        <v>46113</v>
       </c>
       <c r="B48" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -9910,15 +8313,19 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
@@ -9935,13 +8342,13 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
         <v>59</v>
@@ -9950,14 +8357,14 @@
     </row>
     <row r="49">
       <c r="A49" s="18" t="n">
-        <v>46099</v>
+        <v>46113</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -9972,28 +8379,28 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -10001,2280 +8408,18 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B50" t="n">
-        <v>210</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>59</v>
-      </c>
-      <c r="R50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B51" t="n">
-        <v>210</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>59</v>
-      </c>
-      <c r="R51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B52" t="n">
-        <v>210</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>59</v>
-      </c>
-      <c r="R52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B53" t="n">
-        <v>210</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>1</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>59</v>
-      </c>
-      <c r="R53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B54" t="n">
-        <v>210</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>59</v>
-      </c>
-      <c r="R54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B55" t="n">
-        <v>210</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>59</v>
-      </c>
-      <c r="R55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B56" t="n">
-        <v>210</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>59</v>
-      </c>
-      <c r="R56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B57" t="n">
-        <v>210</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>1</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>59</v>
-      </c>
-      <c r="R57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B58" t="n">
-        <v>210</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>59</v>
-      </c>
-      <c r="R58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B59" t="n">
-        <v>210</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>59</v>
-      </c>
-      <c r="R59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B60" t="n">
-        <v>210</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>59</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B61" t="n">
-        <v>210</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>1</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>59</v>
-      </c>
-      <c r="R61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B62" t="n">
-        <v>210</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>59</v>
-      </c>
-      <c r="R62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B63" t="n">
-        <v>210</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>59</v>
-      </c>
-      <c r="R63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B64" t="n">
-        <v>210</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>59</v>
-      </c>
-      <c r="R64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B65" t="n">
-        <v>210</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>59</v>
-      </c>
-      <c r="R65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B66" t="n">
-        <v>210</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>hot-model, basketball, kids</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>59</v>
-      </c>
-      <c r="R66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B67" t="n">
-        <v>210</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>59</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B68" t="n">
-        <v>210</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>59</v>
-      </c>
-      <c r="R68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B69" t="n">
-        <v>210</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>59</v>
-      </c>
-      <c r="R69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B70" t="n">
-        <v>210</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>59</v>
-      </c>
-      <c r="R70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B71" t="n">
-        <v>210</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q71" t="n">
-        <v>59</v>
-      </c>
-      <c r="R71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B72" t="n">
-        <v>210</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L72" t="n">
-        <v>1</v>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>59</v>
-      </c>
-      <c r="R72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B73" t="n">
-        <v>210</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L73" t="n">
-        <v>1</v>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/order/search</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q73" t="n">
-        <v>59</v>
-      </c>
-      <c r="R73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B74" t="n">
-        <v>210</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L74" t="n">
-        <v>1</v>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q74" t="n">
-        <v>59</v>
-      </c>
-      <c r="R74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B75" t="n">
-        <v>210</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L75" t="n">
-        <v>1</v>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>59</v>
-      </c>
-      <c r="R75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B76" t="n">
-        <v>210</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L76" t="n">
-        <v>1</v>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>#main</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>59</v>
-      </c>
-      <c r="R76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B77" t="n">
-        <v>210</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L77" t="n">
-        <v>1</v>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q77" t="n">
-        <v>59</v>
-      </c>
-      <c r="R77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B78" t="n">
-        <v>210</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>59</v>
-      </c>
-      <c r="R78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="18" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B79" t="n">
-        <v>210</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>1</v>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q79" t="n">
-        <v>59</v>
-      </c>
-      <c r="R79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="18" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B80" t="n">
-        <v>0</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>1</v>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="n">
-        <v>28</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>50</v>
-      </c>
-      <c r="R80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B81" t="n">
-        <v>130</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>1</v>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>59</v>
-      </c>
-      <c r="R81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B82" t="n">
-        <v>130</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>59</v>
-      </c>
-      <c r="R82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B83" t="n">
-        <v>130</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>1</v>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q83" t="n">
-        <v>59</v>
-      </c>
-      <c r="R83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="18" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B84" t="n">
-        <v>130</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L84" t="n">
-        <v>1</v>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q84" t="n">
-        <v>59</v>
-      </c>
-      <c r="R84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12448,7 +8593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12467,7 +8612,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  83 releases</t>
+          <t>Next 35 Days  ·  48 releases</t>
         </is>
       </c>
     </row>
@@ -12485,7 +8630,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
@@ -12546,7 +8691,7 @@
       </c>
       <c r="B10" s="29" t="inlineStr">
         <is>
-          <t>$208</t>
+          <t>$201</t>
         </is>
       </c>
       <c r="C10" s="24" t="n"/>
@@ -12603,7 +8748,7 @@
         </is>
       </c>
       <c r="B15" s="34" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
@@ -12611,7 +8756,7 @@
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -12621,7 +8766,7 @@
         </is>
       </c>
       <c r="B16" s="30" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
@@ -12646,7 +8791,7 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="24" t="n"/>
@@ -12665,7 +8810,7 @@
         </is>
       </c>
       <c r="B22" s="42" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
@@ -12681,11 +8826,11 @@
         </is>
       </c>
       <c r="B23" s="42" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>████████████</t>
+          <t>█████████</t>
         </is>
       </c>
       <c r="D23" s="24" t="n"/>
@@ -12697,11 +8842,11 @@
         </is>
       </c>
       <c r="B24" s="42" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C24" s="43" t="inlineStr">
         <is>
-          <t>███████████</t>
+          <t>████████</t>
         </is>
       </c>
       <c r="D24" s="24" t="n"/>
@@ -12713,11 +8858,11 @@
         </is>
       </c>
       <c r="B25" s="42" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
-          <t>████</t>
+          <t>███</t>
         </is>
       </c>
       <c r="D25" s="24" t="n"/>
@@ -12725,11 +8870,11 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B26" s="42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" s="43" t="inlineStr">
         <is>
@@ -12741,15 +8886,15 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="41" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B27" s="42" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C27" s="43" t="inlineStr">
         <is>
-          <t>███</t>
+          <t>██</t>
         </is>
       </c>
       <c r="D27" s="24" t="n"/>
@@ -12761,7 +8906,7 @@
         </is>
       </c>
       <c r="B28" s="42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28" s="43" t="inlineStr">
         <is>
@@ -12785,22 +8930,6 @@
         </is>
       </c>
       <c r="D29" s="24" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="41" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="B30" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="43" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="D30" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -742,7 +742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -1515,13 +1515,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>16</v>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="n">
+        <v>26</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1543,15 +1543,19 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1582,7 +1586,7 @@
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1599,17 +1603,17 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
@@ -1623,7 +1627,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1643,7 +1647,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1660,15 +1664,19 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -1680,7 +1688,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1694,13 +1702,13 @@
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="6" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>22</v>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1717,24 +1725,20 @@
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1745,7 +1749,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1765,7 +1769,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1782,12 +1786,12 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="L19" s="12" t="inlineStr"/>
@@ -1802,7 +1806,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1822,7 +1826,7 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1844,15 +1848,19 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L20" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
-      <c r="M20" s="6" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1863,7 +1871,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1905,14 +1913,10 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1944,7 +1948,7 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1966,12 +1970,12 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L22" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M22" s="6" t="inlineStr"/>
@@ -1985,7 +1989,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2027,10 +2031,14 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M23" s="6" t="inlineStr"/>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -2042,7 +2050,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2056,13 +2064,13 @@
       </c>
       <c r="C24" s="5" t="inlineStr"/>
       <c r="D24" s="6" t="inlineStr"/>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>12</v>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F24" s="14" t="n">
+        <v>22</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2084,10 +2092,14 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2099,7 +2111,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2141,7 +2153,7 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr"/>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2198,14 +2210,10 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="L26" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr"/>
       <c r="N26" s="6" t="inlineStr">
         <is>
@@ -2217,7 +2225,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2231,13 +2239,13 @@
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
-        <v>24</v>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
         <is>
@@ -2259,14 +2267,10 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr"/>
       <c r="N27" s="6" t="inlineStr">
         <is>
@@ -2278,7 +2282,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2292,13 +2296,13 @@
       </c>
       <c r="C28" s="5" t="inlineStr"/>
       <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F28" s="14" t="n">
-        <v>24</v>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2320,12 +2324,12 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr"/>
@@ -2339,7 +2343,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2381,7 +2385,7 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
@@ -2400,7 +2404,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2442,12 +2446,12 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2461,7 +2465,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2475,13 +2479,13 @@
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n">
-        <v>12</v>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F31" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2503,12 +2507,12 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M31" s="6" t="inlineStr"/>
@@ -2522,7 +2526,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2531,16 +2535,18 @@
       <c r="A32" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n">
-        <v>12</v>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F32" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2548,7 +2554,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2562,18 +2568,18 @@
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2581,7 +2587,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2601,7 +2607,7 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2618,12 +2624,12 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -2642,7 +2648,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2651,9 +2657,7 @@
       <c r="A34" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B34" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B34" s="5" t="inlineStr"/>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="7" t="inlineStr">
@@ -2662,7 +2666,7 @@
         </is>
       </c>
       <c r="F34" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2679,19 +2683,23 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr"/>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O34" s="6" t="n">
@@ -2699,7 +2707,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -2741,7 +2749,7 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr">
@@ -2760,7 +2768,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2780,7 +2788,7 @@
         </is>
       </c>
       <c r="F36" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2797,12 +2805,12 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="L36" s="12" t="inlineStr"/>
@@ -2817,7 +2825,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2837,7 +2845,7 @@
         </is>
       </c>
       <c r="F37" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2854,15 +2862,19 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -2874,7 +2886,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2916,7 +2928,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2931,7 +2943,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2973,7 +2985,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -2988,7 +3000,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3030,7 +3042,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3045,7 +3057,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3087,7 +3099,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -3102,7 +3114,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -3144,7 +3156,7 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr"/>
@@ -3159,7 +3171,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -3201,7 +3213,7 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr"/>
@@ -3216,7 +3228,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -3236,7 +3248,7 @@
         </is>
       </c>
       <c r="F44" s="8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3253,24 +3265,16 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M44" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3281,25 +3285,27 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F45" s="14" t="n">
-        <v>32</v>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3316,23 +3322,19 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3340,25 +3342,27 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F46" s="14" t="n">
-        <v>32</v>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3375,23 +3379,27 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O46" s="6" t="n">
@@ -3399,14 +3407,14 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
@@ -3417,7 +3425,7 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3425,7 +3433,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3434,23 +3442,23 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3458,27 +3466,25 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F48" s="8" t="n">
-        <v>16</v>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F48" s="14" t="n">
+        <v>32</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3495,23 +3501,23 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3519,27 +3525,25 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46102</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F49" s="8" t="n">
-        <v>12</v>
+      <c r="E49" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F49" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3547,7 +3551,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3556,19 +3560,23 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3576,27 +3584,25 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46107</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="n">
-        <v>7</v>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F50" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3604,7 +3610,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3613,23 +3619,23 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -3637,7 +3643,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -3657,7 +3663,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3674,17 +3680,17 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
@@ -3698,10 +3704,189 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q51" s="12" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C52" s="5" t="inlineStr"/>
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F52" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I52" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K52" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L52" s="12" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr"/>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q51" s="12" t="inlineStr"/>
+      <c r="Q54" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3718,7 +3903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3776,22 +3961,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3799,29 +3984,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-15T07:17:05Z</t>
+          <t>2026-03-15T17:02:39Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3829,29 +4014,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-15T07:17:05Z</t>
+          <t>2026-03-15T17:02:39Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 3 x Teyana Taylor Concrete Rose</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -3859,1327 +4044,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Crew Socks (4 Pairs) Jordan x Teyana Taylor Everyday Plus Cushioned</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Jumpsuit Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Short-Sleeve Tee Jordan x Teyana Taylor</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>adidas DON Issue 7 "Best Of Adi"</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-15T07:17:05Z</t>
+          <t>2026-03-15T17:02:39Z</t>
         </is>
       </c>
     </row>
@@ -5194,7 +4059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R49"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6032,7 +4897,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -6052,15 +4917,19 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6082,7 +4951,7 @@
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -6113,17 +4982,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -6142,13 +5011,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -6179,15 +5048,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -6204,13 +5077,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -6226,7 +5099,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6241,24 +5114,20 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6274,13 +5143,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -6311,12 +5180,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -6336,13 +5205,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -6378,15 +5247,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6402,13 +5275,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -6444,14 +5317,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -6468,7 +5337,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -6510,12 +5379,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -6534,13 +5403,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -6576,10 +5445,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -6596,7 +5469,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -6618,7 +5491,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6638,10 +5511,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -6658,13 +5535,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -6700,7 +5577,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -6720,7 +5597,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -6762,14 +5639,10 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
@@ -6786,7 +5659,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -6808,7 +5681,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -6828,14 +5701,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
@@ -6852,13 +5721,13 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q25" t="n">
         <v>59</v>
@@ -6874,7 +5743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6894,12 +5763,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -6918,13 +5787,13 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
         <v>59</v>
@@ -6960,7 +5829,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6984,7 +5853,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
@@ -7026,12 +5895,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -7050,7 +5919,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
@@ -7072,7 +5941,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -7092,12 +5961,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -7116,13 +5985,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -7134,11 +6003,11 @@
         <v>46099</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -7158,23 +6027,23 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -7182,16 +6051,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
@@ -7219,12 +6088,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -7248,13 +6117,13 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
         <v>59</v>
@@ -7266,7 +6135,7 @@
         <v>46099</v>
       </c>
       <c r="B32" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -7285,24 +6154,28 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -7310,13 +6183,17 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/4a1c66575467445342b9085cc4510900_1772681368.webp</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q32" t="n">
         <v>59</v>
@@ -7352,7 +6229,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -7376,7 +6253,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -7413,12 +6290,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -7438,13 +6315,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -7475,15 +6352,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -7500,13 +6381,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -7542,7 +6423,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -7562,7 +6443,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -7604,7 +6485,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -7624,7 +6505,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -7666,7 +6547,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -7686,7 +6567,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -7728,7 +6609,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -7748,7 +6629,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -7790,7 +6671,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -7810,7 +6691,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -7852,7 +6733,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -7872,7 +6753,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -7909,24 +6790,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7942,13 +6815,13 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>59</v>
@@ -7957,14 +6830,14 @@
     </row>
     <row r="43">
       <c r="A43" s="18" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7979,28 +6852,24 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -8008,17 +6877,13 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
         <v>59</v>
@@ -8027,14 +6892,14 @@
     </row>
     <row r="44">
       <c r="A44" s="18" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -8049,28 +6914,32 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L44" t="n">
@@ -8078,17 +6947,13 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="Q44" t="n">
         <v>59</v>
@@ -8097,7 +6962,7 @@
     </row>
     <row r="45">
       <c r="A45" s="18" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -8119,28 +6984,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -8148,29 +7013,33 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="18" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B46" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -8185,28 +7054,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -8214,13 +7083,17 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
+        </is>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="Q46" t="n">
         <v>59</v>
@@ -8229,14 +7102,14 @@
     </row>
     <row r="47">
       <c r="A47" s="18" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="B47" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -8251,24 +7124,28 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr"/>
+          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -8276,29 +7153,29 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q47" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="18" t="n">
-        <v>46113</v>
+        <v>46107</v>
       </c>
       <c r="B48" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8313,28 +7190,28 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -8342,16 +7219,16 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q48" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
@@ -8379,17 +7256,17 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -8408,18 +7285,212 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q49" t="n">
         <v>59</v>
       </c>
       <c r="R49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B50" t="n">
+        <v>130</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>59</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B51" t="n">
+        <v>130</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>59</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B52" t="n">
+        <v>130</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>59</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8612,7 +7683,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  48 releases</t>
+          <t>Next 35 Days  ·  51 releases</t>
         </is>
       </c>
     </row>
@@ -8630,7 +7701,7 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="24" t="n"/>
@@ -8748,7 +7819,7 @@
         </is>
       </c>
       <c r="B15" s="34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C15" s="35" t="inlineStr">
         <is>
@@ -8756,7 +7827,7 @@
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8766,7 +7837,7 @@
         </is>
       </c>
       <c r="B16" s="30" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="38" t="inlineStr">
         <is>
@@ -8791,7 +7862,7 @@
         </is>
       </c>
       <c r="B19" s="28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" s="24" t="n"/>
       <c r="D19" s="24" t="n"/>
@@ -8810,7 +7881,7 @@
         </is>
       </c>
       <c r="B22" s="42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
@@ -8826,11 +7897,11 @@
         </is>
       </c>
       <c r="B23" s="42" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>██████████</t>
         </is>
       </c>
       <c r="D23" s="24" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -53,10 +53,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,10 +67,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
     <font>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
     <font>
       <b val="1"/>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:Q58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -862,11 +862,11 @@
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -883,15 +883,19 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr"/>
+          <t>adidas Fear Of God Athletics III</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr">
         <is>
@@ -903,25 +907,25 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+          <t>https://sneakernews.com/2026/03/02/adidas-fear-of-god-athletics-iii-kj5967</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -929,7 +933,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -938,19 +942,15 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
-        </is>
-      </c>
-      <c r="L5" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe</t>
+        </is>
+      </c>
+      <c r="L5" s="12" t="inlineStr"/>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
@@ -976,11 +976,11 @@
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F6" s="8" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -997,23 +997,23 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1021,27 +1021,25 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1049,7 +1047,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1058,19 +1056,23 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L7" s="12" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="L7" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1078,25 +1080,25 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1113,17 +1115,17 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1137,27 +1139,25 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46098</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1174,27 +1174,23 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Thug Club x Converse Chuck 70</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M9" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1202,7 +1198,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>javascript:void(0)</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1218,11 +1214,11 @@
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1239,24 +1235,16 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L10" s="12" t="inlineStr">
-        <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1267,7 +1255,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1276,18 +1264,16 @@
       <c r="A11" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B11" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1295,7 +1281,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1309,18 +1295,18 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1328,7 +1314,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1344,11 +1330,11 @@
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1370,15 +1356,19 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M12" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1389,7 +1379,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1405,11 +1395,11 @@
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1426,20 +1416,24 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1450,7 +1444,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1464,13 +1458,13 @@
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n">
-        <v>7</v>
+      <c r="F14" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1487,15 +1481,19 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1507,7 +1505,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1523,11 +1521,11 @@
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1544,24 +1542,20 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr"/>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1572,7 +1566,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1586,13 +1580,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n">
-        <v>12</v>
+      <c r="F16" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1609,15 +1603,19 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L16" s="12" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
@@ -1629,7 +1627,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1645,11 +1643,11 @@
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1666,19 +1664,15 @@
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr">
         <is>
@@ -1690,7 +1684,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1706,11 +1700,11 @@
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1732,15 +1726,19 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L18" s="12" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="M18" s="6" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1751,7 +1749,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1767,11 +1765,11 @@
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1793,14 +1791,10 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1812,7 +1806,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1828,11 +1822,11 @@
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
@@ -1854,10 +1848,14 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr"/>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1869,7 +1867,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1883,12 +1881,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr"/>
       <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n">
+      <c r="F21" s="14" t="n">
         <v>12</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
@@ -1911,10 +1909,14 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1926,7 +1928,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1942,11 +1944,11 @@
       <c r="D22" s="6" t="inlineStr"/>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
@@ -1968,10 +1970,14 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -1983,7 +1989,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -1997,12 +2003,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr"/>
       <c r="D23" s="6" t="inlineStr"/>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F23" s="8" t="n">
+      <c r="F23" s="14" t="n">
         <v>12</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
@@ -2025,14 +2031,10 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr"/>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -2044,7 +2046,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2060,11 +2062,11 @@
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2086,14 +2088,10 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2103,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2121,11 +2119,11 @@
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2147,14 +2145,10 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="L25" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L25" s="12" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr"/>
       <c r="N25" s="6" t="inlineStr">
         <is>
@@ -2166,7 +2160,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2182,11 +2176,11 @@
       <c r="D26" s="6" t="inlineStr"/>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F26" s="14" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
         <is>
@@ -2208,12 +2202,12 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M26" s="6" t="inlineStr"/>
@@ -2227,7 +2221,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2241,12 +2235,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F27" s="14" t="n">
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="n">
         <v>24</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2269,12 +2263,12 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
@@ -2288,7 +2282,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2304,11 +2298,11 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2330,12 +2324,12 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr"/>
@@ -2349,7 +2343,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2358,16 +2352,18 @@
       <c r="A29" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B29" s="5" t="inlineStr"/>
+      <c r="B29" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2375,7 +2371,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2389,18 +2385,18 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2408,7 +2404,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2424,11 +2420,11 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2445,17 +2441,17 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2469,7 +2465,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2485,11 +2481,11 @@
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F31" s="8" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2506,15 +2502,19 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2540,13 +2540,13 @@
       </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="7" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>7</v>
+      <c r="F32" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2563,12 +2563,12 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L32" s="12" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2596,18 +2596,16 @@
       <c r="A33" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B33" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B33" s="5" t="inlineStr"/>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F33" s="8" t="n">
-        <v>3</v>
+      <c r="F33" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
         <is>
@@ -2624,19 +2622,23 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="L33" s="12" t="inlineStr"/>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+        </is>
+      </c>
+      <c r="L33" s="12" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="M33" s="6" t="inlineStr"/>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O33" s="6" t="n">
@@ -2644,7 +2646,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2658,13 +2660,13 @@
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
-        <v>3</v>
+      <c r="F34" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
@@ -2681,15 +2683,19 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -2701,7 +2707,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -2715,13 +2721,13 @@
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F35" s="8" t="n">
-        <v>3</v>
+      <c r="F35" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2738,12 +2744,12 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr"/>
@@ -2758,7 +2764,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2772,13 +2778,13 @@
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="7" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F36" s="8" t="n">
-        <v>3</v>
+      <c r="F36" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2795,15 +2801,19 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
@@ -2815,7 +2825,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2829,12 +2839,12 @@
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="7" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F37" s="8" t="n">
+      <c r="F37" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
@@ -2857,7 +2867,7 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L37" s="12" t="inlineStr"/>
@@ -2872,7 +2882,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2886,12 +2896,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="7" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -2914,7 +2924,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2929,7 +2939,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2943,12 +2953,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F39" s="8" t="n">
+      <c r="F39" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -2971,7 +2981,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -2986,7 +2996,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3000,12 +3010,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F40" s="8" t="n">
+      <c r="F40" s="14" t="n">
         <v>3</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3028,7 +3038,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3043,7 +3053,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3057,13 +3067,13 @@
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F41" s="8" t="n">
-        <v>17</v>
+      <c r="F41" s="14" t="n">
+        <v>3</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
         <is>
@@ -3080,24 +3090,16 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr"/>
       <c r="N41" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3108,25 +3110,27 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B42" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
@@ -3134,7 +3138,7 @@
         </is>
       </c>
       <c r="H42" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
@@ -3143,23 +3147,19 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O42" s="6" t="n">
@@ -3167,25 +3167,27 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B43" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
         <is>
@@ -3193,7 +3195,7 @@
         </is>
       </c>
       <c r="H43" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
@@ -3202,23 +3204,19 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr"/>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O43" s="6" t="n">
@@ -3226,25 +3224,27 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B44" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
@@ -3261,23 +3261,19 @@
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, exclusive</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O44" s="6" t="n">
@@ -3285,25 +3281,27 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
-        <v>46100</v>
-      </c>
-      <c r="B45" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F45" s="8" t="n">
-        <v>12</v>
+      <c r="F45" s="14" t="n">
+        <v>17</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
         <is>
@@ -3320,19 +3318,27 @@
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr"/>
-      <c r="M45" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O45" s="6" t="n">
@@ -3340,7 +3346,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -3354,11 +3360,11 @@
       <c r="D46" s="6" t="inlineStr"/>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F46" s="8" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3380,10 +3386,14 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="L46" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="L46" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M46" s="6" t="inlineStr"/>
       <c r="N46" s="6" t="inlineStr">
         <is>
@@ -3395,25 +3405,25 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>28</v>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>32</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3421,7 +3431,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3430,23 +3440,23 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3454,25 +3464,25 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46107</v>
+        <v>46100</v>
       </c>
       <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F48" s="14" t="n">
-        <v>24</v>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="n">
+        <v>34</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3494,18 +3504,18 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, running, exclusive</t>
         </is>
       </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3513,27 +3523,25 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="7" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F49" s="8" t="n">
-        <v>16</v>
+      <c r="F49" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3550,23 +3558,19 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L49" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="L49" s="12" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3574,26 +3578,24 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B50" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B50" s="5" t="inlineStr"/>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
-      <c r="E50" s="7" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F50" s="8" t="n">
+      <c r="F50" s="14" t="n">
         <v>12</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
@@ -3616,14 +3618,14 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Nike Ja 3 "At Dawn"</t>
         </is>
       </c>
       <c r="L50" s="12" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -3631,27 +3633,25 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B51" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46102</v>
+      </c>
+      <c r="B51" s="5" t="inlineStr"/>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
@@ -3668,23 +3668,23 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M51" s="6" t="inlineStr"/>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -3692,27 +3692,25 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B52" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46102</v>
+      </c>
+      <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F52" s="8" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3720,7 +3718,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3729,34 +3727,392 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P52" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q52" s="12" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B53" s="5" t="inlineStr"/>
+      <c r="C53" s="5" t="inlineStr"/>
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I53" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K53" s="12" t="inlineStr">
+        <is>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr"/>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+        </is>
+      </c>
+      <c r="Q53" s="12" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B54" s="5" t="inlineStr"/>
+      <c r="C54" s="5" t="inlineStr"/>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F54" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I54" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K54" s="12" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr"/>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="Q54" s="12" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C55" s="5" t="inlineStr"/>
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>16</v>
+      </c>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I55" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K55" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L55" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M55" s="6" t="inlineStr"/>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
           <t>footlocker</t>
         </is>
       </c>
-      <c r="O52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P52" s="12" t="inlineStr">
+      <c r="O55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q55" s="12" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C56" s="5" t="inlineStr"/>
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F56" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I56" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K56" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr"/>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P56" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q56" s="12" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C57" s="5" t="inlineStr"/>
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H57" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K57" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M57" s="6" t="inlineStr"/>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q57" s="12" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr"/>
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G58" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K58" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L58" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M58" s="6" t="inlineStr"/>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" s="12" t="inlineStr">
         <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q52" s="12" t="inlineStr"/>
+      <c r="Q58" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3773,13 +4129,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="47" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -3831,12 +4187,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3846,7 +4202,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas DON Issue 7 "Best Of Adi"</t>
+          <t>adidas Fear Of God Athletics III</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -3854,29 +4210,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -3884,29 +4240,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 14 Retro Black and University Blue</t>
+          <t>Thug Club x Converse Chuck 70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -3914,19 +4270,19 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3936,7 +4292,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -3944,19 +4300,19 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3966,7 +4322,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jordan x Teyana Taylor Apparel Collection</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -3974,7 +4330,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
@@ -3986,7 +4342,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3996,7 +4352,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -4004,67 +4360,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16T08:00:07Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-16T08:00:07Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-16T08:00:07Z</t>
+          <t>2026-03-16T19:37:34Z</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R50"/>
+  <dimension ref="A1:R56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4203,7 +4499,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4218,15 +4514,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Shoe</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>adidas Fear Of God Athletics III</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
@@ -4243,13 +4543,13 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+          <t>https://sneakernews.com/2026/03/02/adidas-fear-of-god-athletics-iii-kj5967</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Q2" t="n">
         <v>50</v>
@@ -4258,14 +4558,14 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4280,19 +4580,15 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
@@ -4309,16 +4605,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>https://sneakernews.com/2025/10/10/jacquemus-nike-moon-shoe-spring-2026</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/2606b3ba58d54a083c894b52edcd3cad_1773072526.webp</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
@@ -4331,7 +4631,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4346,28 +4646,28 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>lifestyle</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -4375,13 +4675,13 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="Q4" t="n">
         <v>50</v>
@@ -4390,14 +4690,14 @@
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="B5" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4412,24 +4712,28 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>hot-model, skateboarding</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4437,29 +4741,29 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q5" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4474,17 +4778,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Converse x Anonymous Club Chuck 70</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>lifestyle</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -4503,13 +4807,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -4518,14 +4822,14 @@
     </row>
     <row r="7">
       <c r="A7" s="15" t="n">
-        <v>46099</v>
+        <v>46098</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4540,32 +4844,28 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Thug Club x Converse Chuck 70</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>lifestyle</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4573,16 +4873,16 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>javascript:void(0)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="Q7" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -4595,7 +4895,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4610,24 +4910,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4643,13 +4935,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -4661,11 +4953,11 @@
         <v>46099</v>
       </c>
       <c r="B9" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4685,23 +4977,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>retro, kids</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -4709,16 +5001,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Q9" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
@@ -4731,7 +5023,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4751,15 +5043,19 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4775,13 +5071,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -4797,7 +5093,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4812,20 +5108,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4841,13 +5141,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -4878,15 +5178,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>retro, kids</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -4903,13 +5207,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -4925,7 +5229,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4940,24 +5244,20 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4973,13 +5273,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -5010,15 +5310,19 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
@@ -5035,13 +5339,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -5057,7 +5361,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5072,19 +5376,15 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
@@ -5101,13 +5401,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5123,7 +5423,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5143,15 +5443,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>running</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5167,13 +5471,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5189,7 +5493,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5209,14 +5513,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -5233,13 +5533,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -5255,7 +5555,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5275,10 +5575,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -5295,13 +5599,13 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q18" t="n">
         <v>59</v>
@@ -5337,10 +5641,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -5357,7 +5665,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -5379,7 +5687,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -5399,10 +5707,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -5419,13 +5731,13 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q20" t="n">
         <v>59</v>
@@ -5461,14 +5773,10 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -5485,7 +5793,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -5507,7 +5815,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5527,14 +5835,10 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -5551,13 +5855,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -5573,7 +5877,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5593,14 +5897,10 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
@@ -5617,13 +5917,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -5639,7 +5939,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5659,12 +5959,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -5683,13 +5983,13 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q24" t="n">
         <v>59</v>
@@ -5725,12 +6025,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -5749,7 +6049,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -5771,7 +6071,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5791,12 +6091,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -5815,13 +6115,13 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q26" t="n">
         <v>59</v>
@@ -5833,11 +6133,11 @@
         <v>46099</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5857,23 +6157,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -5881,16 +6181,16 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q27" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
@@ -5903,7 +6203,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5918,17 +6218,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -5947,13 +6247,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -5969,7 +6269,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5984,15 +6284,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -6009,13 +6313,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -6046,12 +6350,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6075,13 +6379,13 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q30" t="n">
         <v>59</v>
@@ -6093,7 +6397,7 @@
         <v>46099</v>
       </c>
       <c r="B31" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6112,24 +6416,28 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -6137,13 +6445,17 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/4a1c66575467445342b9085cc4510900_1772681368.webp</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="Q31" t="n">
         <v>59</v>
@@ -6174,15 +6486,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -6199,13 +6515,13 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
         <v>59</v>
@@ -6236,12 +6552,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -6261,13 +6577,13 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q33" t="n">
         <v>59</v>
@@ -6298,15 +6614,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -6323,13 +6643,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -6365,7 +6685,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -6385,7 +6705,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -6427,7 +6747,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
+          <t>Launched</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6447,7 +6767,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -6489,7 +6809,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
+          <t>Order Status</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6509,7 +6829,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -6551,7 +6871,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Upcoming</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6571,7 +6891,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -6608,24 +6928,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6641,13 +6953,13 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
         <v>59</v>
@@ -6656,14 +6968,14 @@
     </row>
     <row r="40">
       <c r="A40" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6678,28 +6990,24 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L40" t="n">
@@ -6707,29 +7015,29 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6744,28 +7052,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L41" t="n">
@@ -6773,29 +7077,29 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6810,28 +7114,24 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>hot-model, running, exclusive</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -6839,25 +7139,25 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="15" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6876,24 +7176,32 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L43" t="n">
@@ -6901,17 +7209,13 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q43" t="n">
         <v>59</v>
@@ -6927,7 +7231,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6947,10 +7251,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Fragment Design x Nike Book 2</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
@@ -6967,17 +7275,17 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/89230f46018b76e4f9b802663c124080_1769803648.webp</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="Q44" t="n">
         <v>59</v>
@@ -6986,7 +7294,7 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B45" t="n">
         <v>0</v>
@@ -7008,28 +7316,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7037,22 +7345,26 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/63594afa8c9c063216f1d0e1bcac4b37_1773326960.webp</t>
+        </is>
+      </c>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46107</v>
+        <v>46100</v>
       </c>
       <c r="B46" t="n">
         <v>0</v>
@@ -7079,23 +7391,23 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, running, exclusive</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7103,13 +7415,13 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="Q46" t="n">
         <v>50</v>
@@ -7118,10 +7430,10 @@
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B47" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -7140,28 +7452,24 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7169,13 +7477,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
+        </is>
+      </c>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q47" t="n">
         <v>59</v>
@@ -7184,10 +7496,10 @@
     </row>
     <row r="48">
       <c r="A48" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B48" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7211,19 +7523,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+          <t>Nike Ja 3 "At Dawn"</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7231,10 +7543,14 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
         <v>12</v>
@@ -7246,14 +7562,14 @@
     </row>
     <row r="49">
       <c r="A49" s="15" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="B49" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7268,28 +7584,28 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -7297,29 +7613,29 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q49" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46113</v>
+        <v>46102</v>
       </c>
       <c r="B50" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7334,28 +7650,28 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Shoes Air Jordan 14 Retro</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7363,18 +7679,410 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>50</v>
+      </c>
+      <c r="R50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="15" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>50</v>
+      </c>
+      <c r="R51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>50</v>
+      </c>
+      <c r="R52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B53" t="n">
+        <v>130</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>59</v>
+      </c>
+      <c r="R53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B54" t="n">
+        <v>130</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>59</v>
+      </c>
+      <c r="R54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B55" t="n">
+        <v>130</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
         <v>7</v>
       </c>
-      <c r="Q50" t="n">
+      <c r="Q55" t="n">
         <v>59</v>
       </c>
-      <c r="R50" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B56" t="n">
+        <v>130</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L56" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>59</v>
+      </c>
+      <c r="R56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7519,8 +8227,8 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="E4" s="13" t="n"/>
+      <c r="F4" s="14" t="n"/>
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="11" t="n"/>
@@ -7567,7 +8275,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  49 releases</t>
+          <t>Next 35 Days  ·  55 releases</t>
         </is>
       </c>
     </row>
@@ -7585,7 +8293,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -7646,7 +8354,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$201</t>
+          <t>$202</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -7703,7 +8411,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -7711,7 +8419,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -7721,7 +8429,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -7765,7 +8473,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -7781,7 +8489,7 @@
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
@@ -7801,7 +8509,7 @@
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>███████</t>
+          <t>██████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -7809,7 +8517,7 @@
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="38" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B25" s="39" t="n">
@@ -7817,7 +8525,7 @@
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
-          <t>███</t>
+          <t>██</t>
         </is>
       </c>
       <c r="D25" s="21" t="n"/>
@@ -7825,7 +8533,7 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B26" s="39" t="n">
@@ -7833,7 +8541,7 @@
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
-          <t>███</t>
+          <t>██</t>
         </is>
       </c>
       <c r="D26" s="21" t="n"/>
@@ -7841,11 +8549,11 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B27" s="39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -7857,15 +8565,15 @@
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="38" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B28" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>█</t>
+          <t>██</t>
         </is>
       </c>
       <c r="D28" s="21" t="n"/>
@@ -7877,11 +8585,11 @@
         </is>
       </c>
       <c r="B29" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>█</t>
+          <t>██</t>
         </is>
       </c>
       <c r="D29" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -53,10 +53,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
     <font>
-      <color rgb="00FFC000"/>
+      <color rgb="0000E676"/>
     </font>
     <font>
       <b val="1"/>
@@ -67,10 +67,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
-      <color rgb="0000E676"/>
+      <color rgb="00FFC000"/>
     </font>
     <font>
       <b val="1"/>
@@ -308,7 +308,7 @@
     <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -320,7 +320,7 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -855,18 +855,20 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C4" s="5" t="inlineStr"/>
       <c r="D4" s="6" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -874,7 +876,7 @@
         </is>
       </c>
       <c r="H4" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
@@ -888,18 +890,14 @@
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
-        </is>
-      </c>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr"/>
       <c r="M4" s="6" t="inlineStr"/>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O4" s="6" t="n">
@@ -907,25 +905,25 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n">
-        <v>24</v>
+      <c r="E5" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -947,18 +945,18 @@
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -966,25 +964,27 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -1001,23 +1001,27 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="inlineStr"/>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1025,25 +1029,27 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46098</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
+        <v>46099</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1051,7 +1057,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1060,23 +1066,27 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1084,7 +1094,7 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>javascript:void(0)</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
@@ -1100,11 +1110,11 @@
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1121,16 +1131,24 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="L8" s="12" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="inlineStr">
+        <is>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1141,7 +1159,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1150,16 +1168,18 @@
       <c r="A9" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F9" s="8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1167,7 +1187,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1181,18 +1201,18 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1200,7 +1220,7 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
@@ -1216,11 +1236,11 @@
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1242,19 +1262,15 @@
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr"/>
       <c r="N10" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1265,7 +1281,7 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
@@ -1281,11 +1297,11 @@
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1302,24 +1318,20 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1330,7 +1342,7 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
@@ -1344,13 +1356,13 @@
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F12" s="14" t="n">
-        <v>16</v>
+      <c r="F12" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1367,19 +1379,15 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="L12" s="12" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
@@ -1391,7 +1399,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1407,11 +1415,11 @@
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1428,20 +1436,24 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L13" s="12" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1452,7 +1464,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1468,11 +1480,11 @@
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1489,20 +1501,24 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="inlineStr"/>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1513,7 +1529,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1527,13 +1543,13 @@
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F15" s="14" t="n">
-        <v>7</v>
+      <c r="F15" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1550,12 +1566,12 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr"/>
@@ -1570,7 +1586,7 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
@@ -1584,13 +1600,13 @@
       </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>22</v>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1612,19 +1628,15 @@
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1635,7 +1647,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
@@ -1651,11 +1663,11 @@
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="G17" s="9" t="inlineStr">
         <is>
@@ -1677,19 +1689,15 @@
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr"/>
       <c r="N17" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -1700,7 +1708,7 @@
       </c>
       <c r="P17" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="Q17" s="12" t="inlineStr"/>
@@ -1716,11 +1724,11 @@
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
@@ -1742,10 +1750,14 @@
       </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L18" s="12" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="inlineStr"/>
       <c r="N18" s="6" t="inlineStr">
         <is>
@@ -1757,7 +1769,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="Q18" s="12" t="inlineStr"/>
@@ -1773,11 +1785,11 @@
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G19" s="9" t="inlineStr">
         <is>
@@ -1799,14 +1811,10 @@
       </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="L19" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr"/>
       <c r="N19" s="6" t="inlineStr">
         <is>
@@ -1818,7 +1826,7 @@
       </c>
       <c r="P19" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="Q19" s="12" t="inlineStr"/>
@@ -1832,12 +1840,12 @@
       </c>
       <c r="C20" s="5" t="inlineStr"/>
       <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="8" t="n">
         <v>12</v>
       </c>
       <c r="G20" s="9" t="inlineStr">
@@ -1860,14 +1868,10 @@
       </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="L20" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr"/>
       <c r="N20" s="6" t="inlineStr">
         <is>
@@ -1879,7 +1883,7 @@
       </c>
       <c r="P20" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="Q20" s="12" t="inlineStr"/>
@@ -1895,11 +1899,11 @@
       <c r="D21" s="6" t="inlineStr"/>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
@@ -1921,14 +1925,10 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="L21" s="12" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr"/>
       <c r="N21" s="6" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="P21" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="Q21" s="12" t="inlineStr"/>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr"/>
       <c r="D22" s="6" t="inlineStr"/>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F22" s="14" t="n">
+      <c r="F22" s="8" t="n">
         <v>12</v>
       </c>
       <c r="G22" s="9" t="inlineStr">
@@ -1982,10 +1982,14 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="L22" s="12" t="inlineStr"/>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M22" s="6" t="inlineStr"/>
       <c r="N22" s="6" t="inlineStr">
         <is>
@@ -1997,7 +2001,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="Q22" s="12" t="inlineStr"/>
@@ -2013,11 +2017,11 @@
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G23" s="9" t="inlineStr">
         <is>
@@ -2039,10 +2043,14 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="L23" s="12" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L23" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M23" s="6" t="inlineStr"/>
       <c r="N23" s="6" t="inlineStr">
         <is>
@@ -2054,7 +2062,7 @@
       </c>
       <c r="P23" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="Q23" s="12" t="inlineStr"/>
@@ -2070,11 +2078,11 @@
       <c r="D24" s="6" t="inlineStr"/>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
@@ -2096,10 +2104,14 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="L24" s="12" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="L24" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M24" s="6" t="inlineStr"/>
       <c r="N24" s="6" t="inlineStr">
         <is>
@@ -2111,7 +2123,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="Q24" s="12" t="inlineStr"/>
@@ -2127,11 +2139,11 @@
       <c r="D25" s="6" t="inlineStr"/>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F25" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G25" s="9" t="inlineStr">
         <is>
@@ -2153,12 +2165,12 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L25" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M25" s="6" t="inlineStr"/>
@@ -2172,7 +2184,7 @@
       </c>
       <c r="P25" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="Q25" s="12" t="inlineStr"/>
@@ -2186,12 +2198,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr"/>
       <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="n">
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F26" s="14" t="n">
         <v>24</v>
       </c>
       <c r="G26" s="9" t="inlineStr">
@@ -2214,7 +2226,7 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L26" s="12" t="inlineStr">
@@ -2233,7 +2245,7 @@
       </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q26" s="12" t="inlineStr"/>
@@ -2247,12 +2259,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr"/>
       <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F27" s="14" t="n">
         <v>24</v>
       </c>
       <c r="G27" s="9" t="inlineStr">
@@ -2275,12 +2287,12 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L27" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M27" s="6" t="inlineStr"/>
@@ -2294,7 +2306,7 @@
       </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q27" s="12" t="inlineStr"/>
@@ -2310,11 +2322,11 @@
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F28" s="8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G28" s="9" t="inlineStr">
         <is>
@@ -2336,12 +2348,12 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="L28" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M28" s="6" t="inlineStr"/>
@@ -2355,7 +2367,7 @@
       </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q28" s="12" t="inlineStr"/>
@@ -2364,18 +2376,16 @@
       <c r="A29" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>210</v>
-      </c>
+      <c r="B29" s="5" t="inlineStr"/>
       <c r="C29" s="5" t="inlineStr"/>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F29" s="8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G29" s="9" t="inlineStr">
         <is>
@@ -2383,7 +2393,7 @@
         </is>
       </c>
       <c r="H29" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
@@ -2397,18 +2407,18 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M29" s="6" t="inlineStr"/>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O29" s="6" t="n">
@@ -2416,7 +2426,7 @@
       </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="Q29" s="12" t="inlineStr"/>
@@ -2432,11 +2442,11 @@
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F30" s="8" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G30" s="9" t="inlineStr">
         <is>
@@ -2453,17 +2463,17 @@
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L30" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M30" s="6" t="inlineStr"/>
@@ -2477,7 +2487,7 @@
       </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="Q30" s="12" t="inlineStr"/>
@@ -2491,13 +2501,13 @@
       </c>
       <c r="C31" s="5" t="inlineStr"/>
       <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F31" s="14" t="n">
-        <v>12</v>
+      <c r="F31" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G31" s="9" t="inlineStr">
         <is>
@@ -2514,19 +2524,15 @@
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr"/>
       <c r="N31" s="6" t="inlineStr">
         <is>
@@ -2538,7 +2544,7 @@
       </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q31" s="12" t="inlineStr"/>
@@ -2547,16 +2553,18 @@
       <c r="A32" s="4" t="n">
         <v>46099</v>
       </c>
-      <c r="B32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="n">
+        <v>210</v>
+      </c>
       <c r="C32" s="5" t="inlineStr"/>
       <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F32" s="14" t="n">
-        <v>12</v>
+      <c r="F32" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
@@ -2564,7 +2572,7 @@
         </is>
       </c>
       <c r="H32" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
@@ -2573,23 +2581,19 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr"/>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O32" s="6" t="n">
@@ -2597,7 +2601,7 @@
       </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="Q32" s="12" t="inlineStr"/>
@@ -2611,12 +2615,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr"/>
       <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="13" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G33" s="9" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="L33" s="12" t="inlineStr">
@@ -2658,7 +2662,7 @@
       </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="Q33" s="12" t="inlineStr"/>
@@ -2672,12 +2676,12 @@
       </c>
       <c r="C34" s="5" t="inlineStr"/>
       <c r="D34" s="6" t="inlineStr"/>
-      <c r="E34" s="13" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="8" t="n">
         <v>7</v>
       </c>
       <c r="G34" s="9" t="inlineStr">
@@ -2695,15 +2699,19 @@
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="L34" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="L34" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M34" s="6" t="inlineStr"/>
       <c r="N34" s="6" t="inlineStr">
         <is>
@@ -2715,7 +2723,7 @@
       </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="Q34" s="12" t="inlineStr"/>
@@ -2729,13 +2737,13 @@
       </c>
       <c r="C35" s="5" t="inlineStr"/>
       <c r="D35" s="6" t="inlineStr"/>
-      <c r="E35" s="13" t="inlineStr">
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F35" s="14" t="n">
-        <v>7</v>
+      <c r="F35" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G35" s="9" t="inlineStr">
         <is>
@@ -2752,12 +2760,12 @@
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="L35" s="12" t="inlineStr"/>
@@ -2772,7 +2780,7 @@
       </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="Q35" s="12" t="inlineStr"/>
@@ -2786,13 +2794,13 @@
       </c>
       <c r="C36" s="5" t="inlineStr"/>
       <c r="D36" s="6" t="inlineStr"/>
-      <c r="E36" s="13" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F36" s="14" t="n">
-        <v>7</v>
+      <c r="F36" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G36" s="9" t="inlineStr">
         <is>
@@ -2809,19 +2817,15 @@
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="L36" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L36" s="12" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr"/>
       <c r="N36" s="6" t="inlineStr">
         <is>
@@ -2833,7 +2837,7 @@
       </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="Q36" s="12" t="inlineStr"/>
@@ -2847,13 +2851,13 @@
       </c>
       <c r="C37" s="5" t="inlineStr"/>
       <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="13" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F37" s="14" t="n">
-        <v>7</v>
+      <c r="F37" s="8" t="n">
+        <v>3</v>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
@@ -2870,19 +2874,15 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>Saucony</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr"/>
       <c r="N37" s="6" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="Q37" s="12" t="inlineStr"/>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="C38" s="5" t="inlineStr"/>
       <c r="D38" s="6" t="inlineStr"/>
-      <c r="E38" s="13" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F38" s="14" t="n">
+      <c r="F38" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G38" s="9" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr"/>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="Q38" s="12" t="inlineStr"/>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr"/>
       <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="13" t="inlineStr">
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F39" s="14" t="n">
+      <c r="F39" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G39" s="9" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr"/>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="Q39" s="12" t="inlineStr"/>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr"/>
       <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="13" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G40" s="9" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr"/>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="Q40" s="12" t="inlineStr"/>
@@ -3079,12 +3079,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr"/>
       <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="13" t="inlineStr">
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F41" s="14" t="n">
+      <c r="F41" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G41" s="9" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="L41" s="12" t="inlineStr"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="Q41" s="12" t="inlineStr"/>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr"/>
       <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="13" t="inlineStr">
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F42" s="14" t="n">
+      <c r="F42" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G42" s="9" t="inlineStr">
@@ -3164,10 +3164,14 @@
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="L42" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="L42" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M42" s="6" t="inlineStr"/>
       <c r="N42" s="6" t="inlineStr">
         <is>
@@ -3179,7 +3183,7 @@
       </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="Q42" s="12" t="inlineStr"/>
@@ -3193,12 +3197,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr"/>
       <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="13" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F43" s="14" t="n">
+      <c r="F43" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G43" s="9" t="inlineStr">
@@ -3221,10 +3225,14 @@
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="L43" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+        </is>
+      </c>
+      <c r="L43" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M43" s="6" t="inlineStr"/>
       <c r="N43" s="6" t="inlineStr">
         <is>
@@ -3236,7 +3244,7 @@
       </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="Q43" s="12" t="inlineStr"/>
@@ -3250,12 +3258,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr"/>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="13" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F44" s="14" t="n">
+      <c r="F44" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G44" s="9" t="inlineStr">
@@ -3278,10 +3286,14 @@
       </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M44" s="6" t="inlineStr"/>
       <c r="N44" s="6" t="inlineStr">
         <is>
@@ -3293,7 +3305,7 @@
       </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
         </is>
       </c>
       <c r="Q44" s="12" t="inlineStr"/>
@@ -3307,12 +3319,12 @@
       </c>
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="6" t="inlineStr"/>
-      <c r="E45" s="13" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F45" s="14" t="n">
+      <c r="F45" s="8" t="n">
         <v>3</v>
       </c>
       <c r="G45" s="9" t="inlineStr">
@@ -3335,14 +3347,10 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr"/>
       <c r="N45" s="6" t="inlineStr">
         <is>
@@ -3354,7 +3362,7 @@
       </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="Q45" s="12" t="inlineStr"/>
@@ -3368,13 +3376,13 @@
       </c>
       <c r="C46" s="5" t="inlineStr"/>
       <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="13" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F46" s="14" t="n">
-        <v>3</v>
+      <c r="F46" s="8" t="n">
+        <v>17</v>
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
@@ -3391,20 +3399,24 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -3415,27 +3427,25 @@
       </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="Q46" s="12" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B47" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr"/>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
       <c r="E47" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3443,7 +3453,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3452,23 +3462,23 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3476,27 +3486,25 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B48" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B48" s="5" t="inlineStr"/>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3504,7 +3512,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3513,19 +3521,23 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="L48" s="12" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="M48" s="6" t="inlineStr"/>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3533,27 +3545,25 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
-        <v>46099</v>
-      </c>
-      <c r="B49" s="5" t="n">
-        <v>210</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B49" s="5" t="inlineStr"/>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
       <c r="E49" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3561,7 +3571,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3570,27 +3580,23 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="M49" s="6" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3598,7 +3604,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -3612,11 +3618,11 @@
       <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3624,7 +3630,7 @@
         </is>
       </c>
       <c r="H50" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
@@ -3638,14 +3644,10 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
@@ -3657,7 +3659,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -3671,11 +3673,11 @@
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3683,7 +3685,7 @@
         </is>
       </c>
       <c r="H51" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
@@ -3697,14 +3699,10 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="L51" s="12" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
       <c r="N51" s="6" t="inlineStr">
         <is>
@@ -3716,25 +3714,25 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B52" s="5" t="inlineStr"/>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F52" s="8" t="n">
-        <v>34</v>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F52" s="14" t="n">
+        <v>28</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3751,23 +3749,23 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -3775,25 +3773,25 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B53" s="5" t="inlineStr"/>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr"/>
       <c r="E53" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3801,7 +3799,7 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
@@ -3810,19 +3808,23 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="L53" s="12" t="inlineStr"/>
+          <t>Shoes Air Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L53" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -3830,25 +3832,25 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="5" t="inlineStr"/>
       <c r="D54" s="6" t="inlineStr"/>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3856,7 +3858,7 @@
         </is>
       </c>
       <c r="H54" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
@@ -3870,14 +3872,18 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="L54" s="12" t="inlineStr"/>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="L54" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O54" s="6" t="n">
@@ -3885,25 +3891,25 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="B55" s="5" t="inlineStr"/>
       <c r="C55" s="5" t="inlineStr"/>
       <c r="D55" s="6" t="inlineStr"/>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F55" s="8" t="n">
-        <v>28</v>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F55" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3920,17 +3926,17 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
@@ -3944,25 +3950,27 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B56" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B56" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C56" s="5" t="inlineStr"/>
       <c r="D56" s="6" t="inlineStr"/>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
@@ -3970,7 +3978,7 @@
         </is>
       </c>
       <c r="H56" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
@@ -3984,18 +3992,18 @@
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L56" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M56" s="6" t="inlineStr"/>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O56" s="6" t="n">
@@ -4003,25 +4011,27 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46104</v>
-      </c>
-      <c r="B57" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B57" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="6" t="inlineStr"/>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F57" s="8" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
@@ -4029,7 +4039,7 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
@@ -4043,18 +4053,14 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr"/>
       <c r="M57" s="6" t="inlineStr"/>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O57" s="6" t="n">
@@ -4062,25 +4068,27 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B58" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B58" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C58" s="5" t="inlineStr"/>
       <c r="D58" s="6" t="inlineStr"/>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F58" s="8" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
@@ -4088,7 +4096,7 @@
         </is>
       </c>
       <c r="H58" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
@@ -4097,23 +4105,23 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr"/>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O58" s="6" t="n">
@@ -4121,7 +4129,7 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q58" s="12" t="inlineStr"/>
@@ -4135,13 +4143,13 @@
       </c>
       <c r="C59" s="5" t="inlineStr"/>
       <c r="D59" s="6" t="inlineStr"/>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="F59" s="14" t="n">
-        <v>16</v>
+      <c r="F59" s="8" t="n">
+        <v>7</v>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
@@ -4158,17 +4166,17 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>women</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
@@ -4182,189 +4190,10 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q59" s="12" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B60" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C60" s="5" t="inlineStr"/>
-      <c r="D60" s="6" t="inlineStr"/>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F60" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="G60" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H60" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I60" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K60" s="12" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L60" s="12" t="inlineStr"/>
-      <c r="M60" s="6" t="inlineStr"/>
-      <c r="N60" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P60" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="Q60" s="12" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B61" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C61" s="5" t="inlineStr"/>
-      <c r="D61" s="6" t="inlineStr"/>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F61" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G61" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I61" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J61" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K61" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L61" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O61" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P61" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="Q61" s="12" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B62" s="5" t="n">
-        <v>130</v>
-      </c>
-      <c r="C62" s="5" t="inlineStr"/>
-      <c r="D62" s="6" t="inlineStr"/>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F62" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="G62" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H62" s="10" t="n">
-        <v>59</v>
-      </c>
-      <c r="I62" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J62" s="6" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="L62" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="O62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P62" s="12" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="Q62" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4381,12 +4210,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -4439,22 +4268,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>adidas HyperBOOST Edge</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -4462,7 +4291,127 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-17T19:39:04Z</t>
+          <t>2026-03-18T07:39:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Converse x Anonymous Club Chuck 70</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:39:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:39:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Converse</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Thug Club x Converse Chuck 70</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:39:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-03-18T07:39:06Z</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4594,14 +4543,14 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -4621,23 +4570,19 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>exclusive</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -4645,22 +4590,22 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/16/adidas-hyperboost-edge-running-shoes/</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -4687,23 +4632,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -4711,13 +4656,13 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/dashawn-jordan-nike-sb-dunk-low-copperhead-ib6208-200/</t>
+          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -4726,14 +4671,14 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4748,28 +4693,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -4777,29 +4726,29 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/converse-x-anonymous-club-chuck-a19255c-020</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -4814,28 +4763,32 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>lifestyle</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>hot-model, retro, exclusive</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -4843,16 +4796,16 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>javascript:void(0)</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R5" t="inlineStr"/>
     </row>
@@ -4865,7 +4818,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4880,16 +4833,24 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4905,13 +4866,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="Q6" t="n">
         <v>59</v>
@@ -4923,11 +4884,11 @@
         <v>46099</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4947,23 +4908,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L7" t="n">
@@ -4971,16 +4932,16 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R7" t="inlineStr"/>
     </row>
@@ -4993,7 +4954,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5013,19 +4974,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hot-model, retro, exclusive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>retro, kids</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5041,13 +4998,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/F4391100.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="Q8" t="n">
         <v>59</v>
@@ -5063,7 +5020,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5078,24 +5035,20 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>retro, exclusive, kids</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5111,13 +5064,13 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="Q9" t="n">
         <v>59</v>
@@ -5148,19 +5101,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
@@ -5177,13 +5126,13 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q10" t="n">
         <v>59</v>
@@ -5199,7 +5148,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5214,20 +5163,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>retro, kids</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5243,13 +5196,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -5265,7 +5218,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5280,20 +5233,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5309,13 +5266,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -5346,12 +5303,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -5371,13 +5328,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
         <v>59</v>
@@ -5413,19 +5370,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, women</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5441,13 +5394,13 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
         <v>59</v>
@@ -5463,7 +5416,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5483,19 +5436,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>hot-model, basketball, exclusive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>running</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -5511,13 +5460,13 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="Q15" t="n">
         <v>59</v>
@@ -5533,7 +5482,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5553,10 +5502,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
@@ -5573,13 +5526,13 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="Q16" t="n">
         <v>59</v>
@@ -5595,7 +5548,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -5615,14 +5568,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>hot-model, running, women</t>
-        </is>
-      </c>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
@@ -5639,13 +5588,13 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
         <v>59</v>
@@ -5681,14 +5630,10 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
@@ -5705,7 +5650,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -5727,7 +5672,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5747,14 +5692,10 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>running, exclusive</t>
-        </is>
-      </c>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
@@ -5771,13 +5712,13 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q19" t="n">
         <v>59</v>
@@ -5813,10 +5754,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
@@ -5833,7 +5778,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -5855,7 +5800,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -5875,10 +5820,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
@@ -5895,13 +5844,13 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/I8116600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q21" t="n">
         <v>59</v>
@@ -5917,7 +5866,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -5937,10 +5886,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
@@ -5957,13 +5910,13 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
         <v>59</v>
@@ -5979,7 +5932,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -5999,12 +5952,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -6023,13 +5976,13 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q23" t="n">
         <v>59</v>
@@ -6065,7 +6018,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6089,7 +6042,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -6131,12 +6084,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -6155,7 +6108,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
@@ -6177,7 +6130,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -6197,12 +6150,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -6221,13 +6174,13 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q26" t="n">
         <v>59</v>
@@ -6239,11 +6192,11 @@
         <v>46099</v>
       </c>
       <c r="B27" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -6263,23 +6216,23 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
+          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -6287,16 +6240,16 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
+          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q27" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
@@ -6309,7 +6262,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -6324,17 +6277,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>hot-model, basketball, kids</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -6353,13 +6306,13 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="n">
         <v>59</v>
@@ -6390,19 +6343,15 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
@@ -6419,13 +6368,13 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q29" t="n">
         <v>59</v>
@@ -6437,7 +6386,7 @@
         <v>46099</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6456,28 +6405,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike Zoom GT Cut 4 "Think Pink"</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>running</t>
-        </is>
-      </c>
+          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -6485,16 +6430,16 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/12/nike-zoom-gt-cut-4-think-pink-kay-yow-io8116-600</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q30" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R30" t="inlineStr"/>
     </row>
@@ -6527,7 +6472,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6551,7 +6496,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -6588,15 +6533,19 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
@@ -6613,7 +6562,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -6650,12 +6599,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>PUMA MB 05 World MENS • TEAL/RED</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -6675,13 +6624,13 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>59</v>
@@ -6712,19 +6661,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
@@ -6741,13 +6686,13 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q34" t="n">
         <v>59</v>
@@ -6778,19 +6723,15 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Saucony</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
@@ -6807,13 +6748,13 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+          <t>https://www.footlocker.com/order/search</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
         <v>59</v>
@@ -6849,7 +6790,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Contact Us</t>
+          <t>Returns-Exchanges</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -6869,7 +6810,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
@@ -6911,7 +6852,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Launched</t>
+          <t>Shipping Info</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
@@ -6931,7 +6872,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/launched</t>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
@@ -6973,7 +6914,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Order Status</t>
+          <t>Skip To Main</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -6993,7 +6934,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/order/search</t>
+          <t>#main</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -7035,7 +6976,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Returns-Exchanges</t>
+          <t>Store Pickup</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -7055,7 +6996,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+          <t>https://www.footlocker.com/help/store-pickup</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
@@ -7097,10 +7038,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
@@ -7117,7 +7062,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
@@ -7159,10 +7104,14 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
@@ -7179,7 +7128,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>#main</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -7221,10 +7170,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
@@ -7241,7 +7194,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/help/store-pickup</t>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
@@ -7283,14 +7236,10 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
@@ -7307,7 +7256,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+          <t>https://www.footlocker.com/release-calendar</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -7344,20 +7293,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>kids</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -7373,13 +7326,13 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="Q44" t="n">
         <v>59</v>
@@ -7388,14 +7341,14 @@
     </row>
     <row r="45">
       <c r="A45" s="15" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B45" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7410,28 +7363,28 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7439,29 +7392,29 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q45" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="15" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B46" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7476,24 +7429,28 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr"/>
+          <t>Fragment Design x Nike Mind 001</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7501,29 +7458,29 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="Q46" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="15" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B47" t="n">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7538,32 +7495,28 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>Nike Air Max 90 QS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>lifestyle, exclusive</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>App</t>
-        </is>
-      </c>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7571,16 +7524,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="Q47" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
@@ -7593,7 +7546,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7613,14 +7566,10 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
@@ -7637,16 +7586,20 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
+        </is>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Q48" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R48" t="inlineStr"/>
     </row>
@@ -7659,7 +7612,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7679,14 +7632,10 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
@@ -7703,22 +7652,26 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Q49" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
@@ -7740,28 +7693,28 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7769,13 +7722,13 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Q50" t="n">
         <v>50</v>
@@ -7784,14 +7737,14 @@
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7806,24 +7759,28 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Shoes Air Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7831,33 +7788,29 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
-        </is>
-      </c>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q51" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7877,19 +7830,23 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -7897,26 +7854,22 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
-        </is>
-      </c>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="Q52" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -7938,17 +7891,17 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -7967,13 +7920,13 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q53" t="n">
         <v>50</v>
@@ -7982,14 +7935,14 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46102</v>
+        <v>46113</v>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -8009,23 +7962,23 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L54" t="n">
@@ -8033,29 +7986,29 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="Q54" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46104</v>
+        <v>46113</v>
       </c>
       <c r="B55" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8075,23 +8028,19 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -8099,29 +8048,29 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="Q55" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46107</v>
+        <v>46113</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8136,28 +8085,28 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L56" t="n">
@@ -8165,16 +8114,16 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R56" t="inlineStr"/>
     </row>
@@ -8202,17 +8151,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8231,212 +8180,18 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
         <v>59</v>
       </c>
       <c r="R57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B58" t="n">
-        <v>130</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>1</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>59</v>
-      </c>
-      <c r="R58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B59" t="n">
-        <v>130</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>1</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>59</v>
-      </c>
-      <c r="R59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="15" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B60" t="n">
-        <v>130</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>footlocker</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>59</v>
-      </c>
-      <c r="R60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8581,8 +8336,8 @@
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
-      <c r="E4" s="13" t="n"/>
-      <c r="F4" s="14" t="n"/>
+      <c r="E4" s="7" t="n"/>
+      <c r="F4" s="8" t="n"/>
       <c r="G4" s="11" t="n"/>
       <c r="H4" s="6" t="n"/>
       <c r="I4" s="11" t="n"/>
@@ -8610,7 +8365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8629,7 +8384,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  59 releases</t>
+          <t>Next 35 Days  ·  56 releases</t>
         </is>
       </c>
     </row>
@@ -8647,7 +8402,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -8765,7 +8520,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -8773,7 +8528,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8783,7 +8538,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -8808,7 +8563,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -8923,11 +8678,11 @@
         </is>
       </c>
       <c r="B28" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>█</t>
         </is>
       </c>
       <c r="D28" s="21" t="n"/>
@@ -8935,34 +8690,18 @@
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="38" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Saucony</t>
         </is>
       </c>
       <c r="B29" s="39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>
-          <t>██</t>
+          <t>█</t>
         </is>
       </c>
       <c r="D29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="38" t="inlineStr">
-        <is>
-          <t>Saucony</t>
-        </is>
-      </c>
-      <c r="B30" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="40" t="inlineStr">
-        <is>
-          <t>█</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q59"/>
+  <dimension ref="A1:Q96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -3436,16 +3436,18 @@
       <c r="A47" s="4" t="n">
         <v>46100</v>
       </c>
-      <c r="B47" s="5" t="inlineStr"/>
+      <c r="B47" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C47" s="5" t="inlineStr"/>
       <c r="D47" s="6" t="inlineStr"/>
-      <c r="E47" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F47" s="14" t="n">
-        <v>32</v>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="n">
+        <v>12</v>
       </c>
       <c r="G47" s="9" t="inlineStr">
         <is>
@@ -3453,7 +3455,7 @@
         </is>
       </c>
       <c r="H47" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
@@ -3462,23 +3464,19 @@
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="L47" s="12" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="L47" s="12" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr"/>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O47" s="6" t="n">
@@ -3486,7 +3484,7 @@
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="Q47" s="12" t="inlineStr"/>
@@ -3495,7 +3493,9 @@
       <c r="A48" s="4" t="n">
         <v>46100</v>
       </c>
-      <c r="B48" s="5" t="inlineStr"/>
+      <c r="B48" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C48" s="5" t="inlineStr"/>
       <c r="D48" s="6" t="inlineStr"/>
       <c r="E48" s="13" t="inlineStr">
@@ -3504,7 +3504,7 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G48" s="9" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         </is>
       </c>
       <c r="H48" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
@@ -3521,23 +3521,27 @@
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="M48" s="6" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O48" s="6" t="n">
@@ -3545,7 +3549,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="Q48" s="12" t="inlineStr"/>
@@ -3554,16 +3558,18 @@
       <c r="A49" s="4" t="n">
         <v>46100</v>
       </c>
-      <c r="B49" s="5" t="inlineStr"/>
+      <c r="B49" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C49" s="5" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr"/>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F49" s="14" t="n">
-        <v>34</v>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F49" s="8" t="n">
+        <v>16</v>
       </c>
       <c r="G49" s="9" t="inlineStr">
         <is>
@@ -3571,7 +3577,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
@@ -3580,23 +3586,23 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O49" s="6" t="n">
@@ -3604,7 +3610,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="Q49" s="12" t="inlineStr"/>
@@ -3613,7 +3619,9 @@
       <c r="A50" s="4" t="n">
         <v>46100</v>
       </c>
-      <c r="B50" s="5" t="inlineStr"/>
+      <c r="B50" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C50" s="5" t="inlineStr"/>
       <c r="D50" s="6" t="inlineStr"/>
       <c r="E50" s="7" t="inlineStr">
@@ -3622,7 +3630,7 @@
         </is>
       </c>
       <c r="F50" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G50" s="9" t="inlineStr">
         <is>
@@ -3639,19 +3647,23 @@
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="L50" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O50" s="6" t="n">
@@ -3659,7 +3671,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q50" s="12" t="inlineStr"/>
@@ -3668,7 +3680,9 @@
       <c r="A51" s="4" t="n">
         <v>46100</v>
       </c>
-      <c r="B51" s="5" t="inlineStr"/>
+      <c r="B51" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C51" s="5" t="inlineStr"/>
       <c r="D51" s="6" t="inlineStr"/>
       <c r="E51" s="7" t="inlineStr">
@@ -3677,7 +3691,7 @@
         </is>
       </c>
       <c r="F51" s="8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G51" s="9" t="inlineStr">
         <is>
@@ -3694,19 +3708,19 @@
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="L51" s="12" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O51" s="6" t="n">
@@ -3714,16 +3728,18 @@
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q51" s="12" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B52" s="5" t="inlineStr"/>
+        <v>46100</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C52" s="5" t="inlineStr"/>
       <c r="D52" s="6" t="inlineStr"/>
       <c r="E52" s="13" t="inlineStr">
@@ -3732,7 +3748,7 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
@@ -3740,7 +3756,7 @@
         </is>
       </c>
       <c r="H52" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
@@ -3749,23 +3765,27 @@
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="L52" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="M52" s="6" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O52" s="6" t="n">
@@ -3773,16 +3793,18 @@
       </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="Q52" s="12" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
-        <v>46102</v>
-      </c>
-      <c r="B53" s="5" t="inlineStr"/>
+        <v>46100</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>135</v>
+      </c>
       <c r="C53" s="5" t="inlineStr"/>
       <c r="D53" s="6" t="inlineStr"/>
       <c r="E53" s="13" t="inlineStr">
@@ -3791,7 +3813,7 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
@@ -3799,7 +3821,7 @@
         </is>
       </c>
       <c r="H53" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
@@ -3808,23 +3830,27 @@
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="L53" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="M53" s="6" t="inlineStr"/>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O53" s="6" t="n">
@@ -3832,14 +3858,14 @@
       </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="Q53" s="12" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="B54" s="5" t="inlineStr"/>
       <c r="C54" s="5" t="inlineStr"/>
@@ -3850,7 +3876,7 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
@@ -3872,18 +3898,18 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="L54" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O54" s="6" t="n">
@@ -3891,14 +3917,14 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="Q54" s="12" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
-        <v>46107</v>
+        <v>46100</v>
       </c>
       <c r="B55" s="5" t="inlineStr"/>
       <c r="C55" s="5" t="inlineStr"/>
@@ -3909,7 +3935,7 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
@@ -3931,18 +3957,18 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="L55" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O55" s="6" t="n">
@@ -3950,17 +3976,17 @@
       </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="Q55" s="12" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C56" s="5" t="inlineStr"/>
       <c r="D56" s="6" t="inlineStr"/>
@@ -3970,7 +3996,7 @@
         </is>
       </c>
       <c r="F56" s="8" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
@@ -3987,19 +4013,15 @@
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L56" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L56" s="12" t="inlineStr"/>
       <c r="M56" s="6" t="inlineStr"/>
       <c r="N56" s="6" t="inlineStr">
         <is>
@@ -4011,27 +4033,25 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q56" s="12" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B57" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46100</v>
+      </c>
+      <c r="B57" s="5" t="inlineStr"/>
       <c r="C57" s="5" t="inlineStr"/>
       <c r="D57" s="6" t="inlineStr"/>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F57" s="8" t="n">
-        <v>12</v>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F57" s="14" t="n">
+        <v>34</v>
       </c>
       <c r="G57" s="9" t="inlineStr">
         <is>
@@ -4039,7 +4059,7 @@
         </is>
       </c>
       <c r="H57" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
@@ -4053,14 +4073,18 @@
       </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L57" s="12" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="L57" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="M57" s="6" t="inlineStr"/>
       <c r="N57" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="O57" s="6" t="n">
@@ -4068,27 +4092,27 @@
       </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="Q57" s="12" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C58" s="5" t="inlineStr"/>
       <c r="D58" s="6" t="inlineStr"/>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="n">
-        <v>7</v>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F58" s="14" t="n">
+        <v>24</v>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
@@ -4105,17 +4129,17 @@
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L58" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="M58" s="6" t="inlineStr"/>
@@ -4129,17 +4153,17 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q58" s="12" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C59" s="5" t="inlineStr"/>
       <c r="D59" s="6" t="inlineStr"/>
@@ -4149,7 +4173,7 @@
         </is>
       </c>
       <c r="F59" s="8" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G59" s="9" t="inlineStr">
         <is>
@@ -4166,17 +4190,17 @@
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="L59" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>running</t>
         </is>
       </c>
       <c r="M59" s="6" t="inlineStr"/>
@@ -4190,10 +4214,2199 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
+        </is>
+      </c>
+      <c r="Q59" s="12" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B60" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C60" s="5" t="inlineStr"/>
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F60" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="G60" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H60" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K60" s="12" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="L60" s="12" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="M60" s="6" t="inlineStr"/>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P60" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+        </is>
+      </c>
+      <c r="Q60" s="12" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B61" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C61" s="5" t="inlineStr"/>
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F61" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I61" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K61" s="12" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="L61" s="12" t="inlineStr"/>
+      <c r="M61" s="6" t="inlineStr"/>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+        </is>
+      </c>
+      <c r="Q61" s="12" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B62" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C62" s="5" t="inlineStr"/>
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F62" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H62" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I62" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K62" s="12" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="L62" s="12" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr"/>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P62" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+        </is>
+      </c>
+      <c r="Q62" s="12" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B63" s="5" t="inlineStr"/>
+      <c r="C63" s="5" t="inlineStr"/>
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F63" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H63" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I63" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K63" s="12" t="inlineStr">
+        <is>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="L63" s="12" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr"/>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>sneakernews</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P63" s="12" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="Q63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B64" s="5" t="inlineStr"/>
+      <c r="C64" s="5" t="inlineStr"/>
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F64" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G64" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H64" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I64" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K64" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr"/>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>sneakernews</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P64" s="12" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="Q64" s="12" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B65" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C65" s="5" t="inlineStr"/>
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G65" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H65" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I65" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K65" s="12" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="L65" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M65" s="6" t="inlineStr"/>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+        </is>
+      </c>
+      <c r="Q65" s="12" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B66" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C66" s="5" t="inlineStr"/>
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F66" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G66" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H66" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I66" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J66" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K66" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L66" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M66" s="6" t="inlineStr"/>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+        </is>
+      </c>
+      <c r="Q66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C67" s="5" t="inlineStr"/>
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F67" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G67" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H67" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I67" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K67" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="L67" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M67" s="6" t="inlineStr"/>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P67" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+        </is>
+      </c>
+      <c r="Q67" s="12" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B68" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C68" s="5" t="inlineStr"/>
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F68" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G68" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H68" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I68" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K68" s="12" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="L68" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr"/>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P68" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+        </is>
+      </c>
+      <c r="Q68" s="12" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B69" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C69" s="5" t="inlineStr"/>
+      <c r="D69" s="6" t="inlineStr"/>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F69" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G69" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H69" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I69" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K69" s="12" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="L69" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
+      <c r="M69" s="6" t="inlineStr"/>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+        </is>
+      </c>
+      <c r="Q69" s="12" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B70" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C70" s="5" t="inlineStr"/>
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F70" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G70" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H70" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I70" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K70" s="12" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L70" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M70" s="6" t="inlineStr"/>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+        </is>
+      </c>
+      <c r="Q70" s="12" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B71" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr"/>
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F71" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G71" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H71" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I71" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K71" s="12" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L71" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M71" s="6" t="inlineStr"/>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+        </is>
+      </c>
+      <c r="Q71" s="12" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B72" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr"/>
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G72" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I72" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K72" s="12" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L72" s="12" t="inlineStr"/>
+      <c r="M72" s="6" t="inlineStr"/>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="Q72" s="12" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B73" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C73" s="5" t="inlineStr"/>
+      <c r="D73" s="6" t="inlineStr"/>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G73" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I73" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K73" s="12" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="L73" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M73" s="6" t="inlineStr"/>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P73" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+        </is>
+      </c>
+      <c r="Q73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B74" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C74" s="5" t="inlineStr"/>
+      <c r="D74" s="6" t="inlineStr"/>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G74" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H74" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I74" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Saucony</t>
+        </is>
+      </c>
+      <c r="K74" s="12" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="L74" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr"/>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P74" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+        </is>
+      </c>
+      <c r="Q74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B75" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C75" s="5" t="inlineStr"/>
+      <c r="D75" s="6" t="inlineStr"/>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F75" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G75" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H75" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I75" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K75" s="12" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L75" s="12" t="inlineStr"/>
+      <c r="M75" s="6" t="inlineStr"/>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="Q75" s="12" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B76" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C76" s="5" t="inlineStr"/>
+      <c r="D76" s="6" t="inlineStr"/>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F76" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G76" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I76" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K76" s="12" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L76" s="12" t="inlineStr"/>
+      <c r="M76" s="6" t="inlineStr"/>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="Q76" s="12" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B77" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C77" s="5" t="inlineStr"/>
+      <c r="D77" s="6" t="inlineStr"/>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F77" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G77" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I77" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K77" s="12" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L77" s="12" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="Q77" s="12" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B78" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C78" s="5" t="inlineStr"/>
+      <c r="D78" s="6" t="inlineStr"/>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G78" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I78" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K78" s="12" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L78" s="12" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="Q78" s="12" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B79" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C79" s="5" t="inlineStr"/>
+      <c r="D79" s="6" t="inlineStr"/>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F79" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G79" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I79" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K79" s="12" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L79" s="12" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="Q79" s="12" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B80" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C80" s="5" t="inlineStr"/>
+      <c r="D80" s="6" t="inlineStr"/>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F80" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H80" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I80" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K80" s="12" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="L80" s="12" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="12" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="Q80" s="12" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B81" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C81" s="5" t="inlineStr"/>
+      <c r="D81" s="6" t="inlineStr"/>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F81" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G81" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I81" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K81" s="12" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="L81" s="12" t="inlineStr"/>
+      <c r="M81" s="6" t="inlineStr"/>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="Q81" s="12" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B82" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C82" s="5" t="inlineStr"/>
+      <c r="D82" s="6" t="inlineStr"/>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F82" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G82" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I82" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K82" s="12" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="L82" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M82" s="6" t="inlineStr"/>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+        </is>
+      </c>
+      <c r="Q82" s="12" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C83" s="5" t="inlineStr"/>
+      <c r="D83" s="6" t="inlineStr"/>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F83" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G83" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H83" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I83" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K83" s="12" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+        </is>
+      </c>
+      <c r="L83" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M83" s="6" t="inlineStr"/>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P83" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+        </is>
+      </c>
+      <c r="Q83" s="12" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B84" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C84" s="5" t="inlineStr"/>
+      <c r="D84" s="6" t="inlineStr"/>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G84" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I84" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K84" s="12" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="L84" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M84" s="6" t="inlineStr"/>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P84" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+        </is>
+      </c>
+      <c r="Q84" s="12" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B85" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C85" s="5" t="inlineStr"/>
+      <c r="D85" s="6" t="inlineStr"/>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F85" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="G85" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I85" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K85" s="12" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="L85" s="12" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P85" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="Q85" s="12" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B86" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="C86" s="5" t="inlineStr"/>
+      <c r="D86" s="6" t="inlineStr"/>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F86" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I86" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="L86" s="12" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P86" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="Q86" s="12" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="5" t="inlineStr"/>
+      <c r="D87" s="6" t="inlineStr"/>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F87" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I87" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+        </is>
+      </c>
+      <c r="L87" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="M87" s="6" t="inlineStr"/>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P87" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q87" s="12" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr"/>
+      <c r="C88" s="5" t="inlineStr"/>
+      <c r="D88" s="6" t="inlineStr"/>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F88" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I88" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>Shoes Air Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="L88" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="M88" s="6" t="inlineStr"/>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P88" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="Q88" s="12" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr"/>
+      <c r="C89" s="5" t="inlineStr"/>
+      <c r="D89" s="6" t="inlineStr"/>
+      <c r="E89" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F89" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K89" s="12" t="inlineStr">
+        <is>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="L89" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M89" s="6" t="inlineStr"/>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P89" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+        </is>
+      </c>
+      <c r="Q89" s="12" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr"/>
+      <c r="C90" s="5" t="inlineStr"/>
+      <c r="D90" s="6" t="inlineStr"/>
+      <c r="E90" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F90" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G90" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I90" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K90" s="12" t="inlineStr">
+        <is>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="L90" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="M90" s="6" t="inlineStr"/>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P90" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+        </is>
+      </c>
+      <c r="Q90" s="12" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr"/>
+      <c r="C91" s="5" t="inlineStr"/>
+      <c r="D91" s="6" t="inlineStr"/>
+      <c r="E91" s="13" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F91" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="G91" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I91" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K91" s="12" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="L91" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="M91" s="6" t="inlineStr"/>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P91" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="Q91" s="12" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr"/>
+      <c r="C92" s="5" t="inlineStr"/>
+      <c r="D92" s="6" t="inlineStr"/>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F92" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G92" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I92" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K92" s="12" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="L92" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="M92" s="6" t="inlineStr"/>
+      <c r="N92" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+        </is>
+      </c>
+      <c r="Q92" s="12" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B93" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C93" s="5" t="inlineStr"/>
+      <c r="D93" s="6" t="inlineStr"/>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F93" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="G93" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I93" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="K93" s="12" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L93" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P93" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="Q93" s="12" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B94" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C94" s="5" t="inlineStr"/>
+      <c r="D94" s="6" t="inlineStr"/>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F94" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K94" s="12" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L94" s="12" t="inlineStr"/>
+      <c r="M94" s="6" t="inlineStr"/>
+      <c r="N94" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="Q94" s="12" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B95" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C95" s="5" t="inlineStr"/>
+      <c r="D95" s="6" t="inlineStr"/>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F95" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J95" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K95" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L95" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M95" s="6" t="inlineStr"/>
+      <c r="N95" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q95" s="12" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B96" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C96" s="5" t="inlineStr"/>
+      <c r="D96" s="6" t="inlineStr"/>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F96" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="G96" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K96" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L96" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M96" s="6" t="inlineStr"/>
+      <c r="N96" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q59" s="12" t="inlineStr"/>
+      <c r="Q96" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4210,7 +6423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4268,12 +6481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4283,7 +6496,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas HyperBOOST Edge</t>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -4291,29 +6504,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-18T07:39:06Z</t>
+          <t>2026-03-18T19:30:50Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Converse x Anonymous Club Chuck 70</t>
+          <t>Contact Us</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -4321,19 +6534,19 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-18T07:39:06Z</t>
+          <t>2026-03-18T19:30:50Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4343,7 +6556,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dashawn Jordan x Nike SB Dunk Low "Diamondbacks"</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -4351,29 +6564,29 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-18T07:39:06Z</t>
+          <t>2026-03-18T19:30:50Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Thug Club x Converse Chuck 70</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -4381,7 +6594,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-18T07:39:06Z</t>
+          <t>2026-03-18T19:30:50Z</t>
         </is>
       </c>
     </row>
@@ -4393,17 +6606,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>App entry Jordan Air Jordan 1 Retro Low OG MENS • SAIL/OFF WHITE/COCONUT MILK</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -4411,7 +6624,967 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-18T07:39:06Z</t>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ASICS</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Saucony</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-03-18T19:30:50Z</t>
         </is>
       </c>
     </row>
@@ -4426,7 +7599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7344,11 +10517,11 @@
         <v>46100</v>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7363,28 +10536,24 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -7392,16 +10561,16 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
+          <t>https://www.footlocker.com/release-calendar/adidas/JQ9426.html</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R45" t="inlineStr"/>
     </row>
@@ -7410,7 +10579,7 @@
         <v>46100</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -7429,28 +10598,32 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fragment Design x Nike Mind 001</t>
+          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>collab</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>retro, exclusive, kids</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L46" t="n">
@@ -7458,16 +10631,16 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Q46" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R46" t="inlineStr"/>
     </row>
@@ -7476,11 +10649,11 @@
         <v>46100</v>
       </c>
       <c r="B47" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7495,28 +10668,28 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nike Air Max 90 QS</t>
+          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>hot-model, running, exclusive</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L47" t="n">
@@ -7524,16 +10697,16 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/12092007.html</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="Q47" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R47" t="inlineStr"/>
     </row>
@@ -7542,7 +10715,7 @@
         <v>46100</v>
       </c>
       <c r="B48" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -7561,24 +10734,28 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L48" t="n">
@@ -7586,17 +10763,13 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
         <v>59</v>
@@ -7608,7 +10781,7 @@
         <v>46100</v>
       </c>
       <c r="B49" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -7627,24 +10800,24 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nike Ja 3 "At Dawn"</t>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>sneakernews</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/release-dates/</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L49" t="n">
@@ -7652,17 +10825,13 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
-        </is>
-      </c>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
         <v>59</v>
@@ -7671,10 +10840,10 @@
     </row>
     <row r="50">
       <c r="A50" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B50" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -7693,28 +10862,32 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L50" t="n">
@@ -7722,25 +10895,25 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/nike/B6903800.html</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Q50" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="15" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B51" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -7759,28 +10932,32 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>hot-model, basketball, exclusive</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L51" t="n">
@@ -7788,22 +10965,22 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.footlocker.com/release-calendar/nike/M0557001.html</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="Q51" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="15" t="n">
-        <v>46104</v>
+        <v>46100</v>
       </c>
       <c r="B52" t="n">
         <v>0</v>
@@ -7830,23 +11007,23 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Fragment Design x Nike Book 2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -7854,13 +11031,13 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://sneakernews.com/2026/01/28/fragment-design-nike-book-2-io9950-900</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q52" t="n">
         <v>50</v>
@@ -7869,7 +11046,7 @@
     </row>
     <row r="53">
       <c r="A53" s="15" t="n">
-        <v>46107</v>
+        <v>46100</v>
       </c>
       <c r="B53" t="n">
         <v>0</v>
@@ -7896,23 +11073,23 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Fragment Design x Nike Mind 001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>collab</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L53" t="n">
@@ -7920,13 +11097,13 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://sneakernews.com/2026/03/12/fragment-design-nike-liquid-max-mind-001/</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q53" t="n">
         <v>50</v>
@@ -7935,10 +11112,10 @@
     </row>
     <row r="54">
       <c r="A54" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B54" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7957,19 +11134,15 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
@@ -7986,13 +11159,13 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q54" t="n">
         <v>59</v>
@@ -8001,14 +11174,14 @@
     </row>
     <row r="55">
       <c r="A55" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B55" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8028,19 +11201,23 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Nike Air Max 90 QS</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>hot-model, running, exclusive</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>sneakernews</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://sneakernews.com/release-dates/</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -8048,29 +11225,29 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://sneakernews.com/2026/01/09/nike-air-max-90-infrared-reflective-iu1055-100</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="Q55" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B56" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -8085,17 +11262,17 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, women</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -8114,13 +11291,13 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q56" t="n">
         <v>59</v>
@@ -8129,10 +11306,10 @@
     </row>
     <row r="57">
       <c r="A57" s="15" t="n">
-        <v>46113</v>
+        <v>46100</v>
       </c>
       <c r="B57" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -8151,17 +11328,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>running</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -8180,18 +11357,2416 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/41017550.html</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>59</v>
+      </c>
+      <c r="R57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B58" t="n">
+        <v>135</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>running, exclusive</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/R0962001.html</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>59</v>
+      </c>
+      <c r="R58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B59" t="n">
+        <v>135</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/M3074900.html</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>59</v>
+      </c>
+      <c r="R59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B60" t="n">
+        <v>135</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L60" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/41559050.html</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>59</v>
+      </c>
+      <c r="R60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Nike GT Future</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>sneakernews</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/release-dates/</t>
+        </is>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/2026/02/12/nike-gt-future-unseen-hours-iv0521-500/</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/c264dc68428eb4e5705b62d784b539d9_1772126870.webp</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>59</v>
+      </c>
+      <c r="R61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 "At Dawn"</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>sneakernews</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/release-dates/</t>
+        </is>
+      </c>
+      <c r="L62" t="n">
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>https://sneakernews.com/2026/02/18/nike-ja-3-at-dawn-iq6705-001-release-date/</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>https://s3.amazonaws.com/images.kicksfinder.com/products/thumbs/9d847ec5e59f85e83b260ce145e30a48_1772038180.webp</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>59</v>
+      </c>
+      <c r="R62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B63" t="n">
+        <v>135</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L63" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/IR216001.html</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>59</v>
+      </c>
+      <c r="R63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B64" t="n">
+        <v>135</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L64" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018600.html</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>59</v>
+      </c>
+      <c r="R64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B65" t="n">
+        <v>135</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L65" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/B0018101.html</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>59</v>
+      </c>
+      <c r="R65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B66" t="n">
+        <v>135</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L66" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/F2870601.html</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>59</v>
+      </c>
+      <c r="R66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B67" t="n">
+        <v>135</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>hot-model, basketball, kids</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L67" t="n">
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>59</v>
+      </c>
+      <c r="R67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B68" t="n">
+        <v>135</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L68" t="n">
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>59</v>
+      </c>
+      <c r="R68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B69" t="n">
+        <v>135</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L69" t="n">
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31345901.html</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="n">
         <v>7</v>
       </c>
-      <c r="Q57" t="n">
-        <v>59</v>
-      </c>
-      <c r="R57" t="inlineStr"/>
+      <c r="Q69" t="n">
+        <v>59</v>
+      </c>
+      <c r="R69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B70" t="n">
+        <v>135</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L70" t="n">
+        <v>1</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>59</v>
+      </c>
+      <c r="R70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B71" t="n">
+        <v>135</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31360801.html</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>59</v>
+      </c>
+      <c r="R71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B72" t="n">
+        <v>135</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Saucony</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KBDSD.html</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>59</v>
+      </c>
+      <c r="R72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B73" t="n">
+        <v>135</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>59</v>
+      </c>
+      <c r="R73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B74" t="n">
+        <v>135</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L74" t="n">
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>59</v>
+      </c>
+      <c r="R74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B75" t="n">
+        <v>135</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>59</v>
+      </c>
+      <c r="R75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B76" t="n">
+        <v>135</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>59</v>
+      </c>
+      <c r="R76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B77" t="n">
+        <v>135</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>59</v>
+      </c>
+      <c r="R77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B78" t="n">
+        <v>135</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Skip To Main</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>#main</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>59</v>
+      </c>
+      <c r="R78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B79" t="n">
+        <v>135</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Store Pickup</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/help/store-pickup</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>59</v>
+      </c>
+      <c r="R79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B80" t="n">
+        <v>135</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KDRLS.html</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>59</v>
+      </c>
+      <c r="R80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B81" t="n">
+        <v>135</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/494KNTRL.html</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>59</v>
+      </c>
+      <c r="R81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B82" t="n">
+        <v>135</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/ugg/55095119.html</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>59</v>
+      </c>
+      <c r="R82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B83" t="n">
+        <v>135</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Upcoming</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>59</v>
+      </c>
+      <c r="R83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="15" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B84" t="n">
+        <v>135</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>lifestyle, exclusive</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VN08VYA6.html</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>59</v>
+      </c>
+      <c r="R84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="15" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>hot-model, retro, kids</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>50</v>
+      </c>
+      <c r="R85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="15" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Shoes Air Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>50</v>
+      </c>
+      <c r="R86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="15" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>1</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>50</v>
+      </c>
+      <c r="R87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>1</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>50</v>
+      </c>
+      <c r="R88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="15" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>hot-model, running</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>50</v>
+      </c>
+      <c r="R89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="15" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>1</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>50</v>
+      </c>
+      <c r="R90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B91" t="n">
+        <v>130</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>59</v>
+      </c>
+      <c r="R91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B92" t="n">
+        <v>130</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>59</v>
+      </c>
+      <c r="R92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B93" t="n">
+        <v>130</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>59</v>
+      </c>
+      <c r="R93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B94" t="n">
+        <v>130</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>59</v>
+      </c>
+      <c r="R94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8384,7 +13959,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  56 releases</t>
+          <t>Next 35 Days  ·  93 releases</t>
         </is>
       </c>
     </row>
@@ -8402,7 +13977,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -8463,7 +14038,7 @@
       </c>
       <c r="B10" s="26" t="inlineStr">
         <is>
-          <t>$203</t>
+          <t>$173</t>
         </is>
       </c>
       <c r="C10" s="21" t="n"/>
@@ -8520,7 +14095,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -8528,7 +14103,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>56</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -8538,7 +14113,7 @@
         </is>
       </c>
       <c r="B16" s="27" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C16" s="35" t="inlineStr">
         <is>
@@ -8563,7 +14138,7 @@
         </is>
       </c>
       <c r="B19" s="25" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C19" s="21" t="n"/>
       <c r="D19" s="21" t="n"/>
@@ -8582,7 +14157,7 @@
         </is>
       </c>
       <c r="B22" s="39" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C22" s="40" t="inlineStr">
         <is>
@@ -8598,11 +14173,11 @@
         </is>
       </c>
       <c r="B23" s="39" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C23" s="40" t="inlineStr">
         <is>
-          <t>█████████</t>
+          <t>███████████</t>
         </is>
       </c>
       <c r="D23" s="21" t="n"/>
@@ -8614,11 +14189,11 @@
         </is>
       </c>
       <c r="B24" s="39" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C24" s="40" t="inlineStr">
         <is>
-          <t>███████</t>
+          <t>█████</t>
         </is>
       </c>
       <c r="D24" s="21" t="n"/>
@@ -8630,7 +14205,7 @@
         </is>
       </c>
       <c r="B25" s="39" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C25" s="40" t="inlineStr">
         <is>
@@ -8642,11 +14217,11 @@
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="38" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B26" s="39" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26" s="40" t="inlineStr">
         <is>
@@ -8658,11 +14233,11 @@
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="38" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="B27" s="39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C27" s="40" t="inlineStr">
         <is>
@@ -8678,7 +14253,7 @@
         </is>
       </c>
       <c r="B28" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="40" t="inlineStr">
         <is>
@@ -8694,7 +14269,7 @@
         </is>
       </c>
       <c r="B29" s="39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="40" t="inlineStr">
         <is>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -741,7 +741,7 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="67" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -1324,20 +1324,18 @@
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B12" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46112</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>16</v>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1345,7 +1343,7 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1354,23 +1352,23 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1378,7 +1376,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1398,7 +1396,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1415,15 +1413,19 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -1435,7 +1437,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1455,7 +1457,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1472,19 +1474,15 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1496,7 +1494,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1538,7 +1536,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
@@ -1557,10 +1555,130 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="C16" s="5" t="inlineStr"/>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="K16" s="12" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="L16" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr"/>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
           <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
-      <c r="Q15" s="12" t="inlineStr"/>
+      <c r="Q16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1577,13 +1695,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -1635,22 +1753,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -1658,29 +1776,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-20T06:38:04Z</t>
+          <t>2026-03-20T17:56:18Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -1688,1207 +1806,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>App entry Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Contact Us</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Kobe V Protro MENS • METALLIC SILVER/TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Vans</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fragment Design x Nike Book 2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Fragment Design x Nike Mind 001</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS PRE-SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Launched</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike Air Max 90 QS</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike Book 2 MENS • MULTI/SAIL/GAME ROYAL</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike GT Future</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 "At Dawn"</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike Kobe Air Force 1 Low MENS • WHITE/TEAM RED</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Kobe Off Court Slides MENS • TEAM RED/WHITE</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Order Status</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PUMA MB 05 Melo World MENS • TEAL/RED</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Returns-Exchanges</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Shipping Info</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Store Pickup</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Saucony</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • BLACK/DARK SHADOW</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • DEEP CORAL/SACHET PINK</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides GIRLS GRADE SCHOOL • NATURAL/SEA SALT</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>UGG Fluff Yeah Slides WOMENS • BLACK/GREY</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Upcoming</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-20T06:38:04Z</t>
+          <t>2026-03-20T17:56:18Z</t>
         </is>
       </c>
     </row>
@@ -2903,7 +1821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2913,7 +1831,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="63" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="7" customWidth="1" min="9" max="9"/>
     <col width="21" customWidth="1" min="10" max="10"/>
     <col width="54" customWidth="1" min="11" max="11"/>
@@ -3548,14 +2466,14 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46113</v>
+        <v>46112</v>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3570,28 +2488,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -3599,16 +2517,16 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
@@ -3636,15 +2554,19 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>retro, women</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -3661,13 +2583,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -3698,19 +2620,15 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -3727,13 +2645,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -3769,7 +2687,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3793,7 +2711,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -3805,6 +2723,138 @@
         <v>59</v>
       </c>
       <c r="R13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B14" t="n">
+        <v>130</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vans</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>59</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>hot-model, basketball</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>50</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3997,7 +3047,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  12 releases</t>
+          <t>Next 35 Days  ·  14 releases</t>
         </is>
       </c>
     </row>
@@ -4015,7 +3065,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -4133,7 +3183,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -4141,7 +3191,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -4176,7 +3226,7 @@
         </is>
       </c>
       <c r="B19" s="38" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
@@ -4196,7 +3246,7 @@
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>█████████████</t>
+          <t>██████████</t>
         </is>
       </c>
       <c r="D20" s="21" t="n"/>
@@ -4212,7 +3262,7 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>███████</t>
+          <t>█████</t>
         </is>
       </c>
       <c r="D21" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -1695,17 +1695,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1747,66 +1747,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-20T17:56:18Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-20T17:56:18Z</t>
         </is>
       </c>
     </row>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -852,7 +852,7 @@
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
-        <v>46102</v>
+        <v>46104</v>
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="F4" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="inlineStr">
         <is>
@@ -880,17 +880,17 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="L4" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr"/>
@@ -904,14 +904,14 @@
       </c>
       <c r="P4" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="B5" s="5" t="inlineStr"/>
       <c r="C5" s="5" t="inlineStr"/>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -939,17 +939,17 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
@@ -963,14 +963,14 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
@@ -1062,7 +1062,7 @@
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
@@ -1081,14 +1081,14 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
       <c r="C8" s="5" t="inlineStr"/>
@@ -1099,7 +1099,7 @@
         </is>
       </c>
       <c r="F8" s="8" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
@@ -1152,13 +1152,13 @@
       <c r="B9" s="5" t="inlineStr"/>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="n">
-        <v>22</v>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="L9" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr"/>
@@ -1199,25 +1199,25 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B10" s="5" t="inlineStr"/>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>12</v>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="n">
+        <v>28</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1234,17 +1234,17 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="M10" s="6" t="inlineStr"/>
@@ -1258,14 +1258,14 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="B11" s="5" t="inlineStr"/>
       <c r="C11" s="5" t="inlineStr"/>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="F11" s="8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1293,17 +1293,17 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="L11" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="M11" s="6" t="inlineStr"/>
@@ -1317,25 +1317,27 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr"/>
+        <v>46113</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>130</v>
+      </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>24</v>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1343,7 +1345,7 @@
         </is>
       </c>
       <c r="H12" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
@@ -1352,23 +1354,23 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr"/>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O12" s="6" t="n">
@@ -1376,7 +1378,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
@@ -1396,7 +1398,7 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
@@ -1413,19 +1415,15 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -1437,7 +1435,7 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
@@ -1457,7 +1455,7 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1474,15 +1472,19 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L14" s="12" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="L14" s="12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="M14" s="6" t="inlineStr"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1494,7 +1496,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
@@ -1536,7 +1538,7 @@
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
@@ -1555,27 +1557,25 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46113</v>
-      </c>
-      <c r="B16" s="5" t="n">
-        <v>130</v>
-      </c>
+        <v>46115</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>7</v>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1592,23 +1592,23 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="O16" s="6" t="n">
@@ -1616,69 +1616,10 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="Q16" s="12" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr"/>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F17" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="L17" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="M17" s="6" t="inlineStr"/>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="O17" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" s="12" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="Q17" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1695,17 +1636,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1747,6 +1688,96 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:34:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Shoes Air Jordan 14 Retro</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:34:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-03-22T06:34:29Z</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1878,7 +1909,7 @@
     </row>
     <row r="2">
       <c r="A2" s="15" t="n">
-        <v>46102</v>
+        <v>46104</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
@@ -1900,17 +1931,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 14 Retro "Black/University Blue"</t>
+          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1929,13 +1960,13 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q2" t="n">
         <v>50</v>
@@ -1944,7 +1975,7 @@
     </row>
     <row r="3">
       <c r="A3" s="15" t="n">
-        <v>46102</v>
+        <v>46107</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -1966,17 +1997,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Shoes Air Jordan 14 Retro</t>
+          <t>Air Max 90 Vast Grey and Cool Grey</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -1995,13 +2026,13 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-14-retro-black-and-university-blue</t>
+          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q3" t="n">
         <v>50</v>
@@ -2010,7 +2041,7 @@
     </row>
     <row r="4">
       <c r="A4" s="15" t="n">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
@@ -2037,12 +2068,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Kobe 5 Protro Metallic Silver and Team Red</t>
+          <t>Air Max 95 Big Bubble Multi-Color</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -2061,7 +2092,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/kobe-5-protro-metallic-silver-and-team-red</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -2103,7 +2134,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>Air Max 95 Big Bubble Volt and University Red</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2127,7 +2158,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2142,7 +2173,7 @@
     </row>
     <row r="6">
       <c r="A6" s="15" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B6" t="n">
         <v>0</v>
@@ -2169,12 +2200,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>running, exclusive</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -2193,13 +2224,13 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Q6" t="n">
         <v>50</v>
@@ -2215,7 +2246,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2235,12 +2266,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2259,13 +2290,13 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="Q7" t="n">
         <v>50</v>
@@ -2274,14 +2305,14 @@
     </row>
     <row r="8">
       <c r="A8" s="15" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2296,17 +2327,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>kids</t>
+          <t>hot-model, retro, kids</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2325,13 +2356,13 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="Q8" t="n">
         <v>50</v>
@@ -2340,7 +2371,7 @@
     </row>
     <row r="9">
       <c r="A9" s="15" t="n">
-        <v>46109</v>
+        <v>46112</v>
       </c>
       <c r="B9" t="n">
         <v>0</v>
@@ -2362,17 +2393,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
+          <t>hot-model, skateboarding</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2391,13 +2422,13 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Q9" t="n">
         <v>50</v>
@@ -2406,14 +2437,14 @@
     </row>
     <row r="10">
       <c r="A10" s="15" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2428,28 +2459,28 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
+          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>hot-model, skateboarding</t>
+          <t>retro, women</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -2457,16 +2488,16 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
@@ -2494,19 +2525,15 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>retro, women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
@@ -2523,13 +2550,13 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
         <v>59</v>
@@ -2560,15 +2587,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Vans</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
@@ -2585,13 +2616,13 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q12" t="n">
         <v>59</v>
@@ -2627,7 +2658,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2651,7 +2682,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -2666,14 +2697,14 @@
     </row>
     <row r="14">
       <c r="A14" s="15" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="B14" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2688,28 +2719,28 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="L14" t="n">
@@ -2717,84 +2748,18 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="R14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>playwright-linkscan</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/upcoming</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://www.nike.com/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>50</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2987,7 +2952,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>Next 35 Days  ·  14 releases</t>
+          <t>Next 35 Days  ·  13 releases</t>
         </is>
       </c>
     </row>
@@ -3005,7 +2970,7 @@
         </is>
       </c>
       <c r="B5" s="20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="21" t="n"/>
@@ -3123,7 +3088,7 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="32" t="inlineStr">
         <is>
@@ -3131,7 +3096,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
@@ -3166,7 +3131,7 @@
         </is>
       </c>
       <c r="B19" s="38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
@@ -3182,11 +3147,11 @@
         </is>
       </c>
       <c r="B20" s="38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>██████████</t>
+          <t>████</t>
         </is>
       </c>
       <c r="D20" s="21" t="n"/>
@@ -3202,7 +3167,7 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>█████</t>
+          <t>████</t>
         </is>
       </c>
       <c r="D21" s="21" t="n"/>

--- a/output/monthly_tracker.xlsx
+++ b/output/monthly_tracker.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -328,6 +328,9 @@
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -727,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -740,8 +743,8 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="67" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="70" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
     <col width="21" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -911,9 +914,11 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C5" s="5" t="inlineStr"/>
       <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr">
@@ -922,7 +927,7 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" s="9" t="inlineStr">
         <is>
@@ -930,7 +935,7 @@
         </is>
       </c>
       <c r="H5" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
@@ -939,23 +944,23 @@
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>Air Max 90 Vast Grey and Cool Grey</t>
+          <t>Jordan Air Jordan 3 Retro OG MENS • SAIL/JADE AURA/YELLOW</t>
         </is>
       </c>
       <c r="L5" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="M5" s="6" t="inlineStr"/>
       <c r="N5" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O5" s="6" t="n">
@@ -963,25 +968,27 @@
       </c>
       <c r="P5" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-90-vast-grey-and-cool-grey</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4396100.html</t>
         </is>
       </c>
       <c r="Q5" s="12" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C6" s="5" t="inlineStr"/>
       <c r="D6" s="6" t="inlineStr"/>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n">
-        <v>24</v>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
@@ -989,7 +996,7 @@
         </is>
       </c>
       <c r="H6" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
@@ -998,23 +1005,23 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Multi-Color</t>
+          <t>Jordan Retro 3 BOYS GRADE SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L6" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M6" s="6" t="inlineStr"/>
       <c r="N6" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O6" s="6" t="n">
@@ -1022,25 +1029,27 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-multi-color</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4758100.html</t>
         </is>
       </c>
       <c r="Q6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>46107</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C7" s="5" t="inlineStr"/>
       <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="n">
-        <v>24</v>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>16</v>
       </c>
       <c r="G7" s="9" t="inlineStr">
         <is>
@@ -1048,7 +1057,7 @@
         </is>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
@@ -1057,23 +1066,23 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>Air Max 95 Big Bubble Volt and University Red</t>
+          <t>Jordan Retro 3 BOYS PRE-SCHOOL • WHITE/PINK/GREEN</t>
         </is>
       </c>
       <c r="L7" s="12" t="inlineStr">
         <is>
-          <t>hot-model, running</t>
+          <t>retro, kids</t>
         </is>
       </c>
       <c r="M7" s="6" t="inlineStr"/>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O7" s="6" t="n">
@@ -1081,25 +1090,27 @@
       </c>
       <c r="P7" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-max-95-big-bubble-volt-and-university-red</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/F4757100.html</t>
         </is>
       </c>
       <c r="Q7" s="12" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C8" s="5" t="inlineStr"/>
       <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="n">
-        <v>22</v>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G8" s="9" t="inlineStr">
         <is>
@@ -1107,7 +1118,7 @@
         </is>
       </c>
       <c r="H8" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
@@ -1116,23 +1127,23 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>Air Zoom G.T. Cut Orange Pulse and Persian Violet</t>
+          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
         </is>
       </c>
       <c r="L8" s="12" t="inlineStr">
         <is>
-          <t>running, exclusive</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M8" s="6" t="inlineStr"/>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O8" s="6" t="n">
@@ -1140,16 +1151,18 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-zoom-gt-cut-orange-pulse-and-persian-violet-1</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/62262063.html</t>
         </is>
       </c>
       <c r="Q8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>46108</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C9" s="5" t="inlineStr"/>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="13" t="inlineStr">
@@ -1158,7 +1171,7 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G9" s="9" t="inlineStr">
         <is>
@@ -1166,7 +1179,7 @@
         </is>
       </c>
       <c r="H9" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
@@ -1175,23 +1188,19 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="L9" s="12" t="inlineStr">
-        <is>
-          <t>kids</t>
-        </is>
-      </c>
+          <t>Reebok Angel Reese 1 MENS • ATOMIC AQUA/DREAM PURPLE</t>
+        </is>
+      </c>
+      <c r="L9" s="12" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr"/>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O9" s="6" t="n">
@@ -1199,16 +1208,18 @@
       </c>
       <c r="P9" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://www.footlocker.com/release-calendar/reebok/10262837.html</t>
         </is>
       </c>
       <c r="Q9" s="12" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C10" s="5" t="inlineStr"/>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="7" t="inlineStr">
@@ -1217,7 +1228,7 @@
         </is>
       </c>
       <c r="F10" s="8" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="G10" s="9" t="inlineStr">
         <is>
@@ -1225,7 +1236,7 @@
         </is>
       </c>
       <c r="H10" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
@@ -1234,23 +1245,27 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>Baby/Toddler Shoes Jordan 3 Retro "Sail and Jade Aura"</t>
+          <t>ENTRIES OPEN App Entry Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
         </is>
       </c>
       <c r="L10" s="12" t="inlineStr">
         <is>
-          <t>hot-model, retro, kids</t>
-        </is>
-      </c>
-      <c r="M10" s="6" t="inlineStr"/>
+          <t>hot-model, running, women, exclusive</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>App</t>
+        </is>
+      </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O10" s="6" t="n">
@@ -1258,25 +1273,27 @@
       </c>
       <c r="P10" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/air-jordan-3-sail-and-jade-aura</t>
+          <t>https://www.footlocker.com/release-calendar/nike/52599600.html</t>
         </is>
       </c>
       <c r="Q10" s="12" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>46112</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C11" s="5" t="inlineStr"/>
       <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>24</v>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="n">
+        <v>12</v>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
@@ -1284,7 +1301,7 @@
         </is>
       </c>
       <c r="H11" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
@@ -1298,18 +1315,14 @@
       </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>NOTE Manchester x Nike SB Dunk Low Flax and Summit White</t>
-        </is>
-      </c>
-      <c r="L11" s="12" t="inlineStr">
-        <is>
-          <t>hot-model, skateboarding</t>
-        </is>
-      </c>
+          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr"/>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="O11" s="6" t="n">
@@ -1317,27 +1330,27 @@
       </c>
       <c r="P11" s="12" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/t/note-manchester-nike-sb-dunk-low-flax-and-summit-white</t>
+          <t>https://www.footlocker.com/release-calendar/nike/0794400.html</t>
         </is>
       </c>
       <c r="Q11" s="12" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>46113</v>
+        <v>46105</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C12" s="5" t="inlineStr"/>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F12" s="14" t="n">
-        <v>16</v>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
@@ -1354,17 +1367,17 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>Jordan Retro 4 WOMENS • ICED CARMINE/MILK</t>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
         <is>
-          <t>retro, women</t>
+          <t>hot-model, basketball, kids</t>
         </is>
       </c>
       <c r="M12" s="6" t="inlineStr"/>
@@ -1378,17 +1391,17 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/HV0823.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="Q12" s="12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>46113</v>
+        <v>46105</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C13" s="5" t="inlineStr"/>
       <c r="D13" s="6" t="inlineStr"/>
@@ -1420,10 +1433,14 @@
       </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="L13" s="12" t="inlineStr"/>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
+        <is>
+          <t>kids</t>
+        </is>
+      </c>
       <c r="M13" s="6" t="inlineStr"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
@@ -1435,27 +1452,27 @@
       </c>
       <c r="P13" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="Q13" s="12" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>46113</v>
+        <v>46105</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C14" s="5" t="inlineStr"/>
       <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>7</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
@@ -1472,17 +1489,17 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>Vans LX Authentic 44 Archive WOMENS • BLACK/BLUE</t>
+          <t>Nike Pre-School Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L14" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M14" s="6" t="inlineStr"/>
@@ -1496,27 +1513,27 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNDB8CJI.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95461075.html</t>
         </is>
       </c>
       <c r="Q14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>46113</v>
+        <v>46105</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>130</v>
+        <v>165</v>
       </c>
       <c r="C15" s="5" t="inlineStr"/>
       <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="F15" s="14" t="n">
-        <v>7</v>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>24</v>
       </c>
       <c r="G15" s="9" t="inlineStr">
         <is>
@@ -1533,17 +1550,17 @@
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>Vans</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>Vans LX OMU Authentic Pony WOMENS • MARSH/LEOPARD</t>
+          <t>Nike Toddler Air Max 95 GIRLS TODDLER • BLACK/PINK FOAM/MEDIUM GREY</t>
         </is>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, running, kids</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr"/>
@@ -1557,25 +1574,27 @@
       </c>
       <c r="P15" s="12" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/vans/VNEK4UOV.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/95462075.html</t>
         </is>
       </c>
       <c r="Q15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>46115</v>
-      </c>
-      <c r="B16" s="5" t="inlineStr"/>
+        <v>46105</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>165</v>
+      </c>
       <c r="C16" s="5" t="inlineStr"/>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="n">
-        <v>24</v>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>7</v>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
@@ -1583,7 +1602,7 @@
         </is>
       </c>
       <c r="H16" s="10" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
@@ -1592,34 +1611,1560 @@
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>PUMA MB.05 Melo World BOYS GRADE SCHOOL • AQUATIC GREEN/FOR ALL TIME RED</t>
         </is>
       </c>
       <c r="L16" s="12" t="inlineStr">
         <is>
-          <t>hot-model, basketball</t>
+          <t>kids</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr"/>
       <c r="N16" s="6" t="inlineStr">
         <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31280401.html</t>
+        </is>
+      </c>
+      <c r="Q16" s="12" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C17" s="5" t="inlineStr"/>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F17" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>PUMA MB.05 Melo World MENS • TEAL/RED</t>
+        </is>
+      </c>
+      <c r="L17" s="12" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/puma/31279801.html</t>
+        </is>
+      </c>
+      <c r="Q17" s="12" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C18" s="5" t="inlineStr"/>
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K18" s="12" t="inlineStr">
+        <is>
+          <t>Contact Us</t>
+        </is>
+      </c>
+      <c r="L18" s="12" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/articles/360046621694-Contact-Us</t>
+        </is>
+      </c>
+      <c r="Q18" s="12" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C19" s="5" t="inlineStr"/>
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F19" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>Launched</t>
+        </is>
+      </c>
+      <c r="L19" s="12" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr"/>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/launched</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F20" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I20" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K20" s="12" t="inlineStr">
+        <is>
+          <t>Order Status</t>
+        </is>
+      </c>
+      <c r="L20" s="12" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr"/>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/order/search</t>
+        </is>
+      </c>
+      <c r="Q20" s="12" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K21" s="12" t="inlineStr">
+        <is>
+          <t>Returns-Exchanges</t>
+        </is>
+      </c>
+      <c r="L21" s="12" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr"/>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002167714</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>165</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="F22" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I22" s="11" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="K22" s="12" t="inlineStr">
+        <is>
+          <t>Shipping Info</t>
+        </is>
+      </c>
+      <c r="L22" s="12" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr"/>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>https://help.footlocker.com/hc/en-us/categories/360002182413</t>
+        </is>
+      </c>
+      <c r="Q22" s="12" t="inlineStr"/>
+ 